--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -417,7 +417,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>4 de junio de 2026</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>4 de junio de 2026</t>
+          <t>25 de mayo de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -478,40 +478,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41350.53</v>
+      </c>
+      <c r="H4" t="n">
+        <v>123990.17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>165340.7</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>6333.21</v>
-      </c>
-      <c r="H4" t="n">
-        <v>145097.32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>151430.53</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>31360.93</v>
       </c>
       <c r="L4" t="n">
-        <v>5478.23</v>
+        <v>72521.25</v>
       </c>
       <c r="M4" t="n">
-        <v>5478.23</v>
+        <v>103882.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,40 +521,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1985.9</v>
       </c>
       <c r="H5" t="n">
-        <v>14473.52</v>
+        <v>67664.03999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>14473.52</v>
+        <v>69649.94</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2126038.83</v>
+        <v>22574.41</v>
       </c>
       <c r="L5" t="n">
-        <v>2183932.9</v>
+        <v>141422.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4309971.73</v>
+        <v>163996.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -573,13 +573,13 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>5165.6</v>
+        <v>32258.07</v>
       </c>
       <c r="H6" t="n">
-        <v>8472.299999999999</v>
+        <v>28647.06</v>
       </c>
       <c r="I6" t="n">
-        <v>13637.9</v>
+        <v>60905.13</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10200.24</v>
+        <v>59360.72</v>
       </c>
       <c r="M6" t="n">
-        <v>10200.24</v>
+        <v>59360.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7576.13</v>
+        <v>59212.9</v>
       </c>
       <c r="I7" t="n">
-        <v>7576.13</v>
+        <v>59212.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,41 +631,41 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>59833.9</v>
+        <v>251933.62</v>
       </c>
       <c r="M7" t="n">
-        <v>59833.9</v>
+        <v>251933.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1602.22</v>
       </c>
       <c r="H8" t="n">
-        <v>6311.07</v>
+        <v>54162.73</v>
       </c>
       <c r="I8" t="n">
-        <v>6311.07</v>
+        <v>55764.95</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>81428.77</v>
+        <v>123887.07</v>
       </c>
       <c r="M8" t="n">
-        <v>81428.77</v>
+        <v>123887.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3249.59</v>
       </c>
       <c r="H9" t="n">
-        <v>6286.27</v>
+        <v>31354.39</v>
       </c>
       <c r="I9" t="n">
-        <v>6286.27</v>
+        <v>34603.98</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1484.19</v>
       </c>
       <c r="L9" t="n">
-        <v>12361.96</v>
+        <v>36221.39</v>
       </c>
       <c r="M9" t="n">
-        <v>12361.96</v>
+        <v>37705.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,83 +736,83 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1572.63</v>
       </c>
       <c r="H10" t="n">
-        <v>5622.65</v>
+        <v>31364.28</v>
       </c>
       <c r="I10" t="n">
-        <v>5622.65</v>
+        <v>32936.91</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>122442.35</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>145550.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-9557.41</v>
       </c>
       <c r="H11" t="n">
-        <v>5571.56</v>
+        <v>41946.23</v>
       </c>
       <c r="I11" t="n">
-        <v>5571.56</v>
+        <v>32388.82</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1368208.15</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>118391.29</v>
+        <v>10262.23</v>
       </c>
       <c r="M11" t="n">
-        <v>1486599.44</v>
+        <v>10262.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,22 +822,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>24295.37</v>
       </c>
       <c r="H12" t="n">
-        <v>5564.58</v>
+        <v>7700.31</v>
       </c>
       <c r="I12" t="n">
-        <v>5564.58</v>
+        <v>31995.68</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,41 +846,41 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>50165.88</v>
+        <v>80014.48</v>
       </c>
       <c r="M12" t="n">
-        <v>50165.88</v>
+        <v>80014.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2455.46</v>
       </c>
       <c r="H13" t="n">
-        <v>5403.98</v>
+        <v>26614.68</v>
       </c>
       <c r="I13" t="n">
-        <v>5403.98</v>
+        <v>29070.14</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9644.059999999999</v>
+        <v>23159.79</v>
       </c>
       <c r="M13" t="n">
-        <v>9644.059999999999</v>
+        <v>23159.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>22698.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4747.43</v>
+        <v>5178.6</v>
       </c>
       <c r="I14" t="n">
-        <v>4747.43</v>
+        <v>27877.49</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3224.48</v>
+        <v>10866.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3224.48</v>
+        <v>10866.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1562.11</v>
       </c>
       <c r="H15" t="n">
-        <v>4670.98</v>
+        <v>22160.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4670.98</v>
+        <v>23722.71</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2316.79</v>
+        <v>26942.72</v>
       </c>
       <c r="M15" t="n">
-        <v>2316.79</v>
+        <v>26942.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4480.67</v>
+        <v>22804.64</v>
       </c>
       <c r="I16" t="n">
-        <v>4480.67</v>
+        <v>22804.64</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>30607.01</v>
+        <v>71298.36</v>
       </c>
       <c r="M16" t="n">
-        <v>30607.01</v>
+        <v>71298.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1494.27</v>
       </c>
       <c r="H17" t="n">
-        <v>2976.13</v>
+        <v>21235.73</v>
       </c>
       <c r="I17" t="n">
-        <v>2976.13</v>
+        <v>22730</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8829.190000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>8829.190000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2695.94</v>
+        <v>16136.19</v>
       </c>
       <c r="I18" t="n">
-        <v>2695.94</v>
+        <v>16136.19</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,26 +1104,26 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>244220.82</v>
+        <v>9134.42</v>
       </c>
       <c r="M18" t="n">
-        <v>244220.82</v>
+        <v>9134.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>81618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>ALEJANDRA IVETTE PEDROZA MACIAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2424.76</v>
+        <v>15147.88</v>
       </c>
       <c r="I19" t="n">
-        <v>2424.76</v>
+        <v>15147.88</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,26 +1147,26 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>41273.83</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>41273.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2187.26</v>
+        <v>13213.75</v>
       </c>
       <c r="I20" t="n">
-        <v>2187.26</v>
+        <v>13213.75</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>101901.74</v>
+        <v>41779.37</v>
       </c>
       <c r="M20" t="n">
-        <v>101901.74</v>
+        <v>41779.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1806.57</v>
+        <v>10579.65</v>
       </c>
       <c r="I21" t="n">
-        <v>1806.57</v>
+        <v>10579.65</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>16259.14</v>
+        <v>62229</v>
       </c>
       <c r="M21" t="n">
-        <v>16259.14</v>
+        <v>62229</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1766.71</v>
+        <v>9656.709999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>1766.71</v>
+        <v>9656.709999999999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>12660.79</v>
+        <v>90524.08</v>
       </c>
       <c r="M22" t="n">
-        <v>12660.79</v>
+        <v>90524.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1752.92</v>
+        <v>9315.52</v>
       </c>
       <c r="I23" t="n">
-        <v>1752.92</v>
+        <v>9315.52</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>11896.87</v>
+        <v>11444.81</v>
       </c>
       <c r="M23" t="n">
-        <v>11896.87</v>
+        <v>11444.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1743.02</v>
+        <v>8173.66</v>
       </c>
       <c r="I24" t="n">
-        <v>1743.02</v>
+        <v>8173.66</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>92342.45</v>
+        <v>55703</v>
       </c>
       <c r="M24" t="n">
-        <v>92342.45</v>
+        <v>55703</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1742.67</v>
+        <v>7739.54</v>
       </c>
       <c r="I25" t="n">
-        <v>1742.67</v>
+        <v>7739.54</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>100823.26</v>
+        <v>11567.17</v>
       </c>
       <c r="M25" t="n">
-        <v>100823.26</v>
+        <v>11567.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1699.44</v>
+        <v>7482.55</v>
       </c>
       <c r="I26" t="n">
-        <v>1699.44</v>
+        <v>7482.55</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>14986.62</v>
+        <v>2087.15</v>
       </c>
       <c r="M26" t="n">
-        <v>14986.62</v>
+        <v>2087.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1635.54</v>
+        <v>6933.13</v>
       </c>
       <c r="I27" t="n">
-        <v>1635.54</v>
+        <v>6933.13</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,26 +1491,26 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>10748.48</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>10748.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>662.91</v>
+        <v>6833.65</v>
       </c>
       <c r="I28" t="n">
-        <v>662.91</v>
+        <v>6833.65</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8746.040000000001</v>
+        <v>38580.59</v>
       </c>
       <c r="M28" t="n">
-        <v>8746.040000000001</v>
+        <v>38580.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>48.79</v>
+        <v>5556.45</v>
       </c>
       <c r="I29" t="n">
-        <v>48.79</v>
+        <v>5556.45</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>16842.35</v>
+        <v>2506.7</v>
       </c>
       <c r="M29" t="n">
-        <v>16842.35</v>
+        <v>2506.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,38 +1608,38 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4884.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>4884.07</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>17081.33</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>35934.94</v>
+        <v>2603.2</v>
       </c>
       <c r="M30" t="n">
-        <v>53016.27</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,28 +1651,28 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4745.09</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4745.09</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>15585.09</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>71404.87</v>
+        <v>3222.89</v>
       </c>
       <c r="M31" t="n">
-        <v>86989.96000000001</v>
+        <v>3222.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3982.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3982.49</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>4811.58</v>
+        <v>14324.23</v>
       </c>
       <c r="M32" t="n">
-        <v>4811.58</v>
+        <v>14324.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3909.35</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>3909.35</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>41806.1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>41806.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3504.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3504.11</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2584.02</v>
+        <v>16677.83</v>
       </c>
       <c r="M34" t="n">
-        <v>2584.02</v>
+        <v>16677.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2974.66</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2974.66</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>7419.03</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7419.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2315.7</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2315.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,26 +1878,26 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>4865.25</v>
+        <v>5192.26</v>
       </c>
       <c r="M36" t="n">
-        <v>4865.25</v>
+        <v>5192.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1851.71</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1851.71</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,26 +1921,26 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>5559.19</v>
+        <v>7406.83</v>
       </c>
       <c r="M37" t="n">
-        <v>5559.19</v>
+        <v>7406.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,28 +1952,28 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1844.64</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1844.64</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2001.98</v>
       </c>
       <c r="L38" t="n">
-        <v>43244.52</v>
+        <v>105783.12</v>
       </c>
       <c r="M38" t="n">
-        <v>43244.52</v>
+        <v>107785.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1805.68</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1805.68</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,26 +2007,26 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>9678.940000000001</v>
+        <v>18056.81</v>
       </c>
       <c r="M39" t="n">
-        <v>9678.940000000001</v>
+        <v>18056.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1760.54</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1760.54</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>15738.58</v>
+        <v>3201.19</v>
       </c>
       <c r="M40" t="n">
-        <v>15738.58</v>
+        <v>3201.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1752.06</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1752.06</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3911.23</v>
+        <v>14686.63</v>
       </c>
       <c r="M41" t="n">
-        <v>3911.23</v>
+        <v>14686.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1603.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1603.11</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>62978.13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>62978.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>662.59</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>662.59</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>167844.24</v>
+        <v>10490.07</v>
       </c>
       <c r="M43" t="n">
-        <v>167844.24</v>
+        <v>10490.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,16 +2216,188 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>19016.41</v>
       </c>
       <c r="L44" t="n">
-        <v>5557.87</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5557.87</v>
+        <v>19016.41</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>116876</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>16255.46</v>
+      </c>
+      <c r="M45" t="n">
+        <v>16255.46</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>113076</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4584.04</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4584.04</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>111056</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JORGE ANTONIO LUNA LARA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10951.05</v>
+      </c>
+      <c r="M47" t="n">
+        <v>10951.05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JOSE RENE DE ALBA MORALES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>72331.92</v>
+      </c>
+      <c r="M48" t="n">
+        <v>72331.92</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>25 de mayo de 2026</t>
+          <t>5 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,50 +468,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>41350.53</v>
+        <v>1368208.15</v>
       </c>
       <c r="H4" t="n">
-        <v>123990.17</v>
+        <v>5571.56</v>
       </c>
       <c r="I4" t="n">
-        <v>165340.7</v>
+        <v>1373779.71</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>31360.93</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>72521.25</v>
+        <v>118391.29</v>
       </c>
       <c r="M4" t="n">
-        <v>103882.18</v>
+        <v>118391.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,25 +530,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1985.9</v>
+        <v>6333.21</v>
       </c>
       <c r="H5" t="n">
-        <v>67664.03999999999</v>
+        <v>145097.32</v>
       </c>
       <c r="I5" t="n">
-        <v>69649.94</v>
+        <v>151430.53</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>22574.41</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>141422.2</v>
+        <v>5478.23</v>
       </c>
       <c r="M5" t="n">
-        <v>163996.61</v>
+        <v>5478.23</v>
       </c>
     </row>
     <row r="6">
@@ -570,16 +570,16 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>32258.07</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>28647.06</v>
+        <v>16201.74</v>
       </c>
       <c r="I6" t="n">
-        <v>60905.13</v>
+        <v>16201.74</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>59360.72</v>
+        <v>81428.77</v>
       </c>
       <c r="M6" t="n">
-        <v>59360.72</v>
+        <v>81428.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,53 +619,53 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>59212.9</v>
+        <v>14473.52</v>
       </c>
       <c r="I7" t="n">
-        <v>59212.9</v>
+        <v>14473.52</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2126038.83</v>
       </c>
       <c r="L7" t="n">
-        <v>251933.62</v>
+        <v>2183932.9</v>
       </c>
       <c r="M7" t="n">
-        <v>251933.62</v>
+        <v>4309971.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1602.22</v>
+        <v>5165.6</v>
       </c>
       <c r="H8" t="n">
-        <v>54162.73</v>
+        <v>8472.299999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>55764.95</v>
+        <v>13637.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,59 +674,59 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>123887.07</v>
+        <v>10200.24</v>
       </c>
       <c r="M8" t="n">
-        <v>123887.07</v>
+        <v>10200.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3249.59</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>31354.39</v>
+        <v>9360.959999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>34603.98</v>
+        <v>9360.959999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1484.19</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>36221.39</v>
+        <v>237555.82</v>
       </c>
       <c r="M9" t="n">
-        <v>37705.58</v>
+        <v>237555.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,22 +736,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1572.63</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>31364.28</v>
+        <v>7576.13</v>
       </c>
       <c r="I10" t="n">
-        <v>32936.91</v>
+        <v>7576.13</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,41 +760,41 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>59833.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>59833.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-9557.41</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>41946.23</v>
+        <v>6286.27</v>
       </c>
       <c r="I11" t="n">
-        <v>32388.82</v>
+        <v>6286.27</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10262.23</v>
+        <v>12361.96</v>
       </c>
       <c r="M11" t="n">
-        <v>10262.23</v>
+        <v>12361.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,65 +822,65 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5622.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5622.65</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>24295.37</v>
-      </c>
-      <c r="H12" t="n">
-        <v>7700.31</v>
-      </c>
-      <c r="I12" t="n">
-        <v>31995.68</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>23108.1</v>
       </c>
       <c r="L12" t="n">
-        <v>80014.48</v>
+        <v>122442.35</v>
       </c>
       <c r="M12" t="n">
-        <v>80014.48</v>
+        <v>145550.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2455.46</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26614.68</v>
+        <v>5564.58</v>
       </c>
       <c r="I13" t="n">
-        <v>29070.14</v>
+        <v>5564.58</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>23159.79</v>
+        <v>50165.88</v>
       </c>
       <c r="M13" t="n">
-        <v>23159.79</v>
+        <v>50165.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>22698.89</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5178.6</v>
+        <v>5403.98</v>
       </c>
       <c r="I14" t="n">
-        <v>27877.49</v>
+        <v>5403.98</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10866.76</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>10866.76</v>
+        <v>9644.059999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1562.11</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>22160.6</v>
+        <v>4747.43</v>
       </c>
       <c r="I15" t="n">
-        <v>23722.71</v>
+        <v>4747.43</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>26942.72</v>
+        <v>3224.48</v>
       </c>
       <c r="M15" t="n">
-        <v>26942.72</v>
+        <v>3224.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>22804.64</v>
+        <v>4670.98</v>
       </c>
       <c r="I16" t="n">
-        <v>22804.64</v>
+        <v>4670.98</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>71298.36</v>
+        <v>2316.79</v>
       </c>
       <c r="M16" t="n">
-        <v>71298.36</v>
+        <v>2316.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1494.27</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>21235.73</v>
+        <v>4480.67</v>
       </c>
       <c r="I17" t="n">
-        <v>22730</v>
+        <v>4480.67</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8829.190000000001</v>
+        <v>30607.01</v>
       </c>
       <c r="M17" t="n">
-        <v>8829.190000000001</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>16136.19</v>
+        <v>4287.9</v>
       </c>
       <c r="I18" t="n">
-        <v>16136.19</v>
+        <v>4287.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9134.42</v>
+        <v>10139.19</v>
       </c>
       <c r="M18" t="n">
-        <v>9134.42</v>
+        <v>10139.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>81618</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALEJANDRA IVETTE PEDROZA MACIAS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>15147.88</v>
+        <v>3484.54</v>
       </c>
       <c r="I19" t="n">
-        <v>15147.88</v>
+        <v>3484.54</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>99081.39</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>99081.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>13213.75</v>
+        <v>2976.13</v>
       </c>
       <c r="I20" t="n">
-        <v>13213.75</v>
+        <v>2976.13</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>41779.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>41779.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>10579.65</v>
+        <v>2507.93</v>
       </c>
       <c r="I21" t="n">
-        <v>10579.65</v>
+        <v>2507.93</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>62229</v>
+        <v>3051.26</v>
       </c>
       <c r="M21" t="n">
-        <v>62229</v>
+        <v>3051.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9656.709999999999</v>
+        <v>2451.9</v>
       </c>
       <c r="I22" t="n">
-        <v>9656.709999999999</v>
+        <v>2451.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>90524.08</v>
+        <v>15738.58</v>
       </c>
       <c r="M22" t="n">
-        <v>90524.08</v>
+        <v>15738.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>9315.52</v>
+        <v>2424.76</v>
       </c>
       <c r="I23" t="n">
-        <v>9315.52</v>
+        <v>2424.76</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>11444.81</v>
+        <v>41273.83</v>
       </c>
       <c r="M23" t="n">
-        <v>11444.81</v>
+        <v>41273.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8173.66</v>
+        <v>2187.26</v>
       </c>
       <c r="I24" t="n">
-        <v>8173.66</v>
+        <v>2187.26</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>55703</v>
+        <v>101901.74</v>
       </c>
       <c r="M24" t="n">
-        <v>55703</v>
+        <v>101901.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>7739.54</v>
+        <v>1806.57</v>
       </c>
       <c r="I25" t="n">
-        <v>7739.54</v>
+        <v>1806.57</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>11567.17</v>
+        <v>16259.14</v>
       </c>
       <c r="M25" t="n">
-        <v>11567.17</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7482.55</v>
+        <v>1752.92</v>
       </c>
       <c r="I26" t="n">
-        <v>7482.55</v>
+        <v>1752.92</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2087.15</v>
+        <v>11896.87</v>
       </c>
       <c r="M26" t="n">
-        <v>2087.15</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6933.13</v>
+        <v>1743.02</v>
       </c>
       <c r="I27" t="n">
-        <v>6933.13</v>
+        <v>1743.02</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,26 +1491,26 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>92342.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>92342.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6833.65</v>
+        <v>1699.44</v>
       </c>
       <c r="I28" t="n">
-        <v>6833.65</v>
+        <v>1699.44</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>38580.59</v>
+        <v>14986.62</v>
       </c>
       <c r="M28" t="n">
-        <v>38580.59</v>
+        <v>14986.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5556.45</v>
+        <v>1635.54</v>
       </c>
       <c r="I29" t="n">
-        <v>5556.45</v>
+        <v>1635.54</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2506.7</v>
+        <v>10748.48</v>
       </c>
       <c r="M29" t="n">
-        <v>2506.7</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4884.07</v>
+        <v>662.91</v>
       </c>
       <c r="I30" t="n">
-        <v>4884.07</v>
+        <v>662.91</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2603.2</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>2603.2</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4745.09</v>
+        <v>48.79</v>
       </c>
       <c r="I31" t="n">
-        <v>4745.09</v>
+        <v>48.79</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,26 +1663,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3222.89</v>
+        <v>16842.35</v>
       </c>
       <c r="M31" t="n">
-        <v>3222.89</v>
+        <v>16842.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,38 +1694,38 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3982.49</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3982.49</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>17081.33</v>
       </c>
       <c r="L32" t="n">
-        <v>14324.23</v>
+        <v>35934.94</v>
       </c>
       <c r="M32" t="n">
-        <v>14324.23</v>
+        <v>53016.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,28 +1737,28 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3909.35</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3909.35</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>71404.87</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3504.11</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3504.11</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,26 +1792,26 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16677.83</v>
+        <v>4811.58</v>
       </c>
       <c r="M34" t="n">
-        <v>16677.83</v>
+        <v>4811.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2974.66</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2974.66</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>41806.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>41806.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2315.7</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2315.7</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,26 +1878,26 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>5192.26</v>
+        <v>2584.02</v>
       </c>
       <c r="M36" t="n">
-        <v>5192.26</v>
+        <v>2584.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1851.71</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1851.71</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,26 +1921,26 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>7406.83</v>
+        <v>7419.03</v>
       </c>
       <c r="M37" t="n">
-        <v>7406.83</v>
+        <v>7419.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,28 +1952,28 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1844.64</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1844.64</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2001.98</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>105783.12</v>
+        <v>4865.25</v>
       </c>
       <c r="M38" t="n">
-        <v>107785.1</v>
+        <v>4865.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1805.68</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1805.68</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,26 +2007,26 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>18056.81</v>
+        <v>43244.52</v>
       </c>
       <c r="M39" t="n">
-        <v>18056.81</v>
+        <v>43244.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1760.54</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1760.54</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3201.19</v>
+        <v>9678.940000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>3201.19</v>
+        <v>9678.940000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1752.06</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1752.06</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>14686.63</v>
+        <v>3911.23</v>
       </c>
       <c r="M41" t="n">
-        <v>14686.63</v>
+        <v>3911.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1603.11</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1603.11</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>62978.13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>62978.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>662.59</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>662.59</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10490.07</v>
+        <v>167844.24</v>
       </c>
       <c r="M43" t="n">
-        <v>10490.07</v>
+        <v>167844.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,188 +2216,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>19016.41</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>5557.87</v>
       </c>
       <c r="M44" t="n">
-        <v>19016.41</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>116876</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2856</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>16255.46</v>
-      </c>
-      <c r="M45" t="n">
-        <v>16255.46</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>113076</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>4584.04</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4584.04</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>111056</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>10951.05</v>
-      </c>
-      <c r="M47" t="n">
-        <v>10951.05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>72331.92</v>
-      </c>
-      <c r="M48" t="n">
-        <v>72331.92</v>
+        <v>5557.87</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>5 de junio de 2026</t>
+          <t>8 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>16201.74</v>
+        <v>22688.39</v>
       </c>
       <c r="I6" t="n">
-        <v>16201.74</v>
+        <v>22688.39</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9360.959999999999</v>
+        <v>11128.96</v>
       </c>
       <c r="I9" t="n">
-        <v>9360.959999999999</v>
+        <v>11128.96</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>237555.82</v>
+        <v>235787.82</v>
       </c>
       <c r="M9" t="n">
-        <v>237555.82</v>
+        <v>235787.82</v>
       </c>
     </row>
     <row r="10">
@@ -769,17 +769,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,38 +791,38 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6286.27</v>
+        <v>7389.36</v>
       </c>
       <c r="I11" t="n">
-        <v>6286.27</v>
+        <v>7389.36</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>23108.1</v>
       </c>
       <c r="L11" t="n">
-        <v>12361.96</v>
+        <v>120675.64</v>
       </c>
       <c r="M11" t="n">
-        <v>12361.96</v>
+        <v>143783.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,22 +834,22 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5622.65</v>
+        <v>6286.27</v>
       </c>
       <c r="I12" t="n">
-        <v>5622.65</v>
+        <v>6286.27</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>122442.35</v>
+        <v>12361.96</v>
       </c>
       <c r="M12" t="n">
-        <v>145550.45</v>
+        <v>12361.96</v>
       </c>
     </row>
     <row r="13">
@@ -898,7 +898,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5403.98</v>
+        <v>5438.63</v>
       </c>
       <c r="I14" t="n">
-        <v>5403.98</v>
+        <v>5438.63</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9644.059999999999</v>
+        <v>97127.28999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>9644.059999999999</v>
+        <v>97127.28999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4747.43</v>
+        <v>5403.98</v>
       </c>
       <c r="I15" t="n">
-        <v>4747.43</v>
+        <v>5403.98</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3224.48</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>3224.48</v>
+        <v>9644.059999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4670.98</v>
+        <v>5238.69</v>
       </c>
       <c r="I16" t="n">
-        <v>4670.98</v>
+        <v>5238.69</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2316.79</v>
+        <v>88846.77</v>
       </c>
       <c r="M16" t="n">
-        <v>2316.79</v>
+        <v>88846.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,28 +1049,28 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4480.67</v>
+        <v>4747.43</v>
       </c>
       <c r="I17" t="n">
-        <v>4480.67</v>
+        <v>4747.43</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4983.76</v>
       </c>
       <c r="L17" t="n">
-        <v>30607.01</v>
+        <v>3224.48</v>
       </c>
       <c r="M17" t="n">
-        <v>30607.01</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4287.9</v>
+        <v>4670.98</v>
       </c>
       <c r="I18" t="n">
-        <v>4287.9</v>
+        <v>4670.98</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>10139.19</v>
+        <v>2316.79</v>
       </c>
       <c r="M18" t="n">
-        <v>10139.19</v>
+        <v>2316.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3484.54</v>
+        <v>4480.67</v>
       </c>
       <c r="I19" t="n">
-        <v>3484.54</v>
+        <v>4480.67</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>99081.39</v>
+        <v>30607.01</v>
       </c>
       <c r="M19" t="n">
-        <v>99081.39</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2976.13</v>
+        <v>4287.9</v>
       </c>
       <c r="I20" t="n">
-        <v>2976.13</v>
+        <v>4287.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10139.19</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>10139.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2507.93</v>
+        <v>2976.13</v>
       </c>
       <c r="I21" t="n">
-        <v>2507.93</v>
+        <v>2976.13</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3051.26</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3051.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2451.9</v>
+        <v>2507.93</v>
       </c>
       <c r="I22" t="n">
-        <v>2451.9</v>
+        <v>2507.93</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>15738.58</v>
+        <v>3051.26</v>
       </c>
       <c r="M22" t="n">
-        <v>15738.58</v>
+        <v>3051.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2424.76</v>
+        <v>2451.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2424.76</v>
+        <v>2451.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41273.83</v>
+        <v>15738.58</v>
       </c>
       <c r="M23" t="n">
-        <v>41273.83</v>
+        <v>15738.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2187.26</v>
+        <v>2424.76</v>
       </c>
       <c r="I24" t="n">
-        <v>2187.26</v>
+        <v>2424.76</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,26 +1362,26 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>101901.74</v>
+        <v>41273.83</v>
       </c>
       <c r="M24" t="n">
-        <v>101901.74</v>
+        <v>41273.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1806.57</v>
+        <v>2187.26</v>
       </c>
       <c r="I25" t="n">
-        <v>1806.57</v>
+        <v>2187.26</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16259.14</v>
+        <v>101901.74</v>
       </c>
       <c r="M25" t="n">
-        <v>16259.14</v>
+        <v>101901.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="I26" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
       <c r="M26" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1743.02</v>
+        <v>1752.92</v>
       </c>
       <c r="I27" t="n">
-        <v>1743.02</v>
+        <v>1752.92</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>92342.45</v>
+        <v>11896.87</v>
       </c>
       <c r="M27" t="n">
-        <v>92342.45</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="28">
@@ -1534,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>14986.62</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>14986.62</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="29">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>8 de junio de 2026</t>
+          <t>11 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,22 +490,22 @@
         <v>1368208.15</v>
       </c>
       <c r="H4" t="n">
-        <v>5571.56</v>
+        <v>11417.31</v>
       </c>
       <c r="I4" t="n">
-        <v>1373779.71</v>
+        <v>1379625.46</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>35973.34</v>
       </c>
       <c r="L4" t="n">
-        <v>118391.29</v>
+        <v>140630.52</v>
       </c>
       <c r="M4" t="n">
-        <v>118391.29</v>
+        <v>176603.86</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>22688.39</v>
+        <v>32186.47</v>
       </c>
       <c r="I6" t="n">
-        <v>22688.39</v>
+        <v>32186.47</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>81428.77</v>
+        <v>131517.57</v>
       </c>
       <c r="M6" t="n">
-        <v>81428.77</v>
+        <v>131517.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,28 +619,28 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>14473.52</v>
+        <v>22688.39</v>
       </c>
       <c r="I7" t="n">
-        <v>14473.52</v>
+        <v>22688.39</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2126038.83</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2183932.9</v>
+        <v>81428.77</v>
       </c>
       <c r="M7" t="n">
-        <v>4309971.73</v>
+        <v>81428.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5165.6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8472.299999999999</v>
+        <v>21748.19</v>
       </c>
       <c r="I8" t="n">
-        <v>13637.9</v>
+        <v>21748.19</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10200.24</v>
+        <v>1292.01</v>
       </c>
       <c r="M8" t="n">
-        <v>10200.24</v>
+        <v>1292.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1019.74</v>
       </c>
       <c r="H9" t="n">
-        <v>11128.96</v>
+        <v>13575.59</v>
       </c>
       <c r="I9" t="n">
-        <v>11128.96</v>
+        <v>14595.33</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>235787.82</v>
+        <v>8009.05</v>
       </c>
       <c r="M9" t="n">
-        <v>235787.82</v>
+        <v>8009.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,28 +748,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7576.13</v>
+        <v>14473.52</v>
       </c>
       <c r="I10" t="n">
-        <v>7576.13</v>
+        <v>14473.52</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2126038.83</v>
       </c>
       <c r="L10" t="n">
-        <v>59833.9</v>
+        <v>2183932.9</v>
       </c>
       <c r="M10" t="n">
-        <v>59833.9</v>
+        <v>4309971.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,50 +779,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5165.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7389.36</v>
+        <v>8472.299999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>7389.36</v>
+        <v>13637.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>120675.64</v>
+        <v>10200.24</v>
       </c>
       <c r="M11" t="n">
-        <v>143783.74</v>
+        <v>10200.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6286.27</v>
+        <v>12351.32</v>
       </c>
       <c r="I12" t="n">
-        <v>6286.27</v>
+        <v>12351.32</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,26 +846,26 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>12361.96</v>
+        <v>77390.42</v>
       </c>
       <c r="M12" t="n">
-        <v>12361.96</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5564.58</v>
+        <v>11337.05</v>
       </c>
       <c r="I13" t="n">
-        <v>5564.58</v>
+        <v>11337.05</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>50165.88</v>
+        <v>7311.14</v>
       </c>
       <c r="M13" t="n">
-        <v>50165.88</v>
+        <v>7311.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5438.63</v>
+        <v>11128.96</v>
       </c>
       <c r="I14" t="n">
-        <v>5438.63</v>
+        <v>11128.96</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>97127.28999999999</v>
+        <v>235787.82</v>
       </c>
       <c r="M14" t="n">
-        <v>97127.28999999999</v>
+        <v>235787.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,38 +963,38 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5403.98</v>
+        <v>9661.030000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>5403.98</v>
+        <v>9661.030000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25264.95</v>
       </c>
       <c r="L15" t="n">
-        <v>9644.059999999999</v>
+        <v>142129.36</v>
       </c>
       <c r="M15" t="n">
-        <v>9644.059999999999</v>
+        <v>167394.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5238.69</v>
+        <v>8018.51</v>
       </c>
       <c r="I16" t="n">
-        <v>5238.69</v>
+        <v>8018.51</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>88846.77</v>
+        <v>106912.7</v>
       </c>
       <c r="M16" t="n">
-        <v>88846.77</v>
+        <v>106912.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,28 +1049,28 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4747.43</v>
+        <v>7576.13</v>
       </c>
       <c r="I17" t="n">
-        <v>4747.43</v>
+        <v>7576.13</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3224.48</v>
+        <v>59833.9</v>
       </c>
       <c r="M17" t="n">
-        <v>8208.24</v>
+        <v>59833.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4670.98</v>
+        <v>5564.58</v>
       </c>
       <c r="I18" t="n">
-        <v>4670.98</v>
+        <v>5564.58</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2316.79</v>
+        <v>50165.88</v>
       </c>
       <c r="M18" t="n">
-        <v>2316.79</v>
+        <v>50165.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4480.67</v>
+        <v>5403.98</v>
       </c>
       <c r="I19" t="n">
-        <v>4480.67</v>
+        <v>5403.98</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>30607.01</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>30607.01</v>
+        <v>9644.059999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,28 +1178,28 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4287.9</v>
+        <v>5238.69</v>
       </c>
       <c r="I20" t="n">
-        <v>4287.9</v>
+        <v>5238.69</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2948.64</v>
       </c>
       <c r="L20" t="n">
-        <v>10139.19</v>
+        <v>121281.79</v>
       </c>
       <c r="M20" t="n">
-        <v>10139.19</v>
+        <v>124230.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,28 +1221,28 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2976.13</v>
+        <v>4747.43</v>
       </c>
       <c r="I21" t="n">
-        <v>2976.13</v>
+        <v>4747.43</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>4983.76</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3224.48</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2507.93</v>
+        <v>4670.98</v>
       </c>
       <c r="I22" t="n">
-        <v>2507.93</v>
+        <v>4670.98</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3051.26</v>
+        <v>2316.79</v>
       </c>
       <c r="M22" t="n">
-        <v>3051.26</v>
+        <v>2316.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2451.9</v>
+        <v>4480.67</v>
       </c>
       <c r="I23" t="n">
-        <v>2451.9</v>
+        <v>4480.67</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>15738.58</v>
+        <v>30607.01</v>
       </c>
       <c r="M23" t="n">
-        <v>15738.58</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,38 +1350,38 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2424.76</v>
+        <v>4287.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2424.76</v>
+        <v>4287.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2347.66</v>
       </c>
       <c r="L24" t="n">
-        <v>41273.83</v>
+        <v>10139.19</v>
       </c>
       <c r="M24" t="n">
-        <v>41273.83</v>
+        <v>12486.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2187.26</v>
+        <v>2976.13</v>
       </c>
       <c r="I25" t="n">
-        <v>2187.26</v>
+        <v>2976.13</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>101901.74</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>101901.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1806.57</v>
+        <v>2507.93</v>
       </c>
       <c r="I26" t="n">
-        <v>1806.57</v>
+        <v>2507.93</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,26 +1448,26 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>16259.14</v>
+        <v>3051.26</v>
       </c>
       <c r="M26" t="n">
-        <v>16259.14</v>
+        <v>3051.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1752.92</v>
+        <v>2424.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1752.92</v>
+        <v>2424.76</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>11896.87</v>
+        <v>41273.83</v>
       </c>
       <c r="M27" t="n">
-        <v>11896.87</v>
+        <v>41273.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="I28" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
       <c r="M28" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="I29" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
       <c r="M29" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="I30" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>48.79</v>
+        <v>1635.54</v>
       </c>
       <c r="I31" t="n">
-        <v>48.79</v>
+        <v>1635.54</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,26 +1663,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>16842.35</v>
+        <v>10748.48</v>
       </c>
       <c r="M31" t="n">
-        <v>16842.35</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,38 +1694,38 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>17081.33</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>35934.94</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>53016.27</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,38 +1737,38 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>15585.09</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>71404.87</v>
+        <v>16842.35</v>
       </c>
       <c r="M33" t="n">
-        <v>86989.96000000001</v>
+        <v>16842.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1786,22 +1786,22 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>17081.33</v>
       </c>
       <c r="L34" t="n">
-        <v>4811.58</v>
+        <v>35934.94</v>
       </c>
       <c r="M34" t="n">
-        <v>4811.58</v>
+        <v>53016.27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1829,22 +1829,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L35" t="n">
-        <v>41806.1</v>
+        <v>71404.87</v>
       </c>
       <c r="M35" t="n">
-        <v>41806.1</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1878,26 +1878,26 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2584.02</v>
+        <v>4811.58</v>
       </c>
       <c r="M36" t="n">
-        <v>2584.02</v>
+        <v>4811.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>7419.03</v>
+        <v>41806.1</v>
       </c>
       <c r="M37" t="n">
-        <v>7419.03</v>
+        <v>41806.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>4865.25</v>
+        <v>7419.03</v>
       </c>
       <c r="M38" t="n">
-        <v>4865.25</v>
+        <v>7419.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>43244.52</v>
+        <v>4865.25</v>
       </c>
       <c r="M39" t="n">
-        <v>43244.52</v>
+        <v>4865.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
       <c r="M40" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3911.23</v>
+        <v>9678.940000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>3911.23</v>
+        <v>9678.940000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>4094.59</v>
       </c>
       <c r="L42" t="n">
-        <v>62978.13</v>
+        <v>48951.77</v>
       </c>
       <c r="M42" t="n">
-        <v>62978.13</v>
+        <v>53046.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>167844.24</v>
+        <v>62978.13</v>
       </c>
       <c r="M43" t="n">
-        <v>167844.24</v>
+        <v>62978.13</v>
       </c>
     </row>
     <row r="44">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>11 de junio de 2026</t>
+          <t>16 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -484,28 +484,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1377569.81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13221.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1390791.39</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>1368208.15</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11417.31</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1379625.46</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
       <c r="K4" t="n">
-        <v>35973.34</v>
+        <v>26611.68</v>
       </c>
       <c r="L4" t="n">
-        <v>140630.52</v>
+        <v>138826.25</v>
       </c>
       <c r="M4" t="n">
-        <v>176603.86</v>
+        <v>165437.93</v>
       </c>
     </row>
     <row r="5">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>32186.47</v>
+        <v>45386.23</v>
       </c>
       <c r="I6" t="n">
-        <v>32186.47</v>
+        <v>45386.23</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>131517.57</v>
+        <v>101720.41</v>
       </c>
       <c r="M6" t="n">
-        <v>131517.57</v>
+        <v>101720.41</v>
       </c>
     </row>
     <row r="7">
@@ -613,34 +613,34 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>20152.56</v>
       </c>
       <c r="H7" t="n">
-        <v>22688.39</v>
+        <v>24430.88</v>
       </c>
       <c r="I7" t="n">
-        <v>22688.39</v>
+        <v>44583.44</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>199095.91</v>
       </c>
       <c r="L7" t="n">
-        <v>81428.77</v>
+        <v>79686.28</v>
       </c>
       <c r="M7" t="n">
-        <v>81428.77</v>
+        <v>278782.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,28 +662,28 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>21748.19</v>
+        <v>22723.02</v>
       </c>
       <c r="I8" t="n">
-        <v>21748.19</v>
+        <v>22723.02</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>25264.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1292.01</v>
+        <v>129067.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1292.01</v>
+        <v>154332.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1019.74</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>13575.59</v>
+        <v>21748.19</v>
       </c>
       <c r="I9" t="n">
-        <v>14595.33</v>
+        <v>21748.19</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8009.05</v>
+        <v>1292.01</v>
       </c>
       <c r="M9" t="n">
-        <v>8009.05</v>
+        <v>1292.01</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,40 +779,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5165.6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8472.299999999999</v>
+        <v>13724.04</v>
       </c>
       <c r="I11" t="n">
-        <v>13637.9</v>
+        <v>13724.04</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3977.57</v>
       </c>
       <c r="L11" t="n">
-        <v>10200.24</v>
+        <v>276945.99</v>
       </c>
       <c r="M11" t="n">
-        <v>10200.24</v>
+        <v>280923.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,50 +822,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5165.6</v>
       </c>
       <c r="H12" t="n">
-        <v>12351.32</v>
+        <v>8472.299999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>12351.32</v>
+        <v>13637.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10913.33</v>
       </c>
       <c r="L12" t="n">
-        <v>77390.42</v>
+        <v>10200.24</v>
       </c>
       <c r="M12" t="n">
-        <v>77390.42</v>
+        <v>21113.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>11337.05</v>
+        <v>13575.59</v>
       </c>
       <c r="I13" t="n">
-        <v>11337.05</v>
+        <v>13575.59</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>17895.39</v>
       </c>
       <c r="L13" t="n">
-        <v>7311.14</v>
+        <v>8009.05</v>
       </c>
       <c r="M13" t="n">
-        <v>7311.14</v>
+        <v>25904.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>11128.96</v>
+        <v>12351.32</v>
       </c>
       <c r="I14" t="n">
-        <v>11128.96</v>
+        <v>12351.32</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>235787.82</v>
+        <v>77390.42</v>
       </c>
       <c r="M14" t="n">
-        <v>235787.82</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>9661.030000000001</v>
+        <v>11827.87</v>
       </c>
       <c r="I15" t="n">
-        <v>9661.030000000001</v>
+        <v>11827.87</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>25264.95</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>142129.36</v>
+        <v>43902.59</v>
       </c>
       <c r="M15" t="n">
-        <v>167394.31</v>
+        <v>43902.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8018.51</v>
+        <v>11337.05</v>
       </c>
       <c r="I16" t="n">
-        <v>8018.51</v>
+        <v>11337.05</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>106912.7</v>
+        <v>7311.14</v>
       </c>
       <c r="M16" t="n">
-        <v>106912.7</v>
+        <v>7311.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>7576.13</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>7576.13</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>59833.9</v>
+        <v>105140.07</v>
       </c>
       <c r="M17" t="n">
-        <v>59833.9</v>
+        <v>105140.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,40 +1080,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4094.59</v>
       </c>
       <c r="H18" t="n">
-        <v>5564.58</v>
+        <v>3911.28</v>
       </c>
       <c r="I18" t="n">
-        <v>5564.58</v>
+        <v>8005.87</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1793.93</v>
       </c>
       <c r="L18" t="n">
-        <v>50165.88</v>
+        <v>64773.79</v>
       </c>
       <c r="M18" t="n">
-        <v>50165.88</v>
+        <v>66567.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5403.98</v>
+        <v>7576.13</v>
       </c>
       <c r="I19" t="n">
-        <v>5403.98</v>
+        <v>7576.13</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9644.059999999999</v>
+        <v>59833.9</v>
       </c>
       <c r="M19" t="n">
-        <v>9644.059999999999</v>
+        <v>59833.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,38 +1178,38 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5238.69</v>
+        <v>7418.53</v>
       </c>
       <c r="I20" t="n">
-        <v>5238.69</v>
+        <v>7418.53</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2948.64</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>121281.79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>124230.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,28 +1221,28 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4747.43</v>
+        <v>6399.41</v>
       </c>
       <c r="I21" t="n">
-        <v>4747.43</v>
+        <v>6399.41</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3224.48</v>
+        <v>23171.21</v>
       </c>
       <c r="M21" t="n">
-        <v>8208.24</v>
+        <v>23171.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4670.98</v>
+        <v>5559.19</v>
       </c>
       <c r="I22" t="n">
-        <v>4670.98</v>
+        <v>5559.19</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2316.79</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2316.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,28 +1307,28 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4480.67</v>
+        <v>5403.98</v>
       </c>
       <c r="I23" t="n">
-        <v>4480.67</v>
+        <v>5403.98</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3115.46</v>
       </c>
       <c r="L23" t="n">
-        <v>30607.01</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>30607.01</v>
+        <v>12759.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4287.9</v>
+        <v>5238.69</v>
       </c>
       <c r="I24" t="n">
-        <v>4287.9</v>
+        <v>5238.69</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2347.66</v>
+        <v>2948.64</v>
       </c>
       <c r="L24" t="n">
-        <v>10139.19</v>
+        <v>121281.79</v>
       </c>
       <c r="M24" t="n">
-        <v>12486.85</v>
+        <v>124230.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2976.13</v>
+        <v>4747.43</v>
       </c>
       <c r="I25" t="n">
-        <v>2976.13</v>
+        <v>4747.43</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4983.76</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3224.48</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,38 +1436,38 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2507.93</v>
+        <v>4670.98</v>
       </c>
       <c r="I26" t="n">
-        <v>2507.93</v>
+        <v>4670.98</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>79362.39</v>
       </c>
       <c r="L26" t="n">
-        <v>3051.26</v>
+        <v>2316.79</v>
       </c>
       <c r="M26" t="n">
-        <v>3051.26</v>
+        <v>81679.17999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2424.76</v>
+        <v>4480.67</v>
       </c>
       <c r="I27" t="n">
-        <v>2424.76</v>
+        <v>4480.67</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>41273.83</v>
+        <v>30607.01</v>
       </c>
       <c r="M27" t="n">
-        <v>41273.83</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1806.57</v>
+        <v>4287.9</v>
       </c>
       <c r="I28" t="n">
-        <v>1806.57</v>
+        <v>4287.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2347.66</v>
       </c>
       <c r="L28" t="n">
-        <v>16259.14</v>
+        <v>10139.19</v>
       </c>
       <c r="M28" t="n">
-        <v>16259.14</v>
+        <v>12486.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1752.92</v>
+        <v>2976.13</v>
       </c>
       <c r="I29" t="n">
-        <v>1752.92</v>
+        <v>2976.13</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>11896.87</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>11896.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="I30" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
       <c r="M30" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="I31" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
       <c r="M31" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="I32" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,38 +1737,38 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>48.79</v>
+        <v>1667.89</v>
       </c>
       <c r="I33" t="n">
-        <v>48.79</v>
+        <v>1667.89</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>17081.33</v>
       </c>
       <c r="L33" t="n">
-        <v>16842.35</v>
+        <v>32782.12</v>
       </c>
       <c r="M33" t="n">
-        <v>16842.35</v>
+        <v>49863.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,38 +1780,38 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1635.54</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1635.54</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>17081.33</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>35934.94</v>
+        <v>10748.48</v>
       </c>
       <c r="M34" t="n">
-        <v>53016.27</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,28 +1823,28 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>15585.09</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>71404.87</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>86989.96000000001</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,26 +1878,26 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>4811.58</v>
+        <v>16842.35</v>
       </c>
       <c r="M36" t="n">
-        <v>4811.58</v>
+        <v>16842.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1915,32 +1915,32 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>41806.1</v>
+        <v>24835.65</v>
       </c>
       <c r="M37" t="n">
-        <v>41806.1</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1958,22 +1958,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L38" t="n">
-        <v>7419.03</v>
+        <v>71404.87</v>
       </c>
       <c r="M38" t="n">
-        <v>7419.03</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,26 +2007,26 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4865.25</v>
+        <v>4811.58</v>
       </c>
       <c r="M39" t="n">
-        <v>4865.25</v>
+        <v>4811.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>43244.52</v>
+        <v>41806.1</v>
       </c>
       <c r="M40" t="n">
-        <v>43244.52</v>
+        <v>41806.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>9678.940000000001</v>
+        <v>4865.25</v>
       </c>
       <c r="M41" t="n">
-        <v>9678.940000000001</v>
+        <v>4865.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>4094.59</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>48951.77</v>
+        <v>43244.52</v>
       </c>
       <c r="M42" t="n">
-        <v>53046.36</v>
+        <v>43244.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>62978.13</v>
+        <v>9678.940000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>62978.13</v>
+        <v>9678.940000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,9 +2222,52 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>62978.13</v>
+      </c>
+      <c r="M44" t="n">
+        <v>62978.13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>5557.87</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>5557.87</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>16 de junio de 2026</t>
+          <t>17 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>45386.23</v>
+        <v>51819.85</v>
       </c>
       <c r="I6" t="n">
-        <v>45386.23</v>
+        <v>51819.85</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>101720.41</v>
+        <v>95286.8</v>
       </c>
       <c r="M6" t="n">
-        <v>101720.41</v>
+        <v>95286.8</v>
       </c>
     </row>
     <row r="7">
@@ -625,16 +625,16 @@
         <v>44583.44</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>199095.91</v>
+        <v>262979.08</v>
       </c>
       <c r="L7" t="n">
         <v>79686.28</v>
       </c>
       <c r="M7" t="n">
-        <v>278782.19</v>
+        <v>342665.36</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +656,28 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2156.85</v>
       </c>
       <c r="H8" t="n">
-        <v>22723.02</v>
+        <v>31377.49</v>
       </c>
       <c r="I8" t="n">
-        <v>22723.02</v>
+        <v>33534.34</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>25264.95</v>
+        <v>23108.1</v>
       </c>
       <c r="L8" t="n">
-        <v>129067.31</v>
+        <v>120415.19</v>
       </c>
       <c r="M8" t="n">
-        <v>154332.26</v>
+        <v>143523.29</v>
       </c>
     </row>
     <row r="9">
@@ -711,65 +711,65 @@
         <v>21748.19</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2078.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1292.01</v>
+        <v>24159.87</v>
       </c>
       <c r="M9" t="n">
-        <v>1292.01</v>
+        <v>26238.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1192.09</v>
       </c>
       <c r="H10" t="n">
-        <v>14473.52</v>
+        <v>17557.13</v>
       </c>
       <c r="I10" t="n">
-        <v>14473.52</v>
+        <v>18749.22</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2126038.83</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2183932.9</v>
+        <v>32782.12</v>
       </c>
       <c r="M10" t="n">
-        <v>4309971.73</v>
+        <v>32782.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,28 +791,28 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="I11" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3977.57</v>
+        <v>2317913.6</v>
       </c>
       <c r="L11" t="n">
-        <v>276945.99</v>
+        <v>2183932.9</v>
       </c>
       <c r="M11" t="n">
-        <v>280923.56</v>
+        <v>4501846.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,40 +822,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5165.6</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8472.299999999999</v>
+        <v>13724.04</v>
       </c>
       <c r="I12" t="n">
-        <v>13637.9</v>
+        <v>13724.04</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>10913.33</v>
+        <v>3977.57</v>
       </c>
       <c r="L12" t="n">
-        <v>10200.24</v>
+        <v>276945.99</v>
       </c>
       <c r="M12" t="n">
-        <v>21113.57</v>
+        <v>280923.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,40 +865,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5165.6</v>
       </c>
       <c r="H13" t="n">
-        <v>13575.59</v>
+        <v>8472.299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>13575.59</v>
+        <v>13637.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>17895.39</v>
+        <v>10913.33</v>
       </c>
       <c r="L13" t="n">
-        <v>8009.05</v>
+        <v>10200.24</v>
       </c>
       <c r="M13" t="n">
-        <v>25904.44</v>
+        <v>21113.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,28 +920,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>12351.32</v>
+        <v>13575.59</v>
       </c>
       <c r="I14" t="n">
-        <v>12351.32</v>
+        <v>13575.59</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>17895.39</v>
       </c>
       <c r="L14" t="n">
-        <v>77390.42</v>
+        <v>8009.05</v>
       </c>
       <c r="M14" t="n">
-        <v>77390.42</v>
+        <v>25904.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>11827.87</v>
+        <v>12351.32</v>
       </c>
       <c r="I15" t="n">
-        <v>11827.87</v>
+        <v>12351.32</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,26 +975,26 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>43902.59</v>
+        <v>77390.42</v>
       </c>
       <c r="M15" t="n">
-        <v>43902.59</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11337.05</v>
+        <v>11827.87</v>
       </c>
       <c r="I16" t="n">
-        <v>11337.05</v>
+        <v>11827.87</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7311.14</v>
+        <v>43902.59</v>
       </c>
       <c r="M16" t="n">
-        <v>7311.14</v>
+        <v>43902.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9791.139999999999</v>
+        <v>11337.05</v>
       </c>
       <c r="I17" t="n">
-        <v>9791.139999999999</v>
+        <v>11337.05</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>105140.07</v>
+        <v>7311.14</v>
       </c>
       <c r="M17" t="n">
-        <v>105140.07</v>
+        <v>7311.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,40 +1080,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4094.59</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3911.28</v>
+        <v>10584.87</v>
       </c>
       <c r="I18" t="n">
-        <v>8005.87</v>
+        <v>10584.87</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1793.93</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64773.79</v>
+        <v>56825.12</v>
       </c>
       <c r="M18" t="n">
-        <v>66567.72</v>
+        <v>56825.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5888.52</v>
       </c>
       <c r="H19" t="n">
-        <v>7576.13</v>
+        <v>3911.28</v>
       </c>
       <c r="I19" t="n">
-        <v>7576.13</v>
+        <v>9799.799999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,26 +1147,26 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>59833.9</v>
+        <v>64773.79</v>
       </c>
       <c r="M19" t="n">
-        <v>59833.9</v>
+        <v>64773.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7418.53</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>7418.53</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>105140.07</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>105140.07</v>
       </c>
     </row>
     <row r="21">
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6399.41</v>
+        <v>8543.01</v>
       </c>
       <c r="I21" t="n">
-        <v>6399.41</v>
+        <v>8543.01</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>23171.21</v>
+        <v>21027.61</v>
       </c>
       <c r="M21" t="n">
-        <v>23171.21</v>
+        <v>21027.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1675.67</v>
       </c>
       <c r="H22" t="n">
-        <v>5559.19</v>
+        <v>6844.09</v>
       </c>
       <c r="I22" t="n">
-        <v>5559.19</v>
+        <v>8519.76</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>9644.059999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,28 +1307,28 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5403.98</v>
+        <v>8122.72</v>
       </c>
       <c r="I23" t="n">
-        <v>5403.98</v>
+        <v>8122.72</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>3115.46</v>
+        <v>2948.64</v>
       </c>
       <c r="L23" t="n">
-        <v>9644.059999999999</v>
+        <v>118397.75</v>
       </c>
       <c r="M23" t="n">
-        <v>12759.52</v>
+        <v>121346.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5238.69</v>
+        <v>7418.53</v>
       </c>
       <c r="I24" t="n">
-        <v>5238.69</v>
+        <v>7418.53</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2948.64</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>121281.79</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>124230.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="I25" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3224.48</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8208.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4670.98</v>
+        <v>4747.43</v>
       </c>
       <c r="I26" t="n">
-        <v>4670.98</v>
+        <v>4747.43</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>79362.39</v>
+        <v>4983.76</v>
       </c>
       <c r="L26" t="n">
-        <v>2316.79</v>
+        <v>3224.48</v>
       </c>
       <c r="M26" t="n">
-        <v>81679.17999999999</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4480.67</v>
+        <v>4670.98</v>
       </c>
       <c r="I27" t="n">
-        <v>4480.67</v>
+        <v>4670.98</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>79362.39</v>
       </c>
       <c r="L27" t="n">
-        <v>30607.01</v>
+        <v>2316.79</v>
       </c>
       <c r="M27" t="n">
-        <v>30607.01</v>
+        <v>81679.17999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4287.9</v>
+        <v>4480.67</v>
       </c>
       <c r="I28" t="n">
-        <v>4287.9</v>
+        <v>4480.67</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2347.66</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10139.19</v>
+        <v>30607.01</v>
       </c>
       <c r="M28" t="n">
-        <v>12486.85</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,28 +1565,28 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2976.13</v>
+        <v>4287.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2976.13</v>
+        <v>4287.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2347.66</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>10139.19</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>12486.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1806.57</v>
+        <v>2976.13</v>
       </c>
       <c r="I30" t="n">
-        <v>1806.57</v>
+        <v>2976.13</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>16259.14</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>16259.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="I31" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,26 +1663,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
       <c r="M31" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1699.44</v>
+        <v>1786.77</v>
       </c>
       <c r="I32" t="n">
-        <v>1699.44</v>
+        <v>1786.77</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>8550.700000000001</v>
+        <v>40019.33</v>
       </c>
       <c r="M32" t="n">
-        <v>8550.700000000001</v>
+        <v>40019.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,28 +1737,28 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1667.89</v>
+        <v>1752.92</v>
       </c>
       <c r="I33" t="n">
-        <v>1667.89</v>
+        <v>1752.92</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>17081.33</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>32782.12</v>
+        <v>11896.87</v>
       </c>
       <c r="M33" t="n">
-        <v>49863.45</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1635.54</v>
+        <v>1699.44</v>
       </c>
       <c r="I34" t="n">
-        <v>1635.54</v>
+        <v>1699.44</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10748.48</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>10748.48</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>662.91</v>
+        <v>1635.54</v>
       </c>
       <c r="I35" t="n">
-        <v>662.91</v>
+        <v>1635.54</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>8746.040000000001</v>
+        <v>10748.48</v>
       </c>
       <c r="M35" t="n">
-        <v>8746.040000000001</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>48.79</v>
+        <v>662.91</v>
       </c>
       <c r="I36" t="n">
-        <v>48.79</v>
+        <v>662.91</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>16842.35</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>16842.35</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,38 +1909,38 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>8278.549999999999</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>24835.65</v>
+        <v>16842.35</v>
       </c>
       <c r="M37" t="n">
-        <v>33114.2</v>
+        <v>16842.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1961,29 +1961,29 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>15585.09</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>71404.87</v>
+        <v>24835.65</v>
       </c>
       <c r="M38" t="n">
-        <v>86989.96000000001</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2001,32 +2001,32 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L39" t="n">
-        <v>4811.58</v>
+        <v>71404.87</v>
       </c>
       <c r="M39" t="n">
-        <v>4811.58</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>41806.1</v>
+        <v>4811.58</v>
       </c>
       <c r="M40" t="n">
-        <v>41806.1</v>
+        <v>4811.58</v>
       </c>
     </row>
     <row r="41">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>17 de junio de 2026</t>
+          <t>18 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,22 +521,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6333.21</v>
+        <v>283131.64</v>
       </c>
       <c r="H5" t="n">
-        <v>145097.32</v>
+        <v>24430.88</v>
       </c>
       <c r="I5" t="n">
-        <v>151430.53</v>
+        <v>307562.52</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5478.23</v>
+        <v>79686.28</v>
       </c>
       <c r="M5" t="n">
-        <v>5478.23</v>
+        <v>79686.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6333.21</v>
       </c>
       <c r="H6" t="n">
-        <v>51819.85</v>
+        <v>145097.32</v>
       </c>
       <c r="I6" t="n">
-        <v>51819.85</v>
+        <v>151430.53</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>95286.8</v>
+        <v>5478.23</v>
       </c>
       <c r="M6" t="n">
-        <v>95286.8</v>
+        <v>5478.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,31 +616,31 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>20152.56</v>
+        <v>2156.85</v>
       </c>
       <c r="H7" t="n">
-        <v>24430.88</v>
+        <v>31377.49</v>
       </c>
       <c r="I7" t="n">
-        <v>44583.44</v>
+        <v>33534.34</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>262979.08</v>
+        <v>23108.1</v>
       </c>
       <c r="L7" t="n">
-        <v>79686.28</v>
+        <v>120415.19</v>
       </c>
       <c r="M7" t="n">
-        <v>342665.36</v>
+        <v>143523.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -659,31 +659,31 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2156.85</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>31377.49</v>
+        <v>31470.98</v>
       </c>
       <c r="I8" t="n">
-        <v>33534.34</v>
+        <v>31470.98</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>120415.19</v>
+        <v>8009.05</v>
       </c>
       <c r="M8" t="n">
-        <v>143523.29</v>
+        <v>8009.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>94205</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>JOSE ALBERTO CORONADO ROSAS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,114 +705,114 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>21748.19</v>
+        <v>27662.22</v>
       </c>
       <c r="I9" t="n">
-        <v>21748.19</v>
+        <v>27662.22</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2078.9</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24159.87</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26238.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21748.19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>21748.19</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>1192.09</v>
-      </c>
-      <c r="H10" t="n">
-        <v>17557.13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>18749.22</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2078.9</v>
       </c>
       <c r="L10" t="n">
-        <v>32782.12</v>
+        <v>24159.87</v>
       </c>
       <c r="M10" t="n">
-        <v>32782.12</v>
+        <v>26238.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1192.09</v>
       </c>
       <c r="H11" t="n">
-        <v>14473.52</v>
+        <v>17557.13</v>
       </c>
       <c r="I11" t="n">
-        <v>14473.52</v>
+        <v>18749.22</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2317913.6</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2183932.9</v>
+        <v>32782.12</v>
       </c>
       <c r="M11" t="n">
-        <v>4501846.5</v>
+        <v>32782.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,28 +834,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="I12" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3977.57</v>
+        <v>2317913.6</v>
       </c>
       <c r="L12" t="n">
-        <v>276945.99</v>
+        <v>2183932.9</v>
       </c>
       <c r="M12" t="n">
-        <v>280923.56</v>
+        <v>4501846.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,40 +865,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5165.6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8472.299999999999</v>
+        <v>13724.04</v>
       </c>
       <c r="I13" t="n">
-        <v>13637.9</v>
+        <v>13724.04</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>10913.33</v>
+        <v>3977.57</v>
       </c>
       <c r="L13" t="n">
-        <v>10200.24</v>
+        <v>276945.99</v>
       </c>
       <c r="M13" t="n">
-        <v>21113.57</v>
+        <v>280923.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,40 +908,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5165.6</v>
       </c>
       <c r="H14" t="n">
-        <v>13575.59</v>
+        <v>8472.299999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>13575.59</v>
+        <v>13637.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>17895.39</v>
+        <v>10913.33</v>
       </c>
       <c r="L14" t="n">
-        <v>8009.05</v>
+        <v>10200.24</v>
       </c>
       <c r="M14" t="n">
-        <v>25904.44</v>
+        <v>21113.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="I15" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>77390.42</v>
+        <v>42194.48</v>
       </c>
       <c r="M15" t="n">
-        <v>77390.42</v>
+        <v>42194.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11827.87</v>
+        <v>12351.32</v>
       </c>
       <c r="I16" t="n">
-        <v>11827.87</v>
+        <v>12351.32</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43902.59</v>
+        <v>77390.42</v>
       </c>
       <c r="M16" t="n">
-        <v>43902.59</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="17">
@@ -1586,7 +1586,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2976.13</v>
+        <v>3519.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2976.13</v>
+        <v>3519.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>13960.61</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>13960.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1986.88</v>
       </c>
       <c r="H31" t="n">
-        <v>1806.57</v>
+        <v>5321.25</v>
       </c>
       <c r="I31" t="n">
-        <v>1806.57</v>
+        <v>3334.37</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,26 +1663,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>16259.14</v>
+        <v>95286.8</v>
       </c>
       <c r="M31" t="n">
-        <v>16259.14</v>
+        <v>95286.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1786.77</v>
+        <v>2976.13</v>
       </c>
       <c r="I32" t="n">
-        <v>1786.77</v>
+        <v>2976.13</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>40019.33</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>40019.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="I33" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,26 +1749,26 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
       <c r="M33" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1699.44</v>
+        <v>1786.77</v>
       </c>
       <c r="I34" t="n">
-        <v>1699.44</v>
+        <v>1786.77</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>8550.700000000001</v>
+        <v>40019.33</v>
       </c>
       <c r="M34" t="n">
-        <v>8550.700000000001</v>
+        <v>40019.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="I35" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
       <c r="M35" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="I36" t="n">
-        <v>662.91</v>
+        <v>1699.44</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>8746.040000000001</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>48.79</v>
+        <v>1635.54</v>
       </c>
       <c r="I37" t="n">
-        <v>48.79</v>
+        <v>1635.54</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>16842.35</v>
+        <v>10748.48</v>
       </c>
       <c r="M37" t="n">
-        <v>16842.35</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,38 +1952,38 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>8278.549999999999</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>24835.65</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>33114.2</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2004,29 +2004,29 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>15585.09</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>71404.87</v>
+        <v>24835.65</v>
       </c>
       <c r="M39" t="n">
-        <v>86989.96000000001</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L40" t="n">
-        <v>4811.58</v>
+        <v>71404.87</v>
       </c>
       <c r="M40" t="n">
-        <v>4811.58</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4865.25</v>
+        <v>4811.58</v>
       </c>
       <c r="M41" t="n">
-        <v>4865.25</v>
+        <v>4811.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>43244.52</v>
+        <v>4865.25</v>
       </c>
       <c r="M42" t="n">
-        <v>43244.52</v>
+        <v>4865.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
       <c r="M43" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,26 +2222,26 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>62978.13</v>
+        <v>9678.940000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>62978.13</v>
+        <v>9678.940000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2265,9 +2265,52 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>62978.13</v>
+      </c>
+      <c r="M45" t="n">
+        <v>62978.13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>5557.87</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M46" t="n">
         <v>5557.87</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>18 de junio de 2026</t>
+          <t>19 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -484,28 +484,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>1377569.81</v>
+        <v>1404181.49</v>
       </c>
       <c r="H4" t="n">
         <v>13221.58</v>
       </c>
       <c r="I4" t="n">
-        <v>1390791.39</v>
+        <v>1417403.07</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>26611.68</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>138826.25</v>
       </c>
       <c r="M4" t="n">
-        <v>165437.93</v>
+        <v>138826.25</v>
       </c>
     </row>
     <row r="5">
@@ -742,120 +742,120 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2078.9</v>
       </c>
       <c r="H10" t="n">
         <v>21748.19</v>
       </c>
       <c r="I10" t="n">
-        <v>21748.19</v>
+        <v>23827.09</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2078.9</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>24159.87</v>
       </c>
       <c r="M10" t="n">
-        <v>26238.77</v>
+        <v>24159.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8406.719999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10655.41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19062.13</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>1192.09</v>
-      </c>
-      <c r="H11" t="n">
-        <v>17557.13</v>
-      </c>
-      <c r="I11" t="n">
-        <v>18749.22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5488.87</v>
       </c>
       <c r="L11" t="n">
-        <v>32782.12</v>
+        <v>10200.24</v>
       </c>
       <c r="M11" t="n">
-        <v>32782.12</v>
+        <v>15689.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1192.09</v>
       </c>
       <c r="H12" t="n">
-        <v>14473.52</v>
+        <v>17557.13</v>
       </c>
       <c r="I12" t="n">
-        <v>14473.52</v>
+        <v>18749.22</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2317913.6</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2183932.9</v>
+        <v>32782.12</v>
       </c>
       <c r="M12" t="n">
-        <v>4501846.5</v>
+        <v>32782.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="I13" t="n">
-        <v>13724.04</v>
+        <v>14473.52</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3977.57</v>
+        <v>2317913.6</v>
       </c>
       <c r="L13" t="n">
-        <v>276945.99</v>
+        <v>2183932.9</v>
       </c>
       <c r="M13" t="n">
-        <v>280923.56</v>
+        <v>4501846.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,40 +908,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>5165.6</v>
+        <v>3021.65</v>
       </c>
       <c r="H14" t="n">
-        <v>8472.299999999999</v>
+        <v>11199.79</v>
       </c>
       <c r="I14" t="n">
-        <v>13637.9</v>
+        <v>14221.44</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10913.33</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10200.24</v>
+        <v>116584.96</v>
       </c>
       <c r="M14" t="n">
-        <v>21113.57</v>
+        <v>116584.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>13535.98</v>
+        <v>13724.04</v>
       </c>
       <c r="I15" t="n">
-        <v>13535.98</v>
+        <v>13724.04</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3977.57</v>
       </c>
       <c r="L15" t="n">
-        <v>42194.48</v>
+        <v>276945.99</v>
       </c>
       <c r="M15" t="n">
-        <v>42194.48</v>
+        <v>280923.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="I16" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>77390.42</v>
+        <v>39672.88</v>
       </c>
       <c r="M16" t="n">
-        <v>77390.42</v>
+        <v>39672.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>11337.05</v>
+        <v>12351.32</v>
       </c>
       <c r="I17" t="n">
-        <v>11337.05</v>
+        <v>12351.32</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>7311.14</v>
+        <v>77390.42</v>
       </c>
       <c r="M17" t="n">
-        <v>7311.14</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10584.87</v>
+        <v>11337.05</v>
       </c>
       <c r="I18" t="n">
-        <v>10584.87</v>
+        <v>11337.05</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>56825.12</v>
+        <v>7311.14</v>
       </c>
       <c r="M18" t="n">
-        <v>56825.12</v>
+        <v>7311.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>5888.52</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3911.28</v>
+        <v>10584.87</v>
       </c>
       <c r="I19" t="n">
-        <v>9799.799999999999</v>
+        <v>10584.87</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,41 +1147,41 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>64773.79</v>
+        <v>56825.12</v>
       </c>
       <c r="M19" t="n">
-        <v>64773.79</v>
+        <v>56825.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5888.52</v>
       </c>
       <c r="H20" t="n">
-        <v>9791.139999999999</v>
+        <v>3911.28</v>
       </c>
       <c r="I20" t="n">
-        <v>9791.139999999999</v>
+        <v>9799.799999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>105140.07</v>
+        <v>64773.79</v>
       </c>
       <c r="M20" t="n">
-        <v>105140.07</v>
+        <v>64773.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8543.01</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>8543.01</v>
+        <v>9791.139999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,41 +1233,41 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>21027.61</v>
+        <v>105140.07</v>
       </c>
       <c r="M21" t="n">
-        <v>21027.61</v>
+        <v>105140.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1675.67</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6844.09</v>
+        <v>8543.01</v>
       </c>
       <c r="I22" t="n">
-        <v>8519.76</v>
+        <v>8543.01</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9644.059999999999</v>
+        <v>21027.61</v>
       </c>
       <c r="M22" t="n">
-        <v>9644.059999999999</v>
+        <v>21027.61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,34 +1295,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1675.67</v>
       </c>
       <c r="H23" t="n">
-        <v>8122.72</v>
+        <v>6844.09</v>
       </c>
       <c r="I23" t="n">
-        <v>8122.72</v>
+        <v>8519.76</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>2948.64</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>118397.75</v>
+        <v>9644.059999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>121346.39</v>
+        <v>9644.059999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1371,7 +1371,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1986.88</v>
       </c>
       <c r="H25" t="n">
-        <v>5559.19</v>
+        <v>7906.44</v>
       </c>
       <c r="I25" t="n">
-        <v>5559.19</v>
+        <v>5919.56</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>92701.61</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>92701.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="I26" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3224.48</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>8208.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4670.98</v>
+        <v>4747.43</v>
       </c>
       <c r="I27" t="n">
-        <v>4670.98</v>
+        <v>4747.43</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>79362.39</v>
+        <v>4983.76</v>
       </c>
       <c r="L27" t="n">
-        <v>2316.79</v>
+        <v>3224.48</v>
       </c>
       <c r="M27" t="n">
-        <v>81679.17999999999</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4480.67</v>
+        <v>4670.98</v>
       </c>
       <c r="I28" t="n">
-        <v>4480.67</v>
+        <v>4670.98</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>79362.39</v>
       </c>
       <c r="L28" t="n">
-        <v>30607.01</v>
+        <v>2316.79</v>
       </c>
       <c r="M28" t="n">
-        <v>30607.01</v>
+        <v>81679.17999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,28 +1565,28 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4287.9</v>
+        <v>4480.67</v>
       </c>
       <c r="I29" t="n">
-        <v>4287.9</v>
+        <v>4480.67</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2347.66</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10139.19</v>
+        <v>30607.01</v>
       </c>
       <c r="M29" t="n">
-        <v>12486.85</v>
+        <v>30607.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,28 +1608,28 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3519.8</v>
+        <v>4287.9</v>
       </c>
       <c r="I30" t="n">
-        <v>3519.8</v>
+        <v>4287.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2347.66</v>
       </c>
       <c r="L30" t="n">
-        <v>13960.61</v>
+        <v>10139.19</v>
       </c>
       <c r="M30" t="n">
-        <v>13960.61</v>
+        <v>12486.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-1986.88</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>5321.25</v>
+        <v>3519.8</v>
       </c>
       <c r="I31" t="n">
-        <v>3334.37</v>
+        <v>3519.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>95286.8</v>
+        <v>13960.61</v>
       </c>
       <c r="M31" t="n">
-        <v>95286.8</v>
+        <v>13960.61</v>
       </c>
     </row>
     <row r="32">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>19 de junio de 2026</t>
+          <t>22 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>1404181.49</v>
       </c>
       <c r="H4" t="n">
-        <v>13221.58</v>
+        <v>15284.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1417403.07</v>
+        <v>1419465.53</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>138826.25</v>
+        <v>136763.79</v>
       </c>
       <c r="M4" t="n">
-        <v>138826.25</v>
+        <v>136763.79</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         <v>283131.64</v>
       </c>
       <c r="H5" t="n">
-        <v>24430.88</v>
+        <v>25296.38</v>
       </c>
       <c r="I5" t="n">
-        <v>307562.52</v>
+        <v>308428.02</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1227,16 +1227,16 @@
         <v>9791.139999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1742.84</v>
       </c>
       <c r="L21" t="n">
-        <v>105140.07</v>
+        <v>124311.35</v>
       </c>
       <c r="M21" t="n">
-        <v>105140.07</v>
+        <v>126054.19</v>
       </c>
     </row>
     <row r="22">
@@ -1371,7 +1371,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1390,31 +1390,31 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-1986.88</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>7906.44</v>
+        <v>6987.82</v>
       </c>
       <c r="I25" t="n">
-        <v>5919.56</v>
+        <v>6987.82</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>79362.39</v>
       </c>
       <c r="L25" t="n">
-        <v>92701.61</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>92701.61</v>
+        <v>79362.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5559.19</v>
+        <v>6257.28</v>
       </c>
       <c r="I26" t="n">
-        <v>5559.19</v>
+        <v>6257.28</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>28945.76</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>28945.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1476,31 +1476,31 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1986.88</v>
       </c>
       <c r="H27" t="n">
-        <v>4747.43</v>
+        <v>7906.44</v>
       </c>
       <c r="I27" t="n">
-        <v>4747.43</v>
+        <v>5919.56</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>3224.48</v>
+        <v>92701.61</v>
       </c>
       <c r="M27" t="n">
-        <v>8208.24</v>
+        <v>92701.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4670.98</v>
+        <v>5559.19</v>
       </c>
       <c r="I28" t="n">
-        <v>4670.98</v>
+        <v>5559.19</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>79362.39</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2316.79</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>81679.17999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,22 +1565,22 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4480.67</v>
+        <v>4747.43</v>
       </c>
       <c r="I29" t="n">
-        <v>4480.67</v>
+        <v>4747.43</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>4983.76</v>
       </c>
       <c r="L29" t="n">
-        <v>30607.01</v>
+        <v>3224.48</v>
       </c>
       <c r="M29" t="n">
-        <v>30607.01</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="30">
@@ -1930,7 +1930,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>662.91</v>
+        <v>1603.9</v>
       </c>
       <c r="I38" t="n">
-        <v>662.91</v>
+        <v>1603.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>8746.040000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>8746.040000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,38 +1995,38 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1075.86</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1075.86</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>8278.549999999999</v>
+        <v>1433.08</v>
       </c>
       <c r="L39" t="n">
-        <v>24835.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>33114.2</v>
+        <v>1433.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,28 +2038,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>15585.09</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>71404.87</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>86989.96000000001</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2087,32 +2087,32 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>4811.58</v>
+        <v>24835.65</v>
       </c>
       <c r="M41" t="n">
-        <v>4811.58</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2130,16 +2130,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L42" t="n">
-        <v>4865.25</v>
+        <v>71404.87</v>
       </c>
       <c r="M42" t="n">
-        <v>4865.25</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="43">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>22 de junio de 2026</t>
+          <t>23 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -533,10 +533,10 @@
         <v>283131.64</v>
       </c>
       <c r="H5" t="n">
-        <v>25296.38</v>
+        <v>30126.99</v>
       </c>
       <c r="I5" t="n">
-        <v>308428.02</v>
+        <v>313258.63</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>79686.28</v>
+        <v>77956.22</v>
       </c>
       <c r="M5" t="n">
-        <v>79686.28</v>
+        <v>77956.22</v>
       </c>
     </row>
     <row r="6">
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>31470.98</v>
+        <v>33217.27</v>
       </c>
       <c r="I8" t="n">
-        <v>31470.98</v>
+        <v>33217.27</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8009.05</v>
+        <v>6262.76</v>
       </c>
       <c r="M8" t="n">
-        <v>8009.05</v>
+        <v>6262.76</v>
       </c>
     </row>
     <row r="9">
@@ -748,10 +748,10 @@
         <v>2078.9</v>
       </c>
       <c r="H10" t="n">
-        <v>21748.19</v>
+        <v>25332.43</v>
       </c>
       <c r="I10" t="n">
-        <v>23827.09</v>
+        <v>27411.33</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>8406.719999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>10655.41</v>
+        <v>15836.56</v>
       </c>
       <c r="I11" t="n">
-        <v>19062.13</v>
+        <v>24243.28</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -803,102 +803,102 @@
         <v>5488.87</v>
       </c>
       <c r="L11" t="n">
-        <v>10200.24</v>
+        <v>5681.96</v>
       </c>
       <c r="M11" t="n">
-        <v>15689.11</v>
+        <v>11170.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>21929.23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>21929.23</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>1192.09</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17557.13</v>
-      </c>
-      <c r="I12" t="n">
-        <v>18749.22</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3977.57</v>
       </c>
       <c r="L12" t="n">
-        <v>32782.12</v>
+        <v>268740.8</v>
       </c>
       <c r="M12" t="n">
-        <v>32782.12</v>
+        <v>272718.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1192.09</v>
       </c>
       <c r="H13" t="n">
-        <v>14473.52</v>
+        <v>17557.13</v>
       </c>
       <c r="I13" t="n">
-        <v>14473.52</v>
+        <v>18749.22</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2317913.6</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2183932.9</v>
+        <v>32782.12</v>
       </c>
       <c r="M13" t="n">
-        <v>4501846.5</v>
+        <v>32782.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,40 +908,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3021.65</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>11199.79</v>
+        <v>14473.52</v>
       </c>
       <c r="I14" t="n">
-        <v>14221.44</v>
+        <v>14473.52</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2317913.6</v>
       </c>
       <c r="L14" t="n">
-        <v>116584.96</v>
+        <v>2183932.9</v>
       </c>
       <c r="M14" t="n">
-        <v>116584.96</v>
+        <v>4501846.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,50 +951,50 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3021.65</v>
       </c>
       <c r="H15" t="n">
-        <v>13724.04</v>
+        <v>11199.79</v>
       </c>
       <c r="I15" t="n">
-        <v>13724.04</v>
+        <v>14221.44</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3977.57</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>276945.99</v>
+        <v>116584.96</v>
       </c>
       <c r="M15" t="n">
-        <v>280923.56</v>
+        <v>116584.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>13535.98</v>
+        <v>13639.66</v>
       </c>
       <c r="I16" t="n">
-        <v>13535.98</v>
+        <v>13639.66</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1742.84</v>
       </c>
       <c r="L16" t="n">
-        <v>39672.88</v>
+        <v>120462.83</v>
       </c>
       <c r="M16" t="n">
-        <v>39672.88</v>
+        <v>122205.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="I17" t="n">
-        <v>12351.32</v>
+        <v>13535.98</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>77390.42</v>
+        <v>39672.88</v>
       </c>
       <c r="M17" t="n">
-        <v>77390.42</v>
+        <v>39672.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>11337.05</v>
+        <v>12351.32</v>
       </c>
       <c r="I18" t="n">
-        <v>11337.05</v>
+        <v>12351.32</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,26 +1104,26 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>7311.14</v>
+        <v>77390.42</v>
       </c>
       <c r="M18" t="n">
-        <v>7311.14</v>
+        <v>77390.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>10584.87</v>
+        <v>11337.05</v>
       </c>
       <c r="I19" t="n">
-        <v>10584.87</v>
+        <v>11337.05</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>56825.12</v>
+        <v>7311.14</v>
       </c>
       <c r="M19" t="n">
-        <v>56825.12</v>
+        <v>7311.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5888.52</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3911.28</v>
+        <v>10584.87</v>
       </c>
       <c r="I20" t="n">
-        <v>9799.799999999999</v>
+        <v>10584.87</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,53 +1190,53 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>64773.79</v>
+        <v>56825.12</v>
       </c>
       <c r="M20" t="n">
-        <v>64773.79</v>
+        <v>56825.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5888.52</v>
       </c>
       <c r="H21" t="n">
-        <v>9791.139999999999</v>
+        <v>3911.28</v>
       </c>
       <c r="I21" t="n">
-        <v>9791.139999999999</v>
+        <v>9799.799999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1742.84</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>124311.35</v>
+        <v>64773.79</v>
       </c>
       <c r="M21" t="n">
-        <v>126054.19</v>
+        <v>64773.79</v>
       </c>
     </row>
     <row r="22">
@@ -1457,7 +1457,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-1986.88</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>7906.44</v>
+        <v>6080.42</v>
       </c>
       <c r="I27" t="n">
-        <v>5919.56</v>
+        <v>6080.42</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>92701.61</v>
+        <v>3598.57</v>
       </c>
       <c r="M27" t="n">
-        <v>92701.61</v>
+        <v>3598.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1519,31 +1519,31 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1986.88</v>
       </c>
       <c r="H28" t="n">
-        <v>5559.19</v>
+        <v>7906.44</v>
       </c>
       <c r="I28" t="n">
-        <v>5559.19</v>
+        <v>5919.56</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>66840.31</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>92701.61</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>159541.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,28 +1565,28 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="I29" t="n">
-        <v>4747.43</v>
+        <v>5559.19</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3224.48</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>8208.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,28 +1608,28 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4287.9</v>
+        <v>4747.43</v>
       </c>
       <c r="I30" t="n">
-        <v>4287.9</v>
+        <v>4747.43</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>2347.66</v>
+        <v>4983.76</v>
       </c>
       <c r="L30" t="n">
-        <v>10139.19</v>
+        <v>3224.48</v>
       </c>
       <c r="M30" t="n">
-        <v>12486.85</v>
+        <v>8208.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,38 +1651,38 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3519.8</v>
+        <v>4287.9</v>
       </c>
       <c r="I31" t="n">
-        <v>3519.8</v>
+        <v>4287.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2347.66</v>
       </c>
       <c r="L31" t="n">
-        <v>13960.61</v>
+        <v>10139.19</v>
       </c>
       <c r="M31" t="n">
-        <v>13960.61</v>
+        <v>12486.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2976.13</v>
+        <v>3628.52</v>
       </c>
       <c r="I32" t="n">
-        <v>2976.13</v>
+        <v>3628.52</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>38177.58</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>38177.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1806.57</v>
+        <v>3519.8</v>
       </c>
       <c r="I33" t="n">
-        <v>1806.57</v>
+        <v>3519.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,26 +1749,26 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>16259.14</v>
+        <v>13960.61</v>
       </c>
       <c r="M33" t="n">
-        <v>16259.14</v>
+        <v>13960.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1786.77</v>
+        <v>2976.13</v>
       </c>
       <c r="I34" t="n">
-        <v>1786.77</v>
+        <v>2976.13</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>40019.33</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>40019.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="I35" t="n">
-        <v>1752.92</v>
+        <v>1806.57</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
       <c r="M35" t="n">
-        <v>11896.87</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1699.44</v>
+        <v>1752.92</v>
       </c>
       <c r="I36" t="n">
-        <v>1699.44</v>
+        <v>1752.92</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>8550.700000000001</v>
+        <v>11896.87</v>
       </c>
       <c r="M36" t="n">
-        <v>8550.700000000001</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1635.54</v>
+        <v>1699.44</v>
       </c>
       <c r="I37" t="n">
-        <v>1635.54</v>
+        <v>1699.44</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10748.48</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>10748.48</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1603.9</v>
+        <v>1635.54</v>
       </c>
       <c r="I38" t="n">
-        <v>1603.9</v>
+        <v>1635.54</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>10748.48</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>10748.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,28 +1995,28 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1075.86</v>
+        <v>1603.9</v>
       </c>
       <c r="I39" t="n">
-        <v>1075.86</v>
+        <v>1603.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1433.08</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1433.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,28 +2038,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>662.91</v>
+        <v>1075.86</v>
       </c>
       <c r="I40" t="n">
-        <v>662.91</v>
+        <v>1075.86</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1433.08</v>
       </c>
       <c r="L40" t="n">
-        <v>8746.040000000001</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>8746.040000000001</v>
+        <v>1433.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,38 +2081,38 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>8278.549999999999</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>24835.65</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>33114.2</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2133,29 +2133,29 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>15585.09</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>71404.87</v>
+        <v>24835.65</v>
       </c>
       <c r="M42" t="n">
-        <v>86989.96000000001</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2173,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L43" t="n">
-        <v>43244.52</v>
+        <v>71404.87</v>
       </c>
       <c r="M43" t="n">
-        <v>43244.52</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
       <c r="M44" t="n">
-        <v>9678.940000000001</v>
+        <v>43244.52</v>
       </c>
     </row>
     <row r="45">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>23 de junio de 2026</t>
+          <t>24 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>1404181.49</v>
       </c>
       <c r="H4" t="n">
-        <v>15284.04</v>
+        <v>16824.83</v>
       </c>
       <c r="I4" t="n">
-        <v>1419465.53</v>
+        <v>1421006.32</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -573,31 +573,31 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>6333.21</v>
+        <v>191874.77</v>
       </c>
       <c r="H6" t="n">
-        <v>145097.32</v>
+        <v>14473.52</v>
       </c>
       <c r="I6" t="n">
-        <v>151430.53</v>
+        <v>206348.29</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2126038.83</v>
       </c>
       <c r="L6" t="n">
-        <v>5478.23</v>
+        <v>2183932.9</v>
       </c>
       <c r="M6" t="n">
-        <v>5478.23</v>
+        <v>4309971.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,31 +616,31 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2156.85</v>
+        <v>6333.21</v>
       </c>
       <c r="H7" t="n">
-        <v>31377.49</v>
+        <v>145097.32</v>
       </c>
       <c r="I7" t="n">
-        <v>33534.34</v>
+        <v>151430.53</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>120415.19</v>
+        <v>5478.23</v>
       </c>
       <c r="M7" t="n">
-        <v>143523.29</v>
+        <v>5478.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -659,31 +659,31 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2156.85</v>
       </c>
       <c r="H8" t="n">
-        <v>33217.27</v>
+        <v>31377.49</v>
       </c>
       <c r="I8" t="n">
-        <v>33217.27</v>
+        <v>33534.34</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>23108.1</v>
       </c>
       <c r="L8" t="n">
-        <v>6262.76</v>
+        <v>120415.19</v>
       </c>
       <c r="M8" t="n">
-        <v>6262.76</v>
+        <v>143523.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO CORONADO ROSAS</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>27662.22</v>
+        <v>33217.27</v>
       </c>
       <c r="I9" t="n">
-        <v>27662.22</v>
+        <v>33217.27</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>6262.76</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6262.76</v>
       </c>
     </row>
     <row r="10">
@@ -748,10 +748,10 @@
         <v>2078.9</v>
       </c>
       <c r="H10" t="n">
-        <v>25332.43</v>
+        <v>26624.44</v>
       </c>
       <c r="I10" t="n">
-        <v>27411.33</v>
+        <v>28703.34</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24159.87</v>
+        <v>22867.86</v>
       </c>
       <c r="M10" t="n">
-        <v>24159.87</v>
+        <v>22867.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>94205</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,40 +779,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>JOSE ALBERTO CORONADO ROSAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8406.719999999999</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>15836.56</v>
+        <v>27662.22</v>
       </c>
       <c r="I11" t="n">
-        <v>24243.28</v>
+        <v>27662.22</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5488.87</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5681.96</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>11170.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,71 +834,71 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>21929.23</v>
+        <v>27488.71</v>
       </c>
       <c r="I12" t="n">
-        <v>21929.23</v>
+        <v>27488.71</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3977.57</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>268740.8</v>
+        <v>25720.15</v>
       </c>
       <c r="M12" t="n">
-        <v>272718.37</v>
+        <v>25720.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26683.02</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26683.02</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
-        <v>1192.09</v>
-      </c>
-      <c r="H13" t="n">
-        <v>17557.13</v>
-      </c>
-      <c r="I13" t="n">
-        <v>18749.22</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3977.57</v>
       </c>
       <c r="L13" t="n">
-        <v>32782.12</v>
+        <v>263987.05</v>
       </c>
       <c r="M13" t="n">
-        <v>32782.12</v>
+        <v>267964.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,50 +908,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>8406.719999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>14473.52</v>
+        <v>15836.56</v>
       </c>
       <c r="I14" t="n">
-        <v>14473.52</v>
+        <v>24243.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2317913.6</v>
+        <v>5488.87</v>
       </c>
       <c r="L14" t="n">
-        <v>2183932.9</v>
+        <v>5681.96</v>
       </c>
       <c r="M14" t="n">
-        <v>4501846.5</v>
+        <v>11170.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,13 +960,13 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3021.65</v>
+        <v>1192.09</v>
       </c>
       <c r="H15" t="n">
-        <v>11199.79</v>
+        <v>17557.13</v>
       </c>
       <c r="I15" t="n">
-        <v>14221.44</v>
+        <v>18749.22</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,69 +975,69 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>116584.96</v>
+        <v>32782.12</v>
       </c>
       <c r="M15" t="n">
-        <v>116584.96</v>
+        <v>32782.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3021.65</v>
       </c>
       <c r="H16" t="n">
-        <v>13639.66</v>
+        <v>11199.79</v>
       </c>
       <c r="I16" t="n">
-        <v>13639.66</v>
+        <v>14221.44</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1742.84</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>120462.83</v>
+        <v>116584.96</v>
       </c>
       <c r="M16" t="n">
-        <v>122205.67</v>
+        <v>116584.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>13535.98</v>
+        <v>13639.66</v>
       </c>
       <c r="I17" t="n">
-        <v>13535.98</v>
+        <v>13639.66</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1742.84</v>
       </c>
       <c r="L17" t="n">
-        <v>39672.88</v>
+        <v>120462.83</v>
       </c>
       <c r="M17" t="n">
-        <v>39672.88</v>
+        <v>122205.67</v>
       </c>
     </row>
     <row r="18">
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>66840.31</v>
+        <v>65790.7</v>
       </c>
       <c r="L28" t="n">
         <v>92701.61</v>
       </c>
       <c r="M28" t="n">
-        <v>159541.92</v>
+        <v>158492.31</v>
       </c>
     </row>
     <row r="29">
@@ -1801,7 +1801,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>88.39</v>
       </c>
       <c r="H35" t="n">
-        <v>1806.57</v>
+        <v>2509.34</v>
       </c>
       <c r="I35" t="n">
-        <v>1806.57</v>
+        <v>2597.73</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>16259.14</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>16259.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1752.92</v>
+        <v>2488.66</v>
       </c>
       <c r="I36" t="n">
-        <v>1752.92</v>
+        <v>2488.66</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>11896.87</v>
+        <v>40755.88</v>
       </c>
       <c r="M36" t="n">
-        <v>11896.87</v>
+        <v>40755.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1699.44</v>
+        <v>1806.57</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
       <c r="M37" t="n">
-        <v>8550.700000000001</v>
+        <v>16259.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="I38" t="n">
-        <v>1635.54</v>
+        <v>1752.92</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
       <c r="M38" t="n">
-        <v>10748.48</v>
+        <v>11896.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1603.9</v>
+        <v>1699.44</v>
       </c>
       <c r="I39" t="n">
-        <v>1603.9</v>
+        <v>1699.44</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>8550.700000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>8550.700000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,28 +2038,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1075.86</v>
+        <v>1635.54</v>
       </c>
       <c r="I40" t="n">
-        <v>1075.86</v>
+        <v>1635.54</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1433.08</v>
+        <v>9900.389999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>20648.87</v>
       </c>
       <c r="M40" t="n">
-        <v>1433.08</v>
+        <v>30549.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>662.91</v>
+        <v>1603.9</v>
       </c>
       <c r="I41" t="n">
-        <v>662.91</v>
+        <v>1603.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>8746.040000000001</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>8746.040000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,38 +2124,38 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>662.91</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>8278.549999999999</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>24835.65</v>
+        <v>8746.040000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>33114.2</v>
+        <v>8746.040000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2176,29 +2176,29 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>15585.09</v>
+        <v>8278.549999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>71404.87</v>
+        <v>24835.65</v>
       </c>
       <c r="M43" t="n">
-        <v>86989.96000000001</v>
+        <v>33114.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>15585.09</v>
       </c>
       <c r="L44" t="n">
-        <v>43244.52</v>
+        <v>71404.87</v>
       </c>
       <c r="M44" t="n">
-        <v>43244.52</v>
+        <v>86989.96000000001</v>
       </c>
     </row>
     <row r="45">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>24 de junio de 2026</t>
+          <t>30 de junio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -484,28 +484,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>1404181.49</v>
+        <v>1421726.6</v>
       </c>
       <c r="H4" t="n">
-        <v>16824.83</v>
+        <v>21279.16</v>
       </c>
       <c r="I4" t="n">
-        <v>1421006.32</v>
+        <v>1443005.76</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8629</v>
       </c>
       <c r="L4" t="n">
-        <v>136763.79</v>
+        <v>131899.05</v>
       </c>
       <c r="M4" t="n">
-        <v>136763.79</v>
+        <v>140528.05</v>
       </c>
     </row>
     <row r="5">
@@ -527,28 +527,28 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>308451.52</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34008.43</v>
+      </c>
+      <c r="I5" t="n">
+        <v>342459.95</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>283131.64</v>
-      </c>
-      <c r="H5" t="n">
-        <v>30126.99</v>
-      </c>
-      <c r="I5" t="n">
-        <v>313258.63</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5462.26</v>
       </c>
       <c r="L5" t="n">
-        <v>77956.22</v>
+        <v>138991.73</v>
       </c>
       <c r="M5" t="n">
-        <v>77956.22</v>
+        <v>144453.99</v>
       </c>
     </row>
     <row r="6">
@@ -573,25 +573,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>191874.77</v>
+        <v>191362.05</v>
       </c>
       <c r="H6" t="n">
-        <v>14473.52</v>
+        <v>28869.69</v>
       </c>
       <c r="I6" t="n">
-        <v>206348.29</v>
+        <v>220231.74</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2126038.83</v>
+        <v>2140380.13</v>
       </c>
       <c r="L6" t="n">
-        <v>2183932.9</v>
+        <v>2183684.66</v>
       </c>
       <c r="M6" t="n">
-        <v>4309971.73</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="7">
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>6333.21</v>
+        <v>6316.29</v>
       </c>
       <c r="H7" t="n">
-        <v>145097.32</v>
+        <v>150173.18</v>
       </c>
       <c r="I7" t="n">
-        <v>151430.53</v>
+        <v>156489.47</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5478.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5478.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -659,31 +659,31 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2156.85</v>
+        <v>63633.32</v>
       </c>
       <c r="H8" t="n">
-        <v>31377.49</v>
+        <v>57507.18</v>
       </c>
       <c r="I8" t="n">
-        <v>33534.34</v>
+        <v>121140.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>23108.1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>120415.19</v>
+        <v>92453.89999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>143523.29</v>
+        <v>92453.89999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>96052.28</v>
       </c>
       <c r="H9" t="n">
-        <v>33217.27</v>
+        <v>13444.1</v>
       </c>
       <c r="I9" t="n">
-        <v>33217.27</v>
+        <v>109496.38</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6262.76</v>
+        <v>52737.61</v>
       </c>
       <c r="M9" t="n">
-        <v>6262.76</v>
+        <v>52737.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,22 +736,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2078.9</v>
+        <v>52787.07</v>
       </c>
       <c r="H10" t="n">
-        <v>26624.44</v>
+        <v>18449.48</v>
       </c>
       <c r="I10" t="n">
-        <v>28703.34</v>
+        <v>71236.55</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>22867.86</v>
+        <v>48780.37</v>
       </c>
       <c r="M10" t="n">
-        <v>22867.86</v>
+        <v>48780.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,40 +779,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO CORONADO ROSAS</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3925.24</v>
       </c>
       <c r="H11" t="n">
-        <v>27662.22</v>
+        <v>51296.31</v>
       </c>
       <c r="I11" t="n">
-        <v>27662.22</v>
+        <v>55221.55</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>120151.02</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>143197.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,22 +822,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>11380.54</v>
       </c>
       <c r="H12" t="n">
-        <v>27488.71</v>
+        <v>39223.64</v>
       </c>
       <c r="I12" t="n">
-        <v>27488.71</v>
+        <v>50604.18</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>25720.15</v>
+        <v>333287.1</v>
       </c>
       <c r="M12" t="n">
-        <v>25720.15</v>
+        <v>333287.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,40 +865,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>11737.38</v>
       </c>
       <c r="H13" t="n">
-        <v>26683.02</v>
+        <v>26357.78</v>
       </c>
       <c r="I13" t="n">
-        <v>26683.02</v>
+        <v>38095.16</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3977.57</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>263987.05</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>267964.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,50 +908,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>8406.719999999999</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>15836.56</v>
+        <v>33128.49</v>
       </c>
       <c r="I14" t="n">
-        <v>24243.28</v>
+        <v>33128.49</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5488.87</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5681.96</v>
+        <v>6246.02</v>
       </c>
       <c r="M14" t="n">
-        <v>11170.83</v>
+        <v>6246.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,13 +960,13 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1192.09</v>
+        <v>2073.34</v>
       </c>
       <c r="H15" t="n">
-        <v>17557.13</v>
+        <v>26583.82</v>
       </c>
       <c r="I15" t="n">
-        <v>18749.22</v>
+        <v>28657.16</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>32782.12</v>
+        <v>22806.75</v>
       </c>
       <c r="M15" t="n">
-        <v>32782.12</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>94205</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>JOSE ALBERTO CORONADO ROSAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3021.65</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11199.79</v>
+        <v>27588.3</v>
       </c>
       <c r="I16" t="n">
-        <v>14221.44</v>
+        <v>27588.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>116584.96</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>116584.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,53 +1049,53 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>13639.66</v>
+        <v>27415.26</v>
       </c>
       <c r="I17" t="n">
-        <v>13639.66</v>
+        <v>27415.26</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1742.84</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120462.83</v>
+        <v>25651.43</v>
       </c>
       <c r="M17" t="n">
-        <v>122205.67</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1188.91</v>
       </c>
       <c r="H18" t="n">
-        <v>12351.32</v>
+        <v>17510.21</v>
       </c>
       <c r="I18" t="n">
-        <v>12351.32</v>
+        <v>18699.12</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>77390.42</v>
+        <v>32694.52</v>
       </c>
       <c r="M18" t="n">
-        <v>77390.42</v>
+        <v>32694.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3215.45</v>
       </c>
       <c r="H19" t="n">
-        <v>11337.05</v>
+        <v>15344.85</v>
       </c>
       <c r="I19" t="n">
-        <v>11337.05</v>
+        <v>18560.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7311.14</v>
+        <v>134649.12</v>
       </c>
       <c r="M19" t="n">
-        <v>7311.14</v>
+        <v>134649.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>10584.87</v>
+        <v>18267.36</v>
       </c>
       <c r="I20" t="n">
-        <v>10584.87</v>
+        <v>18267.36</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>56825.12</v>
+        <v>71234.57000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>56825.12</v>
+        <v>71234.57000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,22 +1209,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>5888.52</v>
+        <v>16380.01</v>
       </c>
       <c r="H21" t="n">
-        <v>3911.28</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>9799.799999999999</v>
+        <v>16380.01</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,41 +1233,41 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>64773.79</v>
+        <v>49140.03</v>
       </c>
       <c r="M21" t="n">
-        <v>64773.79</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3013.57</v>
       </c>
       <c r="H22" t="n">
-        <v>8543.01</v>
+        <v>13228.03</v>
       </c>
       <c r="I22" t="n">
-        <v>8543.01</v>
+        <v>16241.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>21027.61</v>
+        <v>114215.26</v>
       </c>
       <c r="M22" t="n">
-        <v>21027.61</v>
+        <v>114215.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1675.67</v>
+        <v>11392.35</v>
       </c>
       <c r="H23" t="n">
-        <v>6844.09</v>
+        <v>4454.77</v>
       </c>
       <c r="I23" t="n">
-        <v>8519.76</v>
+        <v>15847.12</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>9644.059999999999</v>
+        <v>18651.6</v>
       </c>
       <c r="M23" t="n">
-        <v>9644.059999999999</v>
+        <v>18651.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>7418.53</v>
+        <v>13129.66</v>
       </c>
       <c r="I24" t="n">
-        <v>7418.53</v>
+        <v>13129.66</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5468.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5468.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6987.82</v>
+        <v>10386.49</v>
       </c>
       <c r="I25" t="n">
-        <v>6987.82</v>
+        <v>10386.49</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>79362.39</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>29761.26</v>
       </c>
       <c r="M25" t="n">
-        <v>79362.39</v>
+        <v>29761.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5872.79</v>
       </c>
       <c r="H26" t="n">
-        <v>6257.28</v>
+        <v>3900.83</v>
       </c>
       <c r="I26" t="n">
-        <v>6257.28</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>28945.76</v>
+        <v>64600.71</v>
       </c>
       <c r="M26" t="n">
-        <v>28945.76</v>
+        <v>64600.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,38 +1479,38 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6080.42</v>
+        <v>8832.15</v>
       </c>
       <c r="I27" t="n">
-        <v>6080.42</v>
+        <v>8832.15</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>4970.44</v>
       </c>
       <c r="L27" t="n">
-        <v>3598.57</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3598.57</v>
+        <v>4970.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1519,31 +1519,31 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-1986.88</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7906.44</v>
+        <v>8520.18</v>
       </c>
       <c r="I28" t="n">
-        <v>5919.56</v>
+        <v>8520.18</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>65790.7</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>92701.61</v>
+        <v>20971.42</v>
       </c>
       <c r="M28" t="n">
-        <v>158492.31</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,22 +1553,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1671.19</v>
       </c>
       <c r="H29" t="n">
-        <v>5559.19</v>
+        <v>6825.8</v>
       </c>
       <c r="I29" t="n">
-        <v>5559.19</v>
+        <v>8496.99</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>9618.290000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>9618.290000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,28 +1608,28 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4747.43</v>
+        <v>7398.71</v>
       </c>
       <c r="I30" t="n">
-        <v>4747.43</v>
+        <v>7398.71</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3224.48</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>8208.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,38 +1651,38 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4287.9</v>
+        <v>6969.14</v>
       </c>
       <c r="I31" t="n">
-        <v>4287.9</v>
+        <v>6969.14</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>2347.66</v>
+        <v>79150.32000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>10139.19</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>12486.85</v>
+        <v>79150.32000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3628.52</v>
+        <v>6240.56</v>
       </c>
       <c r="I32" t="n">
-        <v>3628.52</v>
+        <v>6240.56</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>38177.58</v>
+        <v>28868.4</v>
       </c>
       <c r="M32" t="n">
-        <v>38177.58</v>
+        <v>28868.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3519.8</v>
+        <v>6064.17</v>
       </c>
       <c r="I33" t="n">
-        <v>3519.8</v>
+        <v>6064.17</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>13960.61</v>
+        <v>3588.95</v>
       </c>
       <c r="M33" t="n">
-        <v>13960.61</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2976.13</v>
+        <v>5544.33</v>
       </c>
       <c r="I34" t="n">
-        <v>2976.13</v>
+        <v>5544.33</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1801,32 +1801,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>88.39</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2509.34</v>
+        <v>5322.02</v>
       </c>
       <c r="I35" t="n">
-        <v>2597.73</v>
+        <v>5322.02</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>36742.58</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>36742.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,28 +1866,28 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2488.66</v>
+        <v>4276.44</v>
       </c>
       <c r="I36" t="n">
-        <v>2488.66</v>
+        <v>4276.44</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>2341.38</v>
       </c>
       <c r="L36" t="n">
-        <v>40755.88</v>
+        <v>10112.1</v>
       </c>
       <c r="M36" t="n">
-        <v>40755.88</v>
+        <v>12453.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1806.57</v>
+        <v>3510.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1806.57</v>
+        <v>3510.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>16259.14</v>
+        <v>13923.3</v>
       </c>
       <c r="M37" t="n">
-        <v>16259.14</v>
+        <v>13923.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1752.92</v>
+        <v>3389.81</v>
       </c>
       <c r="I38" t="n">
-        <v>1752.92</v>
+        <v>3389.81</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>11896.87</v>
+        <v>6832.95</v>
       </c>
       <c r="M38" t="n">
-        <v>11896.87</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1699.44</v>
+        <v>2968.17</v>
       </c>
       <c r="I39" t="n">
-        <v>1699.44</v>
+        <v>2968.17</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>8550.700000000001</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>8550.700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,28 +2038,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1635.54</v>
+        <v>2789.54</v>
       </c>
       <c r="I40" t="n">
-        <v>1635.54</v>
+        <v>2789.54</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>9900.389999999999</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>20648.87</v>
+        <v>10823.78</v>
       </c>
       <c r="M40" t="n">
-        <v>30549.26</v>
+        <v>10823.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,22 +2069,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>1603.9</v>
+        <v>2502.64</v>
       </c>
       <c r="I41" t="n">
-        <v>1603.9</v>
+        <v>2590.79</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2102,17 +2102,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,38 +2124,38 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>662.91</v>
+        <v>2027.5</v>
       </c>
       <c r="I42" t="n">
-        <v>662.91</v>
+        <v>2027.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>15543.45</v>
       </c>
       <c r="L42" t="n">
-        <v>8746.040000000001</v>
+        <v>69186.56</v>
       </c>
       <c r="M42" t="n">
-        <v>8746.040000000001</v>
+        <v>84730.00999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2167,38 +2167,38 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1847.67</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1847.67</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>8278.549999999999</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>24835.65</v>
+        <v>3695.34</v>
       </c>
       <c r="M43" t="n">
-        <v>33114.2</v>
+        <v>3695.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2210,28 +2210,28 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1801.74</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1801.74</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>15585.09</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>71404.87</v>
+        <v>16215.69</v>
       </c>
       <c r="M44" t="n">
-        <v>86989.96000000001</v>
+        <v>16215.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2265,26 +2265,26 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>62978.13</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>62978.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>661.14</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>661.14</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2308,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>5557.87</v>
+        <v>8722.67</v>
       </c>
       <c r="M46" t="n">
-        <v>5557.87</v>
+        <v>8722.67</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>30 de junio de 2026</t>
+          <t>7 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,44 +468,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1421726.6</v>
+        <v>4665.02</v>
       </c>
       <c r="H4" t="n">
-        <v>21279.16</v>
+        <v>79155.34</v>
       </c>
       <c r="I4" t="n">
-        <v>1443005.76</v>
+        <v>83820.36</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8629</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>131899.05</v>
+        <v>2310.6</v>
       </c>
       <c r="M4" t="n">
-        <v>140528.05</v>
+        <v>2310.6</v>
       </c>
     </row>
     <row r="5">
@@ -527,34 +527,34 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>308451.52</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>34008.43</v>
+        <v>19707.14</v>
       </c>
       <c r="I5" t="n">
-        <v>342459.95</v>
+        <v>19707.14</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>5462.26</v>
+        <v>3925.94</v>
       </c>
       <c r="L5" t="n">
-        <v>138991.73</v>
+        <v>113630.58</v>
       </c>
       <c r="M5" t="n">
-        <v>144453.99</v>
+        <v>117556.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,40 +564,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>191362.05</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>28869.69</v>
+        <v>12104.18</v>
       </c>
       <c r="I6" t="n">
-        <v>220231.74</v>
+        <v>12104.18</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2183684.66</v>
+        <v>6978.13</v>
       </c>
       <c r="M6" t="n">
-        <v>4324064.79</v>
+        <v>6978.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6316.29</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>150173.18</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>156489.47</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7694.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>63633.32</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>57507.18</v>
+        <v>7555.89</v>
       </c>
       <c r="I8" t="n">
-        <v>121140.5</v>
+        <v>7555.89</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,41 +674,41 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>92453.89999999999</v>
+        <v>54253.97</v>
       </c>
       <c r="M8" t="n">
-        <v>92453.89999999999</v>
+        <v>54253.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>96052.28</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>13444.1</v>
+        <v>5018.34</v>
       </c>
       <c r="I9" t="n">
-        <v>109496.38</v>
+        <v>5018.34</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>52737.61</v>
+        <v>5468.7</v>
       </c>
       <c r="M9" t="n">
-        <v>52737.61</v>
+        <v>5468.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,22 +736,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>52787.07</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>18449.48</v>
+        <v>4468.7</v>
       </c>
       <c r="I10" t="n">
-        <v>71236.55</v>
+        <v>4468.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48780.37</v>
+        <v>22506.75</v>
       </c>
       <c r="M10" t="n">
-        <v>48780.37</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,65 +779,65 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3925.24</v>
+        <v>-3232.45</v>
       </c>
       <c r="H11" t="n">
-        <v>51296.31</v>
+        <v>7580.21</v>
       </c>
       <c r="I11" t="n">
-        <v>55221.55</v>
+        <v>4347.76</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23046.35</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>120151.02</v>
+        <v>29481.97</v>
       </c>
       <c r="M11" t="n">
-        <v>143197.37</v>
+        <v>29481.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>11380.54</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>39223.64</v>
+        <v>3199.93</v>
       </c>
       <c r="I12" t="n">
-        <v>50604.18</v>
+        <v>3199.93</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>333287.1</v>
+        <v>34877.64</v>
       </c>
       <c r="M12" t="n">
-        <v>333287.1</v>
+        <v>34877.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>11737.38</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26357.78</v>
+        <v>2968.17</v>
       </c>
       <c r="I13" t="n">
-        <v>38095.16</v>
+        <v>2968.17</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -914,59 +914,59 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2445.34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2445.34</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>33128.49</v>
-      </c>
-      <c r="I14" t="n">
-        <v>33128.49</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>73595.67</v>
       </c>
       <c r="L14" t="n">
-        <v>6246.02</v>
+        <v>15980.3</v>
       </c>
       <c r="M14" t="n">
-        <v>6246.02</v>
+        <v>89575.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2073.34</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26583.82</v>
+        <v>2418.28</v>
       </c>
       <c r="I15" t="n">
-        <v>28657.16</v>
+        <v>2418.28</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>22806.75</v>
+        <v>20971.42</v>
       </c>
       <c r="M15" t="n">
-        <v>22806.75</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO CORONADO ROSAS</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>27588.3</v>
+        <v>2391.83</v>
       </c>
       <c r="I16" t="n">
-        <v>27588.3</v>
+        <v>2391.83</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>18651.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>18651.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>27415.26</v>
+        <v>2340.27</v>
       </c>
       <c r="I17" t="n">
-        <v>27415.26</v>
+        <v>2340.27</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>25651.43</v>
+        <v>3215.87</v>
       </c>
       <c r="M17" t="n">
-        <v>25651.43</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1188.91</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>17510.21</v>
+        <v>2181.42</v>
       </c>
       <c r="I18" t="n">
-        <v>18699.12</v>
+        <v>2181.42</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>32694.52</v>
+        <v>136368.48</v>
       </c>
       <c r="M18" t="n">
-        <v>32694.52</v>
+        <v>136368.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,40 +1123,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3215.45</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>15344.85</v>
+        <v>2061.35</v>
       </c>
       <c r="I19" t="n">
-        <v>18560.3</v>
+        <v>2061.35</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>15543.45</v>
       </c>
       <c r="L19" t="n">
-        <v>134649.12</v>
+        <v>77925.53999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>134649.12</v>
+        <v>93468.99000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>18267.36</v>
+        <v>1784.16</v>
       </c>
       <c r="I20" t="n">
-        <v>18267.36</v>
+        <v>1784.16</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>71234.57000000001</v>
+        <v>348268.17</v>
       </c>
       <c r="M20" t="n">
-        <v>71234.57000000001</v>
+        <v>348268.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,22 +1209,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>16380.01</v>
+        <v>1774.15</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>16380.01</v>
+        <v>1774.15</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>49140.03</v>
+        <v>36313.01</v>
       </c>
       <c r="M21" t="n">
-        <v>49140.03</v>
+        <v>36313.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,40 +1252,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1761.99</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1761.99</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>3013.57</v>
-      </c>
-      <c r="H22" t="n">
-        <v>13228.03</v>
-      </c>
-      <c r="I22" t="n">
-        <v>16241.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L22" t="n">
-        <v>114215.26</v>
+        <v>123791.17</v>
       </c>
       <c r="M22" t="n">
-        <v>114215.26</v>
+        <v>146837.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>11392.35</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4454.77</v>
+        <v>1761.99</v>
       </c>
       <c r="I23" t="n">
-        <v>15847.12</v>
+        <v>1761.99</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>18651.6</v>
+        <v>13206.35</v>
       </c>
       <c r="M23" t="n">
-        <v>18651.6</v>
+        <v>13206.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>13129.66</v>
+        <v>1748.24</v>
       </c>
       <c r="I24" t="n">
-        <v>13129.66</v>
+        <v>1748.24</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>5468.7</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>5468.7</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>10386.49</v>
+        <v>1738.36</v>
       </c>
       <c r="I25" t="n">
-        <v>10386.49</v>
+        <v>1738.36</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>29761.26</v>
+        <v>117962.13</v>
       </c>
       <c r="M25" t="n">
-        <v>29761.26</v>
+        <v>117962.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5872.79</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3900.83</v>
+        <v>1737.22</v>
       </c>
       <c r="I26" t="n">
-        <v>9773.620000000001</v>
+        <v>1737.22</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>64600.71</v>
+        <v>54969.92</v>
       </c>
       <c r="M26" t="n">
-        <v>64600.71</v>
+        <v>54969.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>8832.15</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>8832.15</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4970.44</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>49140.03</v>
       </c>
       <c r="M27" t="n">
-        <v>4970.44</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8520.18</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>8520.18</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>20971.42</v>
+        <v>32694.52</v>
       </c>
       <c r="M28" t="n">
-        <v>20971.42</v>
+        <v>32694.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,22 +1553,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1671.19</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>6825.8</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>8496.99</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>9618.290000000001</v>
+        <v>6832.95</v>
       </c>
       <c r="M29" t="n">
-        <v>9618.290000000001</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>7398.71</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7398.71</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>25651.43</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,28 +1651,28 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>6969.14</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>6969.14</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>79150.32000000001</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>22806.75</v>
       </c>
       <c r="M31" t="n">
-        <v>79150.32000000001</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6240.56</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>6240.56</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>28868.4</v>
+        <v>16215.69</v>
       </c>
       <c r="M32" t="n">
-        <v>28868.4</v>
+        <v>16215.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,38 +1737,38 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>6064.17</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6064.17</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L33" t="n">
-        <v>3588.95</v>
+        <v>2183684.66</v>
       </c>
       <c r="M33" t="n">
-        <v>3588.95</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5544.33</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>5544.33</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,26 +1792,26 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>134156.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>134156.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>5322.02</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>5322.02</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>36742.58</v>
+        <v>6281.5</v>
       </c>
       <c r="M35" t="n">
-        <v>36742.58</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,28 +1866,28 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>4276.44</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4276.44</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2341.38</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>10112.1</v>
+        <v>3043.1</v>
       </c>
       <c r="M36" t="n">
-        <v>12453.48</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3510.4</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3510.4</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>13923.3</v>
+        <v>35224.49</v>
       </c>
       <c r="M37" t="n">
-        <v>13923.3</v>
+        <v>35224.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3389.81</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3389.81</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>6832.95</v>
+        <v>9653.08</v>
       </c>
       <c r="M38" t="n">
-        <v>6832.95</v>
+        <v>9653.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2968.17</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2968.17</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>68501.49000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>68501.49000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2789.54</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2789.54</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10823.78</v>
+        <v>59518.06</v>
       </c>
       <c r="M40" t="n">
-        <v>10823.78</v>
+        <v>59518.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,22 +2069,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>88.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2502.64</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2590.79</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,26 +2093,26 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>92453.89999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>92453.89999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,194 +2124,22 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2027.5</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2027.5</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>15543.45</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>69186.56</v>
+        <v>3695.34</v>
       </c>
       <c r="M42" t="n">
-        <v>84730.00999999999</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>63441</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1847.67</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1847.67</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
         <v>3695.34</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3695.34</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>112083</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1801.74</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1801.74</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>16215.69</v>
-      </c>
-      <c r="M44" t="n">
-        <v>16215.69</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>116795</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1599.61</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1599.61</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>115404</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>661.14</v>
-      </c>
-      <c r="I46" t="n">
-        <v>661.14</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>8722.67</v>
-      </c>
-      <c r="M46" t="n">
-        <v>8722.67</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>7 de julio de 2026</t>
+          <t>9 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,40 +521,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4377.64</v>
       </c>
       <c r="H5" t="n">
-        <v>19707.14</v>
+        <v>71663.37</v>
       </c>
       <c r="I5" t="n">
-        <v>19707.14</v>
+        <v>76041.00999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3925.94</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>113630.58</v>
+        <v>15980.3</v>
       </c>
       <c r="M5" t="n">
-        <v>117556.52</v>
+        <v>15980.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -576,28 +576,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12104.18</v>
+        <v>20232.35</v>
       </c>
       <c r="I6" t="n">
-        <v>12104.18</v>
+        <v>20232.35</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3925.94</v>
       </c>
       <c r="L6" t="n">
-        <v>6978.13</v>
+        <v>111014</v>
       </c>
       <c r="M6" t="n">
-        <v>6978.13</v>
+        <v>114939.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8496.639999999999</v>
+        <v>12104.18</v>
       </c>
       <c r="I7" t="n">
-        <v>8496.639999999999</v>
+        <v>12104.18</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,26 +631,26 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7694.63</v>
+        <v>6978.13</v>
       </c>
       <c r="M7" t="n">
-        <v>7694.63</v>
+        <v>6978.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7555.89</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>7555.89</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>54253.97</v>
+        <v>5468.7</v>
       </c>
       <c r="M8" t="n">
-        <v>54253.97</v>
+        <v>5468.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5018.34</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>5018.34</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5468.7</v>
+        <v>7694.63</v>
       </c>
       <c r="M9" t="n">
-        <v>5468.7</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4468.7</v>
+        <v>7555.89</v>
       </c>
       <c r="I10" t="n">
-        <v>4468.7</v>
+        <v>7555.89</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,26 +760,26 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>22506.75</v>
+        <v>54253.97</v>
       </c>
       <c r="M10" t="n">
-        <v>22506.75</v>
+        <v>54253.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7580.21</v>
+        <v>6236.42</v>
       </c>
       <c r="I11" t="n">
-        <v>4347.76</v>
+        <v>6236.42</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>29481.97</v>
+        <v>132467.7</v>
       </c>
       <c r="M11" t="n">
-        <v>29481.97</v>
+        <v>132467.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3199.93</v>
+        <v>5224.69</v>
       </c>
       <c r="I12" t="n">
-        <v>3199.93</v>
+        <v>5224.69</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>34877.64</v>
+        <v>114475.8</v>
       </c>
       <c r="M12" t="n">
-        <v>34877.64</v>
+        <v>114475.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2968.17</v>
+        <v>4785.92</v>
       </c>
       <c r="I13" t="n">
-        <v>2968.17</v>
+        <v>4785.92</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>345577.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>345577.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,38 +920,38 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2445.34</v>
+        <v>4468.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2445.34</v>
+        <v>4468.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>73595.67</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>15980.3</v>
+        <v>22506.75</v>
       </c>
       <c r="M14" t="n">
-        <v>89575.97</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-3232.45</v>
       </c>
       <c r="H15" t="n">
-        <v>2418.28</v>
+        <v>7580.21</v>
       </c>
       <c r="I15" t="n">
-        <v>2418.28</v>
+        <v>4347.76</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>20971.42</v>
+        <v>23815.2</v>
       </c>
       <c r="M15" t="n">
-        <v>20971.42</v>
+        <v>23815.2</v>
       </c>
     </row>
     <row r="16">
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2391.83</v>
+        <v>4023</v>
       </c>
       <c r="I16" t="n">
-        <v>2391.83</v>
+        <v>4023</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>18651.6</v>
+        <v>17020.43</v>
       </c>
       <c r="M16" t="n">
-        <v>18651.6</v>
+        <v>17020.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2340.27</v>
+        <v>3199.93</v>
       </c>
       <c r="I17" t="n">
-        <v>2340.27</v>
+        <v>3199.93</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3215.87</v>
+        <v>34877.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3215.87</v>
+        <v>34877.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2181.42</v>
+        <v>2968.17</v>
       </c>
       <c r="I18" t="n">
-        <v>2181.42</v>
+        <v>2968.17</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>136368.48</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>136368.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,28 +1135,28 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2061.35</v>
+        <v>2418.28</v>
       </c>
       <c r="I19" t="n">
-        <v>2061.35</v>
+        <v>2418.28</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>15543.45</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>77925.53999999999</v>
+        <v>20971.42</v>
       </c>
       <c r="M19" t="n">
-        <v>93468.99000000001</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1784.16</v>
+        <v>2340.27</v>
       </c>
       <c r="I20" t="n">
-        <v>1784.16</v>
+        <v>2340.27</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,69 +1190,69 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>348268.17</v>
+        <v>3215.87</v>
       </c>
       <c r="M20" t="n">
-        <v>348268.17</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2061.35</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2061.35</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>1774.15</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1774.15</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>15543.45</v>
       </c>
       <c r="L21" t="n">
-        <v>36313.01</v>
+        <v>77925.53999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>36313.01</v>
+        <v>93468.99000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,28 +1264,28 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1761.99</v>
+        <v>1853.84</v>
       </c>
       <c r="I22" t="n">
-        <v>1761.99</v>
+        <v>1853.84</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>23046.35</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>123791.17</v>
+        <v>132302.17</v>
       </c>
       <c r="M22" t="n">
-        <v>146837.52</v>
+        <v>132302.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H23" t="n">
-        <v>1761.99</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1761.99</v>
+        <v>1774.15</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>13206.35</v>
+        <v>36313.01</v>
       </c>
       <c r="M23" t="n">
-        <v>13206.35</v>
+        <v>36313.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1748.24</v>
+        <v>1761.99</v>
       </c>
       <c r="I24" t="n">
-        <v>1748.24</v>
+        <v>1761.99</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L24" t="n">
-        <v>9075.540000000001</v>
+        <v>123791.17</v>
       </c>
       <c r="M24" t="n">
-        <v>9075.540000000001</v>
+        <v>146837.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1738.36</v>
+        <v>1761.99</v>
       </c>
       <c r="I25" t="n">
-        <v>1738.36</v>
+        <v>1761.99</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>117962.13</v>
+        <v>13206.35</v>
       </c>
       <c r="M25" t="n">
-        <v>117962.13</v>
+        <v>13206.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1737.22</v>
+        <v>1748.24</v>
       </c>
       <c r="I26" t="n">
-        <v>1737.22</v>
+        <v>1748.24</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>54969.92</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>54969.92</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1737.22</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1737.22</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,26 +1491,26 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>49140.03</v>
+        <v>54969.92</v>
       </c>
       <c r="M27" t="n">
-        <v>49140.03</v>
+        <v>54969.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>32694.52</v>
+        <v>49140.03</v>
       </c>
       <c r="M28" t="n">
-        <v>32694.52</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1571,32 +1571,32 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>7023.14</v>
       </c>
       <c r="L29" t="n">
-        <v>6832.95</v>
+        <v>47128.14</v>
       </c>
       <c r="M29" t="n">
-        <v>6832.95</v>
+        <v>54151.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>25651.43</v>
+        <v>32694.52</v>
       </c>
       <c r="M30" t="n">
-        <v>25651.43</v>
+        <v>32694.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>22806.75</v>
+        <v>6832.95</v>
       </c>
       <c r="M31" t="n">
-        <v>22806.75</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>16215.69</v>
+        <v>25651.43</v>
       </c>
       <c r="M32" t="n">
-        <v>16215.69</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1743,32 +1743,32 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2183684.66</v>
+        <v>22806.75</v>
       </c>
       <c r="M33" t="n">
-        <v>4324064.79</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>134156.01</v>
+        <v>16215.69</v>
       </c>
       <c r="M34" t="n">
-        <v>134156.01</v>
+        <v>16215.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1829,22 +1829,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L35" t="n">
-        <v>6281.5</v>
+        <v>2183684.66</v>
       </c>
       <c r="M35" t="n">
-        <v>6281.5</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>35224.49</v>
+        <v>3043.1</v>
       </c>
       <c r="M37" t="n">
-        <v>35224.49</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>9653.08</v>
+        <v>28176.54</v>
       </c>
       <c r="M38" t="n">
-        <v>9653.08</v>
+        <v>28176.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>68501.49000000001</v>
+        <v>9653.08</v>
       </c>
       <c r="M39" t="n">
-        <v>68501.49000000001</v>
+        <v>9653.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>59518.06</v>
+        <v>68501.49000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>59518.06</v>
+        <v>68501.49000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,26 +2093,26 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>92453.89999999999</v>
+        <v>59518.06</v>
       </c>
       <c r="M41" t="n">
-        <v>92453.89999999999</v>
+        <v>59518.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,9 +2136,52 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>92453.89999999999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>92453.89999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>3695.34</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>3695.34</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>9 de julio de 2026</t>
+          <t>14 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>4665.02</v>
+        <v>4377.64</v>
       </c>
       <c r="H4" t="n">
-        <v>79155.34</v>
+        <v>87640.96000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>83820.36</v>
+        <v>92018.60000000001</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,16 +502,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2310.6</v>
+        <v>8271.43</v>
       </c>
       <c r="M4" t="n">
-        <v>2310.6</v>
+        <v>8271.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,13 +530,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>4377.64</v>
+        <v>4665.02</v>
       </c>
       <c r="H5" t="n">
-        <v>71663.37</v>
+        <v>79155.34</v>
       </c>
       <c r="I5" t="n">
-        <v>76041.00999999999</v>
+        <v>83820.36</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15980.3</v>
+        <v>2310.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15980.3</v>
+        <v>2310.6</v>
       </c>
     </row>
     <row r="6">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>20232.35</v>
+        <v>22480.76</v>
       </c>
       <c r="I6" t="n">
-        <v>20232.35</v>
+        <v>22480.76</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -588,10 +588,10 @@
         <v>3925.94</v>
       </c>
       <c r="L6" t="n">
-        <v>111014</v>
+        <v>106740.25</v>
       </c>
       <c r="M6" t="n">
-        <v>114939.94</v>
+        <v>110666.19</v>
       </c>
     </row>
     <row r="7">
@@ -668,32 +668,32 @@
         <v>9483.780000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="L8" t="n">
-        <v>5468.7</v>
+        <v>25194.79</v>
       </c>
       <c r="M8" t="n">
-        <v>5468.7</v>
+        <v>26988.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8496.639999999999</v>
+        <v>9422.16</v>
       </c>
       <c r="I9" t="n">
-        <v>8496.639999999999</v>
+        <v>9422.16</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7694.63</v>
+        <v>124733.86</v>
       </c>
       <c r="M9" t="n">
-        <v>7694.63</v>
+        <v>124733.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7555.89</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>7555.89</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,26 +760,26 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>54253.97</v>
+        <v>7694.63</v>
       </c>
       <c r="M10" t="n">
-        <v>54253.97</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6236.42</v>
+        <v>8422.459999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>6236.42</v>
+        <v>8422.459999999999</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>132467.7</v>
+        <v>341940.48</v>
       </c>
       <c r="M11" t="n">
-        <v>132467.7</v>
+        <v>341940.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5224.69</v>
+        <v>8004.31</v>
       </c>
       <c r="I12" t="n">
-        <v>5224.69</v>
+        <v>8004.31</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>114475.8</v>
+        <v>130699.81</v>
       </c>
       <c r="M12" t="n">
-        <v>114475.8</v>
+        <v>130699.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4785.92</v>
+        <v>7555.89</v>
       </c>
       <c r="I13" t="n">
-        <v>4785.92</v>
+        <v>7555.89</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>345577.01</v>
+        <v>54253.97</v>
       </c>
       <c r="M13" t="n">
-        <v>345577.01</v>
+        <v>54253.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4468.7</v>
+        <v>7489.86</v>
       </c>
       <c r="I14" t="n">
-        <v>4468.7</v>
+        <v>7489.86</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>22506.75</v>
+        <v>52093.59</v>
       </c>
       <c r="M14" t="n">
-        <v>22506.75</v>
+        <v>52093.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7580.21</v>
+        <v>5224.69</v>
       </c>
       <c r="I15" t="n">
-        <v>4347.76</v>
+        <v>5224.69</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23815.2</v>
+        <v>114475.8</v>
       </c>
       <c r="M15" t="n">
-        <v>23815.2</v>
+        <v>114475.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4023</v>
+        <v>4468.7</v>
       </c>
       <c r="I16" t="n">
-        <v>4023</v>
+        <v>4468.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>17020.43</v>
+        <v>22506.75</v>
       </c>
       <c r="M16" t="n">
-        <v>17020.43</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-3232.45</v>
       </c>
       <c r="H17" t="n">
-        <v>3199.93</v>
+        <v>7580.21</v>
       </c>
       <c r="I17" t="n">
-        <v>3199.93</v>
+        <v>4347.76</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>34877.64</v>
+        <v>23815.2</v>
       </c>
       <c r="M17" t="n">
-        <v>34877.64</v>
+        <v>23815.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2968.17</v>
+        <v>4023</v>
       </c>
       <c r="I18" t="n">
-        <v>2968.17</v>
+        <v>4023</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>17020.43</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>17020.43</v>
       </c>
     </row>
     <row r="19">
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2418.28</v>
+        <v>3373.23</v>
       </c>
       <c r="I19" t="n">
-        <v>2418.28</v>
+        <v>3373.23</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,28 +1178,28 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2340.27</v>
+        <v>3294.34</v>
       </c>
       <c r="I20" t="n">
-        <v>2340.27</v>
+        <v>3294.34</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L20" t="n">
-        <v>3215.87</v>
+        <v>122258.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3215.87</v>
+        <v>145305.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,38 +1221,38 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2061.35</v>
+        <v>3199.93</v>
       </c>
       <c r="I21" t="n">
-        <v>2061.35</v>
+        <v>3199.93</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>15543.45</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>77925.53999999999</v>
+        <v>34877.64</v>
       </c>
       <c r="M21" t="n">
-        <v>93468.99000000001</v>
+        <v>34877.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1853.84</v>
+        <v>2968.17</v>
       </c>
       <c r="I22" t="n">
-        <v>1853.84</v>
+        <v>2968.17</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>132302.17</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>132302.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2340.27</v>
       </c>
       <c r="I23" t="n">
-        <v>1774.15</v>
+        <v>2340.27</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>36313.01</v>
+        <v>3215.87</v>
       </c>
       <c r="M23" t="n">
-        <v>36313.01</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,50 +1338,50 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2142.19</v>
       </c>
       <c r="H24" t="n">
-        <v>1761.99</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1761.99</v>
+        <v>2142.19</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>23046.35</v>
+        <v>4880.95</v>
       </c>
       <c r="L24" t="n">
-        <v>123791.17</v>
+        <v>47128.14</v>
       </c>
       <c r="M24" t="n">
-        <v>146837.52</v>
+        <v>52009.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="I25" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>13206.35</v>
+        <v>62382.09</v>
       </c>
       <c r="M25" t="n">
-        <v>13206.35</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1748.24</v>
+        <v>1801.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1748.24</v>
+        <v>1801.74</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>9075.540000000001</v>
+        <v>14413.95</v>
       </c>
       <c r="M26" t="n">
-        <v>9075.540000000001</v>
+        <v>14413.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,40 +1467,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H27" t="n">
-        <v>1737.22</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1737.22</v>
+        <v>1774.15</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L27" t="n">
-        <v>54969.92</v>
+        <v>36313.01</v>
       </c>
       <c r="M27" t="n">
-        <v>54969.92</v>
+        <v>57107.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>49140.03</v>
+        <v>13206.35</v>
       </c>
       <c r="M28" t="n">
-        <v>49140.03</v>
+        <v>13206.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,38 +1565,38 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>7023.14</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>47128.14</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>54151.28</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>32694.52</v>
+        <v>49140.03</v>
       </c>
       <c r="M30" t="n">
-        <v>32694.52</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6832.95</v>
+        <v>32694.52</v>
       </c>
       <c r="M31" t="n">
-        <v>6832.95</v>
+        <v>32694.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
       <c r="M32" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>22806.75</v>
+        <v>25651.43</v>
       </c>
       <c r="M33" t="n">
-        <v>22806.75</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16215.69</v>
+        <v>22806.75</v>
       </c>
       <c r="M34" t="n">
-        <v>16215.69</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="35">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>14 de julio de 2026</t>
+          <t>15 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -640,17 +640,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,28 +662,28 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9483.780000000001</v>
+        <v>10742.45</v>
       </c>
       <c r="I8" t="n">
-        <v>9483.780000000001</v>
+        <v>10742.45</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1793.28</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>25194.79</v>
+        <v>339352.33</v>
       </c>
       <c r="M8" t="n">
-        <v>26988.07</v>
+        <v>339352.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,38 +705,38 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9422.16</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>9422.16</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="L9" t="n">
-        <v>124733.86</v>
+        <v>25194.79</v>
       </c>
       <c r="M9" t="n">
-        <v>124733.86</v>
+        <v>26988.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8496.639999999999</v>
+        <v>9422.16</v>
       </c>
       <c r="I10" t="n">
-        <v>8496.639999999999</v>
+        <v>9422.16</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7694.63</v>
+        <v>124733.86</v>
       </c>
       <c r="M10" t="n">
-        <v>7694.63</v>
+        <v>124733.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8422.459999999999</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>8422.459999999999</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>341940.48</v>
+        <v>7694.63</v>
       </c>
       <c r="M11" t="n">
-        <v>341940.48</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="12">
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7555.89</v>
+        <v>7752.11</v>
       </c>
       <c r="I13" t="n">
-        <v>7555.89</v>
+        <v>7752.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L13" t="n">
-        <v>54253.97</v>
+        <v>117801.08</v>
       </c>
       <c r="M13" t="n">
-        <v>54253.97</v>
+        <v>140847.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7489.86</v>
+        <v>7555.89</v>
       </c>
       <c r="I14" t="n">
-        <v>7489.86</v>
+        <v>7555.89</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>52093.59</v>
+        <v>54253.97</v>
       </c>
       <c r="M14" t="n">
-        <v>52093.59</v>
+        <v>54253.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,38 +963,38 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5224.69</v>
+        <v>7489.86</v>
       </c>
       <c r="I15" t="n">
-        <v>5224.69</v>
+        <v>7489.86</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>43237.93</v>
       </c>
       <c r="L15" t="n">
-        <v>114475.8</v>
+        <v>52093.59</v>
       </c>
       <c r="M15" t="n">
-        <v>114475.8</v>
+        <v>95331.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4468.7</v>
+        <v>6382.31</v>
       </c>
       <c r="I16" t="n">
-        <v>4468.7</v>
+        <v>6382.31</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>22506.75</v>
+        <v>20971.42</v>
       </c>
       <c r="M16" t="n">
-        <v>22506.75</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>7580.21</v>
+        <v>5224.69</v>
       </c>
       <c r="I17" t="n">
-        <v>4347.76</v>
+        <v>5224.69</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>23815.2</v>
+        <v>114475.8</v>
       </c>
       <c r="M17" t="n">
-        <v>23815.2</v>
+        <v>114475.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4023</v>
+        <v>4745.85</v>
       </c>
       <c r="I18" t="n">
-        <v>4023</v>
+        <v>4745.85</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,26 +1104,26 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17020.43</v>
+        <v>88137.78999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>17020.43</v>
+        <v>88137.78999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3373.23</v>
+        <v>4468.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3373.23</v>
+        <v>4468.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>20971.42</v>
+        <v>22506.75</v>
       </c>
       <c r="M19" t="n">
-        <v>20971.42</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1175,41 +1175,41 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-3232.45</v>
       </c>
       <c r="H20" t="n">
-        <v>3294.34</v>
+        <v>7580.21</v>
       </c>
       <c r="I20" t="n">
-        <v>3294.34</v>
+        <v>4347.76</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>23046.35</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>122258.85</v>
+        <v>23815.2</v>
       </c>
       <c r="M20" t="n">
-        <v>145305.2</v>
+        <v>23815.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,38 +1221,38 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3199.93</v>
+        <v>4023</v>
       </c>
       <c r="I21" t="n">
-        <v>3199.93</v>
+        <v>4023</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>33210.52</v>
       </c>
       <c r="L21" t="n">
-        <v>34877.64</v>
+        <v>17020.43</v>
       </c>
       <c r="M21" t="n">
-        <v>34877.64</v>
+        <v>50230.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2968.17</v>
+        <v>3199.93</v>
       </c>
       <c r="I22" t="n">
-        <v>2968.17</v>
+        <v>3199.93</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>34877.64</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>34877.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2340.27</v>
+        <v>2968.17</v>
       </c>
       <c r="I23" t="n">
-        <v>2340.27</v>
+        <v>2968.17</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,93 +1338,93 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2142.19</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2340.27</v>
       </c>
       <c r="I24" t="n">
-        <v>2142.19</v>
+        <v>2340.27</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4880.95</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>47128.14</v>
+        <v>3215.87</v>
       </c>
       <c r="M24" t="n">
-        <v>52009.09</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2142.19</v>
       </c>
       <c r="H25" t="n">
-        <v>2061.35</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2061.35</v>
+        <v>2142.19</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4880.95</v>
       </c>
       <c r="L25" t="n">
-        <v>62382.09</v>
+        <v>47128.14</v>
       </c>
       <c r="M25" t="n">
-        <v>62382.09</v>
+        <v>52009.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1801.74</v>
+        <v>2061.35</v>
       </c>
       <c r="I26" t="n">
-        <v>1801.74</v>
+        <v>2061.35</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>14413.95</v>
+        <v>62382.09</v>
       </c>
       <c r="M26" t="n">
-        <v>14413.95</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,40 +1467,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1801.74</v>
       </c>
       <c r="I27" t="n">
-        <v>1774.15</v>
+        <v>1801.74</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>36313.01</v>
+        <v>14413.95</v>
       </c>
       <c r="M27" t="n">
-        <v>57107.2</v>
+        <v>14413.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,40 +1510,40 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H28" t="n">
-        <v>1761.99</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1761.99</v>
+        <v>1774.15</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L28" t="n">
-        <v>13206.35</v>
+        <v>36313.01</v>
       </c>
       <c r="M28" t="n">
-        <v>13206.35</v>
+        <v>57107.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1748.24</v>
+        <v>1761.99</v>
       </c>
       <c r="I29" t="n">
-        <v>1748.24</v>
+        <v>1761.99</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>9075.540000000001</v>
+        <v>13206.35</v>
       </c>
       <c r="M29" t="n">
-        <v>9075.540000000001</v>
+        <v>13206.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>49140.03</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>49140.03</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1663.43</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1663.43</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>32694.52</v>
+        <v>31031.09</v>
       </c>
       <c r="M31" t="n">
-        <v>32694.52</v>
+        <v>31031.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
       <c r="M32" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
       <c r="M33" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>22806.75</v>
+        <v>25651.43</v>
       </c>
       <c r="M34" t="n">
-        <v>22806.75</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1829,22 +1829,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2183684.66</v>
+        <v>22806.75</v>
       </c>
       <c r="M35" t="n">
-        <v>4324064.79</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1872,22 +1872,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L36" t="n">
-        <v>6281.5</v>
+        <v>2183684.66</v>
       </c>
       <c r="M36" t="n">
-        <v>6281.5</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
       <c r="M38" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>9653.08</v>
+        <v>28176.54</v>
       </c>
       <c r="M39" t="n">
-        <v>9653.08</v>
+        <v>28176.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>68501.49000000001</v>
+        <v>9653.08</v>
       </c>
       <c r="M40" t="n">
-        <v>68501.49000000001</v>
+        <v>9653.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>59518.06</v>
+        <v>68501.49000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>59518.06</v>
+        <v>68501.49000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>92453.89999999999</v>
+        <v>59518.06</v>
       </c>
       <c r="M42" t="n">
-        <v>92453.89999999999</v>
+        <v>59518.06</v>
       </c>
     </row>
     <row r="43">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>15 de julio de 2026</t>
+          <t>17 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>4377.64</v>
+        <v>4665.02</v>
       </c>
       <c r="H4" t="n">
-        <v>87640.96000000001</v>
+        <v>79155.34</v>
       </c>
       <c r="I4" t="n">
-        <v>92018.60000000001</v>
+        <v>83820.36</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,26 +502,26 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8271.43</v>
+        <v>2310.6</v>
       </c>
       <c r="M4" t="n">
-        <v>8271.43</v>
+        <v>2310.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,13 +530,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>4665.02</v>
+        <v>56273.13</v>
       </c>
       <c r="H5" t="n">
-        <v>79155.34</v>
+        <v>1663.43</v>
       </c>
       <c r="I5" t="n">
-        <v>83820.36</v>
+        <v>57936.56</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2310.6</v>
+        <v>31031.09</v>
       </c>
       <c r="M5" t="n">
-        <v>2310.6</v>
+        <v>31031.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,40 +564,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4019.13</v>
       </c>
       <c r="H6" t="n">
-        <v>22480.76</v>
+        <v>48439.14</v>
       </c>
       <c r="I6" t="n">
-        <v>22480.76</v>
+        <v>52458.27</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3925.94</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>106740.25</v>
+        <v>50355.05</v>
       </c>
       <c r="M6" t="n">
-        <v>110666.19</v>
+        <v>50355.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,28 +619,28 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>12104.18</v>
+        <v>22480.76</v>
       </c>
       <c r="I7" t="n">
-        <v>12104.18</v>
+        <v>22480.76</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3925.94</v>
       </c>
       <c r="L7" t="n">
-        <v>6978.13</v>
+        <v>106740.25</v>
       </c>
       <c r="M7" t="n">
-        <v>6978.13</v>
+        <v>110666.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>10742.45</v>
+        <v>19439.59</v>
       </c>
       <c r="I8" t="n">
-        <v>10742.45</v>
+        <v>19439.59</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>339352.33</v>
+        <v>8271.43</v>
       </c>
       <c r="M8" t="n">
-        <v>339352.33</v>
+        <v>8271.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,38 +705,38 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9483.780000000001</v>
+        <v>15796.53</v>
       </c>
       <c r="I9" t="n">
-        <v>9483.780000000001</v>
+        <v>15796.53</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1793.28</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>25194.79</v>
+        <v>103903.95</v>
       </c>
       <c r="M9" t="n">
-        <v>26988.07</v>
+        <v>103903.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,28 +748,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>9422.16</v>
+        <v>14925.31</v>
       </c>
       <c r="I10" t="n">
-        <v>9422.16</v>
+        <v>14925.31</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>23046.35</v>
       </c>
       <c r="L10" t="n">
-        <v>124733.86</v>
+        <v>110627.88</v>
       </c>
       <c r="M10" t="n">
-        <v>124733.86</v>
+        <v>133674.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8496.639999999999</v>
+        <v>12104.18</v>
       </c>
       <c r="I11" t="n">
-        <v>8496.639999999999</v>
+        <v>12104.18</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7694.63</v>
+        <v>6978.13</v>
       </c>
       <c r="M11" t="n">
-        <v>7694.63</v>
+        <v>6978.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8004.31</v>
+        <v>11221.61</v>
       </c>
       <c r="I12" t="n">
-        <v>8004.31</v>
+        <v>11221.61</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>130699.81</v>
+        <v>122934.4</v>
       </c>
       <c r="M12" t="n">
-        <v>130699.81</v>
+        <v>122934.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,22 +877,22 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7752.11</v>
+        <v>10742.45</v>
       </c>
       <c r="I13" t="n">
-        <v>7752.11</v>
+        <v>10742.45</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>23046.35</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>117801.08</v>
+        <v>339352.33</v>
       </c>
       <c r="M13" t="n">
-        <v>140847.43</v>
+        <v>339352.33</v>
       </c>
     </row>
     <row r="14">
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7555.89</v>
+        <v>10556.59</v>
       </c>
       <c r="I14" t="n">
-        <v>7555.89</v>
+        <v>10556.59</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>54253.97</v>
+        <v>51253.23</v>
       </c>
       <c r="M14" t="n">
-        <v>54253.97</v>
+        <v>51253.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7489.86</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>7489.86</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>43237.93</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>52093.59</v>
+        <v>58727.91</v>
       </c>
       <c r="M15" t="n">
-        <v>95331.52</v>
+        <v>58727.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6382.31</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>6382.31</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="L16" t="n">
-        <v>20971.42</v>
+        <v>25194.79</v>
       </c>
       <c r="M16" t="n">
-        <v>20971.42</v>
+        <v>26988.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-3232.45</v>
       </c>
       <c r="H17" t="n">
-        <v>5224.69</v>
+        <v>12516.83</v>
       </c>
       <c r="I17" t="n">
-        <v>5224.69</v>
+        <v>9284.379999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>114475.8</v>
+        <v>18405.23</v>
       </c>
       <c r="M17" t="n">
-        <v>114475.8</v>
+        <v>18405.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4745.85</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>4745.85</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>88137.78999999999</v>
+        <v>7694.63</v>
       </c>
       <c r="M18" t="n">
-        <v>88137.78999999999</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4468.7</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>4468.7</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,26 +1147,26 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>22506.75</v>
+        <v>88137.78999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>22506.75</v>
+        <v>88137.78999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1175,31 +1175,31 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7580.21</v>
+        <v>8004.31</v>
       </c>
       <c r="I20" t="n">
-        <v>4347.76</v>
+        <v>8004.31</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2535.92</v>
       </c>
       <c r="L20" t="n">
-        <v>23815.2</v>
+        <v>130699.81</v>
       </c>
       <c r="M20" t="n">
-        <v>23815.2</v>
+        <v>133235.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,40 +1209,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5863.45</v>
       </c>
       <c r="H21" t="n">
-        <v>4023</v>
+        <v>1160.7</v>
       </c>
       <c r="I21" t="n">
-        <v>4023</v>
+        <v>7024.15</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>33210.52</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>17020.43</v>
+        <v>47128.14</v>
       </c>
       <c r="M21" t="n">
-        <v>50230.95</v>
+        <v>47128.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3199.93</v>
+        <v>6382.31</v>
       </c>
       <c r="I22" t="n">
-        <v>3199.93</v>
+        <v>6382.31</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>34877.64</v>
+        <v>20971.42</v>
       </c>
       <c r="M22" t="n">
-        <v>34877.64</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2968.17</v>
+        <v>6064.17</v>
       </c>
       <c r="I23" t="n">
-        <v>2968.17</v>
+        <v>6064.17</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3588.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2340.27</v>
+        <v>5255.37</v>
       </c>
       <c r="I24" t="n">
-        <v>2340.27</v>
+        <v>5255.37</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,69 +1362,69 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2142.19</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4981.93</v>
       </c>
       <c r="I25" t="n">
-        <v>2142.19</v>
+        <v>4981.93</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4880.95</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>47128.14</v>
+        <v>33095.64</v>
       </c>
       <c r="M25" t="n">
-        <v>52009.09</v>
+        <v>33095.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2061.35</v>
+        <v>4468.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2061.35</v>
+        <v>4468.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>62382.09</v>
+        <v>22506.75</v>
       </c>
       <c r="M26" t="n">
-        <v>62382.09</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1801.74</v>
+        <v>4023</v>
       </c>
       <c r="I27" t="n">
-        <v>1801.74</v>
+        <v>4023</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>33210.52</v>
       </c>
       <c r="L27" t="n">
-        <v>14413.95</v>
+        <v>17020.43</v>
       </c>
       <c r="M27" t="n">
-        <v>14413.95</v>
+        <v>50230.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,40 +1510,40 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2968.17</v>
       </c>
       <c r="I28" t="n">
-        <v>1774.15</v>
+        <v>2968.17</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>36313.01</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>57107.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1761.99</v>
+        <v>2340.27</v>
       </c>
       <c r="I29" t="n">
-        <v>1761.99</v>
+        <v>2340.27</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>13206.35</v>
+        <v>3215.87</v>
       </c>
       <c r="M29" t="n">
-        <v>13206.35</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1748.24</v>
+        <v>2061.35</v>
       </c>
       <c r="I30" t="n">
-        <v>1748.24</v>
+        <v>2061.35</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>9075.540000000001</v>
+        <v>62382.09</v>
       </c>
       <c r="M30" t="n">
-        <v>9075.540000000001</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1663.43</v>
+        <v>1801.74</v>
       </c>
       <c r="I31" t="n">
-        <v>1663.43</v>
+        <v>1801.74</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31031.09</v>
+        <v>14413.95</v>
       </c>
       <c r="M31" t="n">
-        <v>31031.09</v>
+        <v>14413.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,40 +1682,40 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L32" t="n">
-        <v>49140.03</v>
+        <v>36313.01</v>
       </c>
       <c r="M32" t="n">
-        <v>49140.03</v>
+        <v>57107.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>6832.95</v>
+        <v>10864.97</v>
       </c>
       <c r="M33" t="n">
-        <v>6832.95</v>
+        <v>10864.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>25651.43</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>25651.43</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>22806.75</v>
+        <v>49140.03</v>
       </c>
       <c r="M35" t="n">
-        <v>22806.75</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1872,22 +1872,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2183684.66</v>
+        <v>6832.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4324064.79</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>6281.5</v>
+        <v>25651.43</v>
       </c>
       <c r="M37" t="n">
-        <v>6281.5</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>3043.1</v>
+        <v>22806.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3043.1</v>
+        <v>22806.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L39" t="n">
-        <v>28176.54</v>
+        <v>2183684.66</v>
       </c>
       <c r="M39" t="n">
-        <v>28176.54</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>9653.08</v>
+        <v>6281.5</v>
       </c>
       <c r="M40" t="n">
-        <v>9653.08</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>68501.49000000001</v>
+        <v>3043.1</v>
       </c>
       <c r="M41" t="n">
-        <v>68501.49000000001</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,26 +2136,26 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>59518.06</v>
+        <v>28176.54</v>
       </c>
       <c r="M42" t="n">
-        <v>59518.06</v>
+        <v>28176.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2173,15 +2173,58 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>57661.97</v>
       </c>
       <c r="L43" t="n">
+        <v>59518.06</v>
+      </c>
+      <c r="M43" t="n">
+        <v>117180.03</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>3695.34</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>3695.34</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>17 de julio de 2026</t>
+          <t>20 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>4019.13</v>
       </c>
       <c r="H6" t="n">
-        <v>48439.14</v>
+        <v>51315.46</v>
       </c>
       <c r="I6" t="n">
-        <v>52458.27</v>
+        <v>55334.59</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>15796.53</v>
+        <v>18810.1</v>
       </c>
       <c r="I9" t="n">
-        <v>15796.53</v>
+        <v>18810.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>103903.95</v>
+        <v>100890.38</v>
       </c>
       <c r="M9" t="n">
-        <v>103903.95</v>
+        <v>100890.38</v>
       </c>
     </row>
     <row r="10">
@@ -748,28 +748,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>14925.31</v>
+        <v>16663.14</v>
       </c>
       <c r="I10" t="n">
-        <v>14925.31</v>
+        <v>16663.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>23046.35</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>110627.88</v>
+        <v>85843.7</v>
       </c>
       <c r="M10" t="n">
-        <v>133674.23</v>
+        <v>85843.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-3232.45</v>
       </c>
       <c r="H11" t="n">
-        <v>12104.18</v>
+        <v>17991</v>
       </c>
       <c r="I11" t="n">
-        <v>12104.18</v>
+        <v>14758.55</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6978.13</v>
+        <v>12931.03</v>
       </c>
       <c r="M11" t="n">
-        <v>6978.13</v>
+        <v>12931.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>11221.61</v>
+        <v>12104.18</v>
       </c>
       <c r="I12" t="n">
-        <v>11221.61</v>
+        <v>12104.18</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,26 +846,26 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>122934.4</v>
+        <v>6978.13</v>
       </c>
       <c r="M12" t="n">
-        <v>122934.4</v>
+        <v>6978.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>10742.45</v>
+        <v>11221.61</v>
       </c>
       <c r="I13" t="n">
-        <v>10742.45</v>
+        <v>11221.61</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>339352.33</v>
+        <v>122934.4</v>
       </c>
       <c r="M13" t="n">
-        <v>339352.33</v>
+        <v>122934.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10556.59</v>
+        <v>10742.45</v>
       </c>
       <c r="I14" t="n">
-        <v>10556.59</v>
+        <v>10742.45</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>51253.23</v>
+        <v>339352.33</v>
       </c>
       <c r="M14" t="n">
-        <v>51253.23</v>
+        <v>339352.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>9773.620000000001</v>
+        <v>10556.59</v>
       </c>
       <c r="I15" t="n">
-        <v>9773.620000000001</v>
+        <v>10556.59</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,26 +975,26 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>58727.91</v>
+        <v>51253.23</v>
       </c>
       <c r="M15" t="n">
-        <v>58727.91</v>
+        <v>51253.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9483.780000000001</v>
+        <v>10152.32</v>
       </c>
       <c r="I16" t="n">
-        <v>9483.780000000001</v>
+        <v>10152.32</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1793.28</v>
+        <v>57661.97</v>
       </c>
       <c r="L16" t="n">
-        <v>25194.79</v>
+        <v>52737.61</v>
       </c>
       <c r="M16" t="n">
-        <v>26988.07</v>
+        <v>110399.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>12516.83</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>9284.379999999999</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>18405.23</v>
+        <v>58727.91</v>
       </c>
       <c r="M17" t="n">
-        <v>18405.23</v>
+        <v>58727.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8496.639999999999</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>8496.639999999999</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="L18" t="n">
-        <v>7694.63</v>
+        <v>25194.79</v>
       </c>
       <c r="M18" t="n">
-        <v>7694.63</v>
+        <v>26988.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8394.559999999999</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>8394.559999999999</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,26 +1147,26 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>88137.78999999999</v>
+        <v>7694.63</v>
       </c>
       <c r="M19" t="n">
-        <v>88137.78999999999</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,96 +1178,96 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8004.31</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>8004.31</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2535.92</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>130699.81</v>
+        <v>88137.78999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>133235.73</v>
+        <v>88137.78999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5863.45</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1160.7</v>
+        <v>8004.31</v>
       </c>
       <c r="I21" t="n">
-        <v>7024.15</v>
+        <v>8004.31</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2535.92</v>
       </c>
       <c r="L21" t="n">
-        <v>47128.14</v>
+        <v>130699.81</v>
       </c>
       <c r="M21" t="n">
-        <v>47128.14</v>
+        <v>133235.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5863.45</v>
       </c>
       <c r="H22" t="n">
-        <v>6382.31</v>
+        <v>1160.7</v>
       </c>
       <c r="I22" t="n">
-        <v>6382.31</v>
+        <v>7024.15</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>20971.42</v>
+        <v>47128.14</v>
       </c>
       <c r="M22" t="n">
-        <v>20971.42</v>
+        <v>47128.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6064.17</v>
+        <v>6382.31</v>
       </c>
       <c r="I23" t="n">
-        <v>6064.17</v>
+        <v>6382.31</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3588.95</v>
+        <v>20971.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3588.95</v>
+        <v>20971.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5255.37</v>
+        <v>6064.17</v>
       </c>
       <c r="I24" t="n">
-        <v>5255.37</v>
+        <v>6064.17</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,59 +1362,59 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3588.95</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H25" t="n">
-        <v>4981.93</v>
+        <v>3682.12</v>
       </c>
       <c r="I25" t="n">
-        <v>4981.93</v>
+        <v>5456.27</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L25" t="n">
-        <v>33095.64</v>
+        <v>30935.53</v>
       </c>
       <c r="M25" t="n">
-        <v>33095.64</v>
+        <v>51729.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="I26" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,26 +1448,26 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4023</v>
+        <v>4981.93</v>
       </c>
       <c r="I27" t="n">
-        <v>4023</v>
+        <v>4981.93</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>33210.52</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>17020.43</v>
+        <v>33095.64</v>
       </c>
       <c r="M27" t="n">
-        <v>50230.95</v>
+        <v>33095.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2968.17</v>
+        <v>4468.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2968.17</v>
+        <v>4468.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>22506.75</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,38 +1565,38 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2340.27</v>
+        <v>4023</v>
       </c>
       <c r="I29" t="n">
-        <v>2340.27</v>
+        <v>4023</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>33210.52</v>
       </c>
       <c r="L29" t="n">
-        <v>3215.87</v>
+        <v>17020.43</v>
       </c>
       <c r="M29" t="n">
-        <v>3215.87</v>
+        <v>50230.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2061.35</v>
+        <v>2968.17</v>
       </c>
       <c r="I30" t="n">
-        <v>2061.35</v>
+        <v>2968.17</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>62382.09</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>62382.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1801.74</v>
+        <v>2340.27</v>
       </c>
       <c r="I31" t="n">
-        <v>1801.74</v>
+        <v>2340.27</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>14413.95</v>
+        <v>3215.87</v>
       </c>
       <c r="M31" t="n">
-        <v>14413.95</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,50 +1682,50 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2073.34</v>
       </c>
       <c r="I32" t="n">
-        <v>1774.15</v>
+        <v>2073.34</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>36313.01</v>
+        <v>20733.41</v>
       </c>
       <c r="M32" t="n">
-        <v>57107.2</v>
+        <v>20733.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="I33" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>10864.97</v>
+        <v>62382.09</v>
       </c>
       <c r="M33" t="n">
-        <v>10864.97</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1748.24</v>
+        <v>1801.74</v>
       </c>
       <c r="I34" t="n">
-        <v>1748.24</v>
+        <v>1801.74</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9075.540000000001</v>
+        <v>14413.95</v>
       </c>
       <c r="M34" t="n">
-        <v>9075.540000000001</v>
+        <v>14413.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1761.99</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>49140.03</v>
+        <v>10864.97</v>
       </c>
       <c r="M35" t="n">
-        <v>49140.03</v>
+        <v>10864.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>6832.95</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>6832.95</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>25651.43</v>
+        <v>49140.03</v>
       </c>
       <c r="M37" t="n">
-        <v>25651.43</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>22806.75</v>
+        <v>6832.95</v>
       </c>
       <c r="M38" t="n">
-        <v>22806.75</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2183684.66</v>
+        <v>25651.43</v>
       </c>
       <c r="M39" t="n">
-        <v>4324064.79</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L40" t="n">
-        <v>6281.5</v>
+        <v>2183684.66</v>
       </c>
       <c r="M40" t="n">
-        <v>6281.5</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
       <c r="M42" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>57661.97</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>59518.06</v>
+        <v>28176.54</v>
       </c>
       <c r="M43" t="n">
-        <v>117180.03</v>
+        <v>28176.54</v>
       </c>
     </row>
     <row r="44">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>20 de julio de 2026</t>
+          <t>21 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>4665.02</v>
       </c>
       <c r="H4" t="n">
-        <v>79155.34</v>
+        <v>81465.99000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>83820.36</v>
+        <v>86131.00999999999</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2310.6</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2310.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>19439.59</v>
+        <v>21878.94</v>
       </c>
       <c r="I8" t="n">
-        <v>19439.59</v>
+        <v>21878.94</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8271.43</v>
+        <v>98281.48</v>
       </c>
       <c r="M8" t="n">
-        <v>8271.43</v>
+        <v>98281.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>18810.1</v>
+        <v>21181.21</v>
       </c>
       <c r="I9" t="n">
-        <v>18810.1</v>
+        <v>21181.21</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,26 +717,26 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>100890.38</v>
+        <v>6529.81</v>
       </c>
       <c r="M9" t="n">
-        <v>100890.38</v>
+        <v>6529.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>16663.14</v>
+        <v>18802.26</v>
       </c>
       <c r="I10" t="n">
-        <v>16663.14</v>
+        <v>18802.26</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>85843.7</v>
+        <v>8551.469999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>85843.7</v>
+        <v>8551.469999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-3232.45</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>17991</v>
+        <v>16663.14</v>
       </c>
       <c r="I11" t="n">
-        <v>14758.55</v>
+        <v>16663.14</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12931.03</v>
+        <v>85843.7</v>
       </c>
       <c r="M11" t="n">
-        <v>12931.03</v>
+        <v>85843.7</v>
       </c>
     </row>
     <row r="12">
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>339352.33</v>
+        <v>334194.1</v>
       </c>
       <c r="M14" t="n">
-        <v>339352.33</v>
+        <v>334194.1</v>
       </c>
     </row>
     <row r="15">
@@ -1242,7 +1242,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,65 +1252,65 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>5863.45</v>
+        <v>1774.15</v>
       </c>
       <c r="H22" t="n">
-        <v>1160.7</v>
+        <v>6185.56</v>
       </c>
       <c r="I22" t="n">
-        <v>7024.15</v>
+        <v>7959.71</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L22" t="n">
-        <v>47128.14</v>
+        <v>30935.53</v>
       </c>
       <c r="M22" t="n">
-        <v>47128.14</v>
+        <v>51729.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5863.45</v>
       </c>
       <c r="H23" t="n">
-        <v>6382.31</v>
+        <v>1160.7</v>
       </c>
       <c r="I23" t="n">
-        <v>6382.31</v>
+        <v>7024.15</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>20971.42</v>
+        <v>47128.14</v>
       </c>
       <c r="M23" t="n">
-        <v>20971.42</v>
+        <v>47128.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6064.17</v>
+        <v>6818.76</v>
       </c>
       <c r="I24" t="n">
-        <v>6064.17</v>
+        <v>6818.76</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3588.95</v>
+        <v>31258.81</v>
       </c>
       <c r="M24" t="n">
-        <v>3588.95</v>
+        <v>31258.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3682.12</v>
+        <v>6064.17</v>
       </c>
       <c r="I25" t="n">
-        <v>5456.27</v>
+        <v>6064.17</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>30935.53</v>
+        <v>3588.95</v>
       </c>
       <c r="M25" t="n">
-        <v>51729.72</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="26">
@@ -1457,17 +1457,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4981.93</v>
+        <v>4468.7</v>
       </c>
       <c r="I27" t="n">
-        <v>4981.93</v>
+        <v>4468.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>33095.64</v>
+        <v>22506.75</v>
       </c>
       <c r="M27" t="n">
-        <v>33095.64</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4468.7</v>
+        <v>4276.89</v>
       </c>
       <c r="I28" t="n">
-        <v>4468.7</v>
+        <v>4276.89</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>22506.75</v>
+        <v>8350.110000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22506.75</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1586,7 +1586,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-6586.29</v>
       </c>
       <c r="H30" t="n">
-        <v>2968.17</v>
+        <v>10378.79</v>
       </c>
       <c r="I30" t="n">
-        <v>2968.17</v>
+        <v>3792.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>12931.03</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>12931.03</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2340.27</v>
+        <v>3603.49</v>
       </c>
       <c r="I31" t="n">
-        <v>2340.27</v>
+        <v>3603.49</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3215.87</v>
+        <v>12612.21</v>
       </c>
       <c r="M31" t="n">
-        <v>3215.87</v>
+        <v>12612.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2073.34</v>
+        <v>2968.17</v>
       </c>
       <c r="I32" t="n">
-        <v>2073.34</v>
+        <v>2968.17</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>20733.41</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>20733.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2061.35</v>
+        <v>2340.27</v>
       </c>
       <c r="I33" t="n">
-        <v>2061.35</v>
+        <v>2340.27</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>62382.09</v>
+        <v>3215.87</v>
       </c>
       <c r="M33" t="n">
-        <v>62382.09</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1801.74</v>
+        <v>2073.34</v>
       </c>
       <c r="I34" t="n">
-        <v>1801.74</v>
+        <v>2073.34</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,26 +1792,26 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>14413.95</v>
+        <v>20733.41</v>
       </c>
       <c r="M34" t="n">
-        <v>14413.95</v>
+        <v>20733.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="I35" t="n">
-        <v>1761.99</v>
+        <v>2061.35</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>10864.97</v>
+        <v>62382.09</v>
       </c>
       <c r="M35" t="n">
-        <v>10864.97</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="36">
@@ -1887,7 +1887,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
       <c r="M38" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
       <c r="M39" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2183684.66</v>
+        <v>25651.43</v>
       </c>
       <c r="M40" t="n">
-        <v>4324064.79</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2087,22 +2087,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>2140380.13</v>
       </c>
       <c r="L41" t="n">
-        <v>6281.5</v>
+        <v>2183684.66</v>
       </c>
       <c r="M41" t="n">
-        <v>6281.5</v>
+        <v>4324064.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3043.1</v>
+        <v>6281.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
       <c r="M43" t="n">
-        <v>28176.54</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,9 +2222,52 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>28176.54</v>
+      </c>
+      <c r="M44" t="n">
+        <v>28176.54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>3695.34</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>3695.34</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>21 de julio de 2026</t>
+          <t>24 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -496,16 +496,16 @@
         <v>86131.00999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>28672.05</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>28672.05</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         <v>56273.13</v>
       </c>
       <c r="H5" t="n">
-        <v>1663.43</v>
+        <v>3447.9</v>
       </c>
       <c r="I5" t="n">
-        <v>57936.56</v>
+        <v>59721.03</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31031.09</v>
+        <v>29246.63</v>
       </c>
       <c r="M5" t="n">
-        <v>31031.09</v>
+        <v>29246.63</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,28 +619,28 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>22480.76</v>
+        <v>37796.22</v>
       </c>
       <c r="I7" t="n">
-        <v>22480.76</v>
+        <v>37796.22</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3925.94</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>106740.25</v>
+        <v>312298.6</v>
       </c>
       <c r="M7" t="n">
-        <v>110666.19</v>
+        <v>312298.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,28 +662,28 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>21878.94</v>
+        <v>24772.19</v>
       </c>
       <c r="I8" t="n">
-        <v>21878.94</v>
+        <v>24772.19</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3925.94</v>
       </c>
       <c r="L8" t="n">
-        <v>98281.48</v>
+        <v>105014.82</v>
       </c>
       <c r="M8" t="n">
-        <v>98281.48</v>
+        <v>108940.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>21181.21</v>
+        <v>21878.94</v>
       </c>
       <c r="I9" t="n">
-        <v>21181.21</v>
+        <v>21878.94</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,26 +717,26 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6529.81</v>
+        <v>98281.48</v>
       </c>
       <c r="M9" t="n">
-        <v>6529.81</v>
+        <v>98281.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>18802.26</v>
+        <v>21181.21</v>
       </c>
       <c r="I10" t="n">
-        <v>18802.26</v>
+        <v>21181.21</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8551.469999999999</v>
+        <v>6529.81</v>
       </c>
       <c r="M10" t="n">
-        <v>8551.469999999999</v>
+        <v>6529.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,50 +779,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H11" t="n">
-        <v>16663.14</v>
+        <v>17605.42</v>
       </c>
       <c r="I11" t="n">
-        <v>16663.14</v>
+        <v>19379.57</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L11" t="n">
-        <v>85843.7</v>
+        <v>19515.67</v>
       </c>
       <c r="M11" t="n">
-        <v>85843.7</v>
+        <v>40309.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>12104.18</v>
+        <v>18802.26</v>
       </c>
       <c r="I12" t="n">
-        <v>12104.18</v>
+        <v>18802.26</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,26 +846,26 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6978.13</v>
+        <v>8551.469999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>6978.13</v>
+        <v>8551.469999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>11221.61</v>
+        <v>16663.14</v>
       </c>
       <c r="I13" t="n">
-        <v>11221.61</v>
+        <v>16663.14</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,26 +889,26 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>122934.4</v>
+        <v>85843.7</v>
       </c>
       <c r="M13" t="n">
-        <v>122934.4</v>
+        <v>85843.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10742.45</v>
+        <v>15243.2</v>
       </c>
       <c r="I14" t="n">
-        <v>10742.45</v>
+        <v>15243.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>334194.1</v>
+        <v>118912.8</v>
       </c>
       <c r="M14" t="n">
-        <v>334194.1</v>
+        <v>118912.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-6586.29</v>
       </c>
       <c r="H15" t="n">
-        <v>10556.59</v>
+        <v>21344.84</v>
       </c>
       <c r="I15" t="n">
-        <v>10556.59</v>
+        <v>14758.55</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>51253.23</v>
+        <v>12931.03</v>
       </c>
       <c r="M15" t="n">
-        <v>51253.23</v>
+        <v>12931.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>10152.32</v>
+        <v>14434.84</v>
       </c>
       <c r="I16" t="n">
-        <v>10152.32</v>
+        <v>14434.84</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>57661.97</v>
+        <v>2140380.13</v>
       </c>
       <c r="L16" t="n">
-        <v>52737.61</v>
+        <v>2169249.82</v>
       </c>
       <c r="M16" t="n">
-        <v>110399.58</v>
+        <v>4309629.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9773.620000000001</v>
+        <v>12104.18</v>
       </c>
       <c r="I17" t="n">
-        <v>9773.620000000001</v>
+        <v>12104.18</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>58727.91</v>
+        <v>6978.13</v>
       </c>
       <c r="M17" t="n">
-        <v>58727.91</v>
+        <v>6978.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9483.780000000001</v>
+        <v>10556.59</v>
       </c>
       <c r="I18" t="n">
-        <v>9483.780000000001</v>
+        <v>10556.59</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1793.28</v>
+        <v>20327.64</v>
       </c>
       <c r="L18" t="n">
-        <v>25194.79</v>
+        <v>51253.23</v>
       </c>
       <c r="M18" t="n">
-        <v>26988.07</v>
+        <v>71580.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,28 +1135,28 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8496.639999999999</v>
+        <v>10152.32</v>
       </c>
       <c r="I19" t="n">
-        <v>8496.639999999999</v>
+        <v>10152.32</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>57661.97</v>
       </c>
       <c r="L19" t="n">
-        <v>7694.63</v>
+        <v>52737.61</v>
       </c>
       <c r="M19" t="n">
-        <v>7694.63</v>
+        <v>110399.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8394.559999999999</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>8394.559999999999</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>88137.78999999999</v>
+        <v>58727.91</v>
       </c>
       <c r="M20" t="n">
-        <v>88137.78999999999</v>
+        <v>58727.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,28 +1221,28 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8004.31</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>8004.31</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2535.92</v>
+        <v>1793.28</v>
       </c>
       <c r="L21" t="n">
-        <v>130699.81</v>
+        <v>25194.79</v>
       </c>
       <c r="M21" t="n">
-        <v>133235.73</v>
+        <v>26988.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,40 +1252,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6185.56</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>7959.71</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>30935.53</v>
+        <v>7694.63</v>
       </c>
       <c r="M22" t="n">
-        <v>51729.72</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5863.45</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1160.7</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>7024.15</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>47128.14</v>
+        <v>88137.78999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>47128.14</v>
+        <v>88137.78999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6818.76</v>
+        <v>8004.31</v>
       </c>
       <c r="I24" t="n">
-        <v>6818.76</v>
+        <v>8004.31</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2535.92</v>
       </c>
       <c r="L24" t="n">
-        <v>31258.81</v>
+        <v>130699.81</v>
       </c>
       <c r="M24" t="n">
-        <v>31258.81</v>
+        <v>133235.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5863.45</v>
       </c>
       <c r="H25" t="n">
-        <v>6064.17</v>
+        <v>1160.7</v>
       </c>
       <c r="I25" t="n">
-        <v>6064.17</v>
+        <v>7024.15</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,26 +1405,26 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3588.95</v>
+        <v>47128.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3588.95</v>
+        <v>47128.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5255.37</v>
+        <v>6818.76</v>
       </c>
       <c r="I26" t="n">
-        <v>5255.37</v>
+        <v>6818.76</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>31258.81</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>31258.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4468.7</v>
+        <v>6064.17</v>
       </c>
       <c r="I27" t="n">
-        <v>4468.7</v>
+        <v>6064.17</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>22506.75</v>
+        <v>3588.95</v>
       </c>
       <c r="M27" t="n">
-        <v>22506.75</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4276.89</v>
+        <v>5648</v>
       </c>
       <c r="I28" t="n">
-        <v>4276.89</v>
+        <v>5648</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8350.110000000001</v>
+        <v>20733.41</v>
       </c>
       <c r="M28" t="n">
-        <v>8350.110000000001</v>
+        <v>20733.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,28 +1565,28 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4023</v>
+        <v>5255.37</v>
       </c>
       <c r="I29" t="n">
-        <v>4023</v>
+        <v>5255.37</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>33210.52</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>17020.43</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>50230.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-6586.29</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>10378.79</v>
+        <v>4468.7</v>
       </c>
       <c r="I30" t="n">
-        <v>3792.5</v>
+        <v>4468.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>12931.03</v>
+        <v>22506.75</v>
       </c>
       <c r="M30" t="n">
-        <v>12931.03</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3603.49</v>
+        <v>4276.89</v>
       </c>
       <c r="I31" t="n">
-        <v>3603.49</v>
+        <v>4276.89</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>12612.21</v>
+        <v>8350.110000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>12612.21</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,28 +1694,28 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2968.17</v>
+        <v>4023</v>
       </c>
       <c r="I32" t="n">
-        <v>2968.17</v>
+        <v>4023</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>33210.52</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>17020.43</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>50230.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2340.27</v>
+        <v>3603.49</v>
       </c>
       <c r="I33" t="n">
-        <v>2340.27</v>
+        <v>3603.49</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>3215.87</v>
+        <v>12612.21</v>
       </c>
       <c r="M33" t="n">
-        <v>3215.87</v>
+        <v>12612.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2073.34</v>
+        <v>2968.17</v>
       </c>
       <c r="I34" t="n">
-        <v>2073.34</v>
+        <v>2968.17</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,26 +1792,26 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>20733.41</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>20733.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2061.35</v>
+        <v>2340.27</v>
       </c>
       <c r="I35" t="n">
-        <v>2061.35</v>
+        <v>2340.27</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,26 +1835,26 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>62382.09</v>
+        <v>3215.87</v>
       </c>
       <c r="M35" t="n">
-        <v>62382.09</v>
+        <v>3215.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1748.24</v>
+        <v>2061.35</v>
       </c>
       <c r="I36" t="n">
-        <v>1748.24</v>
+        <v>2061.35</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>9075.540000000001</v>
+        <v>62382.09</v>
       </c>
       <c r="M36" t="n">
-        <v>9075.540000000001</v>
+        <v>62382.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1599.61</v>
+        <v>1748.24</v>
       </c>
       <c r="I37" t="n">
-        <v>1599.61</v>
+        <v>1748.24</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
       <c r="M39" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
       <c r="M40" t="n">
-        <v>25651.43</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2087,16 +2087,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2183684.66</v>
+        <v>25651.43</v>
       </c>
       <c r="M41" t="n">
-        <v>4324064.79</v>
+        <v>25651.43</v>
       </c>
     </row>
     <row r="42">
@@ -2136,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>6281.5</v>
+        <v>1429.25</v>
       </c>
       <c r="M42" t="n">
-        <v>6281.5</v>
+        <v>1429.25</v>
       </c>
     </row>
     <row r="43">
@@ -2222,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>28176.54</v>
+        <v>25195.3</v>
       </c>
       <c r="M44" t="n">
-        <v>28176.54</v>
+        <v>25195.3</v>
       </c>
     </row>
     <row r="45">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>24 de julio de 2026</t>
+          <t>28 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -496,16 +496,16 @@
         <v>86131.00999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>28672.05</v>
+        <v>30565.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>28672.05</v>
+        <v>30565.3</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         <v>56273.13</v>
       </c>
       <c r="H5" t="n">
-        <v>3447.9</v>
+        <v>5232.36</v>
       </c>
       <c r="I5" t="n">
-        <v>59721.03</v>
+        <v>61505.49</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>29246.63</v>
+        <v>27462.16</v>
       </c>
       <c r="M5" t="n">
-        <v>29246.63</v>
+        <v>27462.16</v>
       </c>
     </row>
     <row r="6">
@@ -576,10 +576,10 @@
         <v>4019.13</v>
       </c>
       <c r="H6" t="n">
-        <v>51315.46</v>
+        <v>53788.31</v>
       </c>
       <c r="I6" t="n">
-        <v>55334.59</v>
+        <v>57807.44</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>50355.05</v>
+        <v>47882.19</v>
       </c>
       <c r="M6" t="n">
-        <v>50355.05</v>
+        <v>47882.19</v>
       </c>
     </row>
     <row r="7">
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>37796.22</v>
+        <v>51343.54</v>
       </c>
       <c r="I7" t="n">
-        <v>37796.22</v>
+        <v>51343.54</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>312298.6</v>
+        <v>298751.28</v>
       </c>
       <c r="M7" t="n">
-        <v>312298.6</v>
+        <v>298751.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,40 +650,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2670.57</v>
       </c>
       <c r="H8" t="n">
-        <v>24772.19</v>
+        <v>34562.91</v>
       </c>
       <c r="I8" t="n">
-        <v>24772.19</v>
+        <v>37233.48</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3925.94</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>105014.82</v>
+        <v>17020.43</v>
       </c>
       <c r="M8" t="n">
-        <v>108940.76</v>
+        <v>17020.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,28 +705,28 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>21878.94</v>
+        <v>24772.19</v>
       </c>
       <c r="I9" t="n">
-        <v>21878.94</v>
+        <v>24772.19</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3925.94</v>
       </c>
       <c r="L9" t="n">
-        <v>98281.48</v>
+        <v>105014.82</v>
       </c>
       <c r="M9" t="n">
-        <v>98281.48</v>
+        <v>108940.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>21181.21</v>
+        <v>23937.12</v>
       </c>
       <c r="I10" t="n">
-        <v>21181.21</v>
+        <v>23937.12</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,69 +760,69 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6529.81</v>
+        <v>96223.3</v>
       </c>
       <c r="M10" t="n">
-        <v>6529.81</v>
+        <v>96223.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>17605.42</v>
+        <v>23577.55</v>
       </c>
       <c r="I11" t="n">
-        <v>19379.57</v>
+        <v>23577.55</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>19515.67</v>
+        <v>17699.94</v>
       </c>
       <c r="M11" t="n">
-        <v>40309.86</v>
+        <v>17699.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>18802.26</v>
+        <v>21181.21</v>
       </c>
       <c r="I12" t="n">
-        <v>18802.26</v>
+        <v>21181.21</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8551.469999999999</v>
+        <v>6529.81</v>
       </c>
       <c r="M12" t="n">
-        <v>8551.469999999999</v>
+        <v>6529.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,40 +865,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H13" t="n">
-        <v>16663.14</v>
+        <v>17605.42</v>
       </c>
       <c r="I13" t="n">
-        <v>16663.14</v>
+        <v>19379.57</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L13" t="n">
-        <v>85843.7</v>
+        <v>19515.67</v>
       </c>
       <c r="M13" t="n">
-        <v>85843.7</v>
+        <v>40309.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>15243.2</v>
+        <v>18802.26</v>
       </c>
       <c r="I14" t="n">
-        <v>15243.2</v>
+        <v>18802.26</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>118912.8</v>
+        <v>8551.469999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>118912.8</v>
+        <v>8551.469999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -960,41 +960,41 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-6586.29</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>21344.84</v>
+        <v>18449.48</v>
       </c>
       <c r="I15" t="n">
-        <v>14758.55</v>
+        <v>18449.48</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>40607.95</v>
       </c>
       <c r="L15" t="n">
-        <v>12931.03</v>
+        <v>43360.33</v>
       </c>
       <c r="M15" t="n">
-        <v>12931.03</v>
+        <v>83968.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14434.84</v>
+        <v>17573.59</v>
       </c>
       <c r="I16" t="n">
-        <v>14434.84</v>
+        <v>17573.59</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2140380.13</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2169249.82</v>
+        <v>116655.84</v>
       </c>
       <c r="M16" t="n">
-        <v>4309629.95</v>
+        <v>116655.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>12104.18</v>
+        <v>16663.14</v>
       </c>
       <c r="I17" t="n">
-        <v>12104.18</v>
+        <v>16663.14</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,26 +1061,26 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>6978.13</v>
+        <v>85843.7</v>
       </c>
       <c r="M17" t="n">
-        <v>6978.13</v>
+        <v>85843.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10556.59</v>
+        <v>15061.43</v>
       </c>
       <c r="I18" t="n">
-        <v>10556.59</v>
+        <v>15061.43</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>20327.64</v>
+        <v>2535.92</v>
       </c>
       <c r="L18" t="n">
-        <v>51253.23</v>
+        <v>123642.69</v>
       </c>
       <c r="M18" t="n">
-        <v>71580.87</v>
+        <v>126178.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1132,31 +1132,31 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-6586.29</v>
       </c>
       <c r="H19" t="n">
-        <v>10152.32</v>
+        <v>21344.84</v>
       </c>
       <c r="I19" t="n">
-        <v>10152.32</v>
+        <v>14758.55</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>57661.97</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>52737.61</v>
+        <v>12931.03</v>
       </c>
       <c r="M19" t="n">
-        <v>110399.58</v>
+        <v>12931.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,38 +1178,38 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>9773.620000000001</v>
+        <v>14434.84</v>
       </c>
       <c r="I20" t="n">
-        <v>9773.620000000001</v>
+        <v>14434.84</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2230648.56</v>
       </c>
       <c r="L20" t="n">
-        <v>58727.91</v>
+        <v>2169249.82</v>
       </c>
       <c r="M20" t="n">
-        <v>58727.91</v>
+        <v>4399898.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,53 +1221,53 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9483.780000000001</v>
+        <v>13848.72</v>
       </c>
       <c r="I21" t="n">
-        <v>9483.780000000001</v>
+        <v>13848.72</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1793.28</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>25194.79</v>
+        <v>5233.6</v>
       </c>
       <c r="M21" t="n">
-        <v>26988.07</v>
+        <v>5233.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="H22" t="n">
-        <v>8496.639999999999</v>
+        <v>9483.780000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>8496.639999999999</v>
+        <v>11277.06</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>7694.63</v>
+        <v>25194.79</v>
       </c>
       <c r="M22" t="n">
-        <v>7694.63</v>
+        <v>25194.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,38 +1307,38 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8394.559999999999</v>
+        <v>10152.32</v>
       </c>
       <c r="I23" t="n">
-        <v>8394.559999999999</v>
+        <v>10152.32</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>57661.97</v>
       </c>
       <c r="L23" t="n">
-        <v>88137.78999999999</v>
+        <v>52737.61</v>
       </c>
       <c r="M23" t="n">
-        <v>88137.78999999999</v>
+        <v>110399.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8004.31</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>8004.31</v>
+        <v>9773.620000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2535.92</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>130699.81</v>
+        <v>58727.91</v>
       </c>
       <c r="M24" t="n">
-        <v>133235.73</v>
+        <v>58727.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5863.45</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1160.7</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>7024.15</v>
+        <v>8496.639999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,26 +1405,26 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>47128.14</v>
+        <v>7694.63</v>
       </c>
       <c r="M25" t="n">
-        <v>47128.14</v>
+        <v>7694.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6818.76</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>6818.76</v>
+        <v>8394.559999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>31258.81</v>
+        <v>88137.78999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>31258.81</v>
+        <v>88137.78999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,22 +1467,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5863.45</v>
       </c>
       <c r="H27" t="n">
-        <v>6064.17</v>
+        <v>1160.7</v>
       </c>
       <c r="I27" t="n">
-        <v>6064.17</v>
+        <v>7024.15</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>3588.95</v>
+        <v>47128.14</v>
       </c>
       <c r="M27" t="n">
-        <v>3588.95</v>
+        <v>47128.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5648</v>
+        <v>6064.17</v>
       </c>
       <c r="I28" t="n">
-        <v>5648</v>
+        <v>6064.17</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>20733.41</v>
+        <v>3588.95</v>
       </c>
       <c r="M28" t="n">
-        <v>20733.41</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5255.37</v>
+        <v>5648</v>
       </c>
       <c r="I29" t="n">
-        <v>5255.37</v>
+        <v>5648</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>20733.41</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>20733.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="I30" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4276.89</v>
+        <v>4468.7</v>
       </c>
       <c r="I31" t="n">
-        <v>4276.89</v>
+        <v>4468.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8350.110000000001</v>
+        <v>22506.75</v>
       </c>
       <c r="M31" t="n">
-        <v>8350.110000000001</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,28 +1694,28 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4023</v>
+        <v>4276.89</v>
       </c>
       <c r="I32" t="n">
-        <v>4023</v>
+        <v>4276.89</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>33210.52</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>17020.43</v>
+        <v>8350.110000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>50230.95</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3603.49</v>
+        <v>4108.16</v>
       </c>
       <c r="I33" t="n">
-        <v>3603.49</v>
+        <v>4108.16</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,26 +1749,26 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>12612.21</v>
+        <v>21543.27</v>
       </c>
       <c r="M33" t="n">
-        <v>12612.21</v>
+        <v>21543.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2968.17</v>
+        <v>4088.85</v>
       </c>
       <c r="I34" t="n">
-        <v>2968.17</v>
+        <v>4088.85</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>60354.59</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>60354.59</v>
       </c>
     </row>
     <row r="35">
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2340.27</v>
+        <v>4054.21</v>
       </c>
       <c r="I35" t="n">
-        <v>2340.27</v>
+        <v>4054.21</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,26 +1835,26 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3215.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2061.35</v>
+        <v>3603.49</v>
       </c>
       <c r="I36" t="n">
-        <v>2061.35</v>
+        <v>3603.49</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>62382.09</v>
+        <v>12612.21</v>
       </c>
       <c r="M36" t="n">
-        <v>62382.09</v>
+        <v>12612.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1748.24</v>
+        <v>2968.17</v>
       </c>
       <c r="I37" t="n">
-        <v>1748.24</v>
+        <v>2968.17</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>9075.540000000001</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>9075.540000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1599.61</v>
+        <v>2482.01</v>
       </c>
       <c r="I38" t="n">
-        <v>1599.61</v>
+        <v>2482.01</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>22713.31</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>22713.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1748.24</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>49140.03</v>
+        <v>9075.540000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>49140.03</v>
+        <v>9075.540000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>6832.95</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>6832.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>25651.43</v>
+        <v>49140.03</v>
       </c>
       <c r="M41" t="n">
-        <v>25651.43</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1429.25</v>
+        <v>6832.95</v>
       </c>
       <c r="M42" t="n">
-        <v>1429.25</v>
+        <v>6832.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3043.1</v>
+        <v>1429.25</v>
       </c>
       <c r="M43" t="n">
-        <v>3043.1</v>
+        <v>1429.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>25195.3</v>
+        <v>3043.1</v>
       </c>
       <c r="M44" t="n">
-        <v>25195.3</v>
+        <v>3043.1</v>
       </c>
     </row>
     <row r="45">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>28 de julio de 2026</t>
+          <t>29 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -812,7 +812,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>21181.21</v>
+        <v>21194.34</v>
       </c>
       <c r="I12" t="n">
-        <v>21181.21</v>
+        <v>21194.34</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6529.81</v>
+        <v>81312.5</v>
       </c>
       <c r="M12" t="n">
-        <v>6529.81</v>
+        <v>81312.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,93 +865,93 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>17605.42</v>
+        <v>21181.21</v>
       </c>
       <c r="I13" t="n">
-        <v>19379.57</v>
+        <v>21181.21</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19515.67</v>
+        <v>6529.81</v>
       </c>
       <c r="M13" t="n">
-        <v>40309.86</v>
+        <v>6529.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H14" t="n">
-        <v>18802.26</v>
+        <v>17605.42</v>
       </c>
       <c r="I14" t="n">
-        <v>18802.26</v>
+        <v>19379.57</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20794.19</v>
       </c>
       <c r="L14" t="n">
-        <v>8551.469999999999</v>
+        <v>19515.67</v>
       </c>
       <c r="M14" t="n">
-        <v>8551.469999999999</v>
+        <v>40309.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,38 +963,38 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>18449.48</v>
+        <v>18802.26</v>
       </c>
       <c r="I15" t="n">
-        <v>18449.48</v>
+        <v>18802.26</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>40607.95</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>43360.33</v>
+        <v>8551.469999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>83968.28</v>
+        <v>8551.469999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,38 +1006,38 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>17573.59</v>
+        <v>18449.48</v>
       </c>
       <c r="I16" t="n">
-        <v>17573.59</v>
+        <v>18449.48</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>40607.95</v>
       </c>
       <c r="L16" t="n">
-        <v>116655.84</v>
+        <v>43360.33</v>
       </c>
       <c r="M16" t="n">
-        <v>116655.84</v>
+        <v>83968.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>16663.14</v>
+        <v>17573.59</v>
       </c>
       <c r="I17" t="n">
-        <v>16663.14</v>
+        <v>17573.59</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>85843.7</v>
+        <v>116655.84</v>
       </c>
       <c r="M17" t="n">
-        <v>85843.7</v>
+        <v>116655.84</v>
       </c>
     </row>
     <row r="18">
@@ -1098,16 +1098,16 @@
         <v>15061.43</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2535.92</v>
+        <v>9712.389999999999</v>
       </c>
       <c r="L18" t="n">
         <v>123642.69</v>
       </c>
       <c r="M18" t="n">
-        <v>126178.61</v>
+        <v>133355.08</v>
       </c>
     </row>
     <row r="19">
@@ -1313,16 +1313,16 @@
         <v>10152.32</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>57661.97</v>
+        <v>76168.03999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>52737.61</v>
+        <v>71243.67999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>110399.58</v>
+        <v>147411.72</v>
       </c>
     </row>
     <row r="24">
@@ -1887,7 +1887,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2968.17</v>
+        <v>3523.31</v>
       </c>
       <c r="I37" t="n">
-        <v>2968.17</v>
+        <v>3523.31</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>21672.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>21672.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2482.01</v>
+        <v>2968.17</v>
       </c>
       <c r="I38" t="n">
-        <v>2482.01</v>
+        <v>2968.17</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>22713.31</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>22713.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1748.24</v>
+        <v>2789.54</v>
       </c>
       <c r="I39" t="n">
-        <v>1748.24</v>
+        <v>2789.54</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>9075.540000000001</v>
+        <v>8034.24</v>
       </c>
       <c r="M39" t="n">
-        <v>9075.540000000001</v>
+        <v>8034.24</v>
       </c>
     </row>
     <row r="40">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>29 de julio de 2026</t>
+          <t>30 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -484,28 +484,28 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>4665.02</v>
+        <v>33337.07</v>
       </c>
       <c r="H4" t="n">
         <v>81465.99000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>86131.00999999999</v>
+        <v>114803.06</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>30565.3</v>
+        <v>1893.25</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>30565.3</v>
+        <v>1893.25</v>
       </c>
     </row>
     <row r="5">
@@ -576,10 +576,10 @@
         <v>4019.13</v>
       </c>
       <c r="H6" t="n">
-        <v>53788.31</v>
+        <v>55526.32</v>
       </c>
       <c r="I6" t="n">
-        <v>57807.44</v>
+        <v>59545.45</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>47882.19</v>
+        <v>46144.18</v>
       </c>
       <c r="M6" t="n">
-        <v>47882.19</v>
+        <v>46144.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>40607.95</v>
       </c>
       <c r="H7" t="n">
-        <v>51343.54</v>
+        <v>18449.48</v>
       </c>
       <c r="I7" t="n">
-        <v>51343.54</v>
+        <v>59057.43</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>298751.28</v>
+        <v>43360.33</v>
       </c>
       <c r="M7" t="n">
-        <v>298751.28</v>
+        <v>43360.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2670.57</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>34562.91</v>
+        <v>58757.14</v>
       </c>
       <c r="I8" t="n">
-        <v>37233.48</v>
+        <v>58757.14</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17020.43</v>
+        <v>291337.67</v>
       </c>
       <c r="M8" t="n">
-        <v>17020.43</v>
+        <v>291337.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2670.57</v>
       </c>
       <c r="H9" t="n">
-        <v>24772.19</v>
+        <v>36504.99</v>
       </c>
       <c r="I9" t="n">
-        <v>24772.19</v>
+        <v>39175.56</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3925.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>105014.82</v>
+        <v>15078.35</v>
       </c>
       <c r="M9" t="n">
-        <v>108940.76</v>
+        <v>15078.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,50 +736,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>18506.07</v>
       </c>
       <c r="H10" t="n">
-        <v>23937.12</v>
+        <v>13444.1</v>
       </c>
       <c r="I10" t="n">
-        <v>23937.12</v>
+        <v>31950.17</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5054.91</v>
       </c>
       <c r="L10" t="n">
-        <v>96223.3</v>
+        <v>123555.96</v>
       </c>
       <c r="M10" t="n">
-        <v>96223.3</v>
+        <v>128610.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>23577.55</v>
+        <v>25458.8</v>
       </c>
       <c r="I11" t="n">
-        <v>23577.55</v>
+        <v>25458.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>17699.94</v>
+        <v>2252.2</v>
       </c>
       <c r="M11" t="n">
-        <v>17699.94</v>
+        <v>2252.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>21194.34</v>
+        <v>25280.74</v>
       </c>
       <c r="I12" t="n">
-        <v>21194.34</v>
+        <v>25280.74</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>81312.5</v>
+        <v>16366.96</v>
       </c>
       <c r="M12" t="n">
-        <v>81312.5</v>
+        <v>16366.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>21181.21</v>
+        <v>24772.19</v>
       </c>
       <c r="I13" t="n">
-        <v>21181.21</v>
+        <v>24772.19</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3925.94</v>
       </c>
       <c r="L13" t="n">
-        <v>6529.81</v>
+        <v>105014.82</v>
       </c>
       <c r="M13" t="n">
-        <v>6529.81</v>
+        <v>108940.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,50 +908,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1774.15</v>
+        <v>-6586.29</v>
       </c>
       <c r="H14" t="n">
-        <v>17605.42</v>
+        <v>31126.91</v>
       </c>
       <c r="I14" t="n">
-        <v>19379.57</v>
+        <v>24540.62</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19515.67</v>
+        <v>7496.68</v>
       </c>
       <c r="M14" t="n">
-        <v>40309.86</v>
+        <v>7496.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>18802.26</v>
+        <v>23937.12</v>
       </c>
       <c r="I15" t="n">
-        <v>18802.26</v>
+        <v>23937.12</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8551.469999999999</v>
+        <v>96223.3</v>
       </c>
       <c r="M15" t="n">
-        <v>8551.469999999999</v>
+        <v>96223.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,22 +1006,22 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>18449.48</v>
+        <v>21194.34</v>
       </c>
       <c r="I16" t="n">
-        <v>18449.48</v>
+        <v>21194.34</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>40607.95</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43360.33</v>
+        <v>81312.5</v>
       </c>
       <c r="M16" t="n">
-        <v>83968.28</v>
+        <v>81312.5</v>
       </c>
     </row>
     <row r="17">
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>17573.59</v>
+        <v>19815.92</v>
       </c>
       <c r="I17" t="n">
-        <v>17573.59</v>
+        <v>19815.92</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,69 +1061,69 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>116655.84</v>
+        <v>114413.51</v>
       </c>
       <c r="M17" t="n">
-        <v>116655.84</v>
+        <v>114413.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1774.15</v>
       </c>
       <c r="H18" t="n">
-        <v>15061.43</v>
+        <v>17605.42</v>
       </c>
       <c r="I18" t="n">
-        <v>15061.43</v>
+        <v>19379.57</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>9712.389999999999</v>
+        <v>20794.19</v>
       </c>
       <c r="L18" t="n">
-        <v>123642.69</v>
+        <v>19515.67</v>
       </c>
       <c r="M18" t="n">
-        <v>133355.08</v>
+        <v>40309.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1132,41 +1132,41 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-6586.29</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>21344.84</v>
+        <v>18981.03</v>
       </c>
       <c r="I19" t="n">
-        <v>14758.55</v>
+        <v>18981.03</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9712.389999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>12931.03</v>
+        <v>119723.08</v>
       </c>
       <c r="M19" t="n">
-        <v>12931.03</v>
+        <v>129435.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,28 +1178,28 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>14434.84</v>
+        <v>18802.26</v>
       </c>
       <c r="I20" t="n">
-        <v>14434.84</v>
+        <v>18802.26</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2230648.56</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2169249.82</v>
+        <v>8551.469999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>4399898.38</v>
+        <v>8551.469999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,53 +1221,53 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>13848.72</v>
+        <v>14434.84</v>
       </c>
       <c r="I21" t="n">
-        <v>13848.72</v>
+        <v>14434.84</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2230648.56</v>
       </c>
       <c r="L21" t="n">
-        <v>5233.6</v>
+        <v>2169249.82</v>
       </c>
       <c r="M21" t="n">
-        <v>5233.6</v>
+        <v>4399898.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1793.28</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9483.780000000001</v>
+        <v>13848.72</v>
       </c>
       <c r="I22" t="n">
-        <v>11277.06</v>
+        <v>13848.72</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,53 +1276,53 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>25194.79</v>
+        <v>5233.6</v>
       </c>
       <c r="M22" t="n">
-        <v>25194.79</v>
+        <v>5233.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1793.28</v>
       </c>
       <c r="H23" t="n">
-        <v>10152.32</v>
+        <v>11306.68</v>
       </c>
       <c r="I23" t="n">
-        <v>10152.32</v>
+        <v>13099.96</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>76168.03999999999</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>71243.67999999999</v>
+        <v>23371.89</v>
       </c>
       <c r="M23" t="n">
-        <v>147411.72</v>
+        <v>23371.89</v>
       </c>
     </row>
     <row r="24">
@@ -1500,7 +1500,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6064.17</v>
+        <v>6512.77</v>
       </c>
       <c r="I28" t="n">
-        <v>6064.17</v>
+        <v>6512.77</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3588.95</v>
+        <v>19138.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3588.95</v>
+        <v>19138.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5648</v>
+        <v>6064.17</v>
       </c>
       <c r="I29" t="n">
-        <v>5648</v>
+        <v>6064.17</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>20733.41</v>
+        <v>3588.95</v>
       </c>
       <c r="M29" t="n">
-        <v>20733.41</v>
+        <v>3588.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5255.37</v>
+        <v>5648</v>
       </c>
       <c r="I30" t="n">
-        <v>5255.37</v>
+        <v>5648</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>20733.41</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>20733.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ROCIO YANETH OCHOA IBARRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="I31" t="n">
-        <v>4468.7</v>
+        <v>5255.37</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>22506.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4276.89</v>
+        <v>4468.7</v>
       </c>
       <c r="I32" t="n">
-        <v>4276.89</v>
+        <v>4468.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>8350.110000000001</v>
+        <v>22506.75</v>
       </c>
       <c r="M32" t="n">
-        <v>8350.110000000001</v>
+        <v>22506.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4108.16</v>
+        <v>4276.89</v>
       </c>
       <c r="I33" t="n">
-        <v>4108.16</v>
+        <v>4276.89</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>21543.27</v>
+        <v>8350.110000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>21543.27</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1599.61</v>
+        <v>1694.9</v>
       </c>
       <c r="I40" t="n">
-        <v>1599.61</v>
+        <v>1694.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>5138.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5138.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1599.61</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>49140.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
       <c r="M42" t="n">
-        <v>6832.95</v>
+        <v>49140.03</v>
       </c>
     </row>
     <row r="43">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -487,31 +487,31 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>33337.07</v>
+        <v>162964</v>
       </c>
       <c r="H4" t="n">
-        <v>81465.99000000001</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>114803.06</v>
+        <v>162964</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1893.25</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>84466.67</v>
       </c>
       <c r="M4" t="n">
-        <v>1893.25</v>
+        <v>84466.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,22 +521,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>56273.13</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5232.36</v>
+        <v>21079.98</v>
       </c>
       <c r="I5" t="n">
-        <v>61505.49</v>
+        <v>21079.98</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>27462.16</v>
+        <v>49434.03</v>
       </c>
       <c r="M5" t="n">
-        <v>27462.16</v>
+        <v>49434.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4019.13</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>55526.32</v>
+        <v>8476.02</v>
       </c>
       <c r="I6" t="n">
-        <v>59545.45</v>
+        <v>8476.02</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>46144.18</v>
+        <v>5756.97</v>
       </c>
       <c r="M6" t="n">
-        <v>46144.18</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>40607.95</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>18449.48</v>
+        <v>8393.23</v>
       </c>
       <c r="I7" t="n">
-        <v>59057.43</v>
+        <v>8393.23</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>43360.33</v>
+        <v>293606.54</v>
       </c>
       <c r="M7" t="n">
-        <v>43360.33</v>
+        <v>293606.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>58757.14</v>
+        <v>7537.55</v>
       </c>
       <c r="I8" t="n">
-        <v>58757.14</v>
+        <v>7537.55</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>291337.67</v>
+        <v>72817.25999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>291337.67</v>
+        <v>72817.25999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2670.57</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>36504.99</v>
+        <v>5019.7</v>
       </c>
       <c r="I9" t="n">
-        <v>39175.56</v>
+        <v>5019.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15078.35</v>
+        <v>77443.85000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>15078.35</v>
+        <v>77443.85000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,50 +736,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>18506.07</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13444.1</v>
+        <v>4699.16</v>
       </c>
       <c r="I10" t="n">
-        <v>31950.17</v>
+        <v>4699.16</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5054.91</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>123555.96</v>
+        <v>4193.66</v>
       </c>
       <c r="M10" t="n">
-        <v>128610.87</v>
+        <v>4193.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>25458.8</v>
+        <v>3933.48</v>
       </c>
       <c r="I11" t="n">
-        <v>25458.8</v>
+        <v>3933.48</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2252.2</v>
+        <v>114538.09</v>
       </c>
       <c r="M11" t="n">
-        <v>2252.2</v>
+        <v>114538.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>25280.74</v>
+        <v>3468.29</v>
       </c>
       <c r="I12" t="n">
-        <v>25280.74</v>
+        <v>3468.29</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16366.96</v>
+        <v>47900.16</v>
       </c>
       <c r="M12" t="n">
-        <v>16366.96</v>
+        <v>47900.16</v>
       </c>
     </row>
     <row r="13">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>24772.19</v>
+        <v>3443.75</v>
       </c>
       <c r="I13" t="n">
-        <v>24772.19</v>
+        <v>3443.75</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>3925.94</v>
+        <v>3916.42</v>
       </c>
       <c r="L13" t="n">
-        <v>105014.82</v>
+        <v>105415.99</v>
       </c>
       <c r="M13" t="n">
-        <v>108940.76</v>
+        <v>109332.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -917,13 +917,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-6586.29</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>31126.91</v>
+        <v>3215.73</v>
       </c>
       <c r="I14" t="n">
-        <v>24540.62</v>
+        <v>3215.73</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7496.68</v>
+        <v>28233.37</v>
       </c>
       <c r="M14" t="n">
-        <v>7496.68</v>
+        <v>28233.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>23937.12</v>
+        <v>2960.97</v>
       </c>
       <c r="I15" t="n">
-        <v>23937.12</v>
+        <v>2960.97</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>96223.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>96223.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>21194.34</v>
+        <v>2439.24</v>
       </c>
       <c r="I16" t="n">
-        <v>21194.34</v>
+        <v>2439.24</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,41 +1018,41 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>81312.5</v>
+        <v>7690.17</v>
       </c>
       <c r="M16" t="n">
-        <v>81312.5</v>
+        <v>7690.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H17" t="n">
-        <v>19815.92</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>19815.92</v>
+        <v>2396.76</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,69 +1061,69 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>114413.51</v>
+        <v>26364.37</v>
       </c>
       <c r="M17" t="n">
-        <v>114413.51</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1774.15</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>17605.42</v>
+        <v>1843.19</v>
       </c>
       <c r="I18" t="n">
-        <v>19379.57</v>
+        <v>1843.19</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>20794.19</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>19515.67</v>
+        <v>1843.19</v>
       </c>
       <c r="M18" t="n">
-        <v>40309.86</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,38 +1135,38 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>18981.03</v>
+        <v>1757.71</v>
       </c>
       <c r="I19" t="n">
-        <v>18981.03</v>
+        <v>1757.71</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9712.389999999999</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>119723.08</v>
+        <v>9080.91</v>
       </c>
       <c r="M19" t="n">
-        <v>129435.47</v>
+        <v>9080.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>18802.26</v>
+        <v>1627.21</v>
       </c>
       <c r="I20" t="n">
-        <v>18802.26</v>
+        <v>1627.21</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>8551.469999999999</v>
+        <v>15800.91</v>
       </c>
       <c r="M20" t="n">
-        <v>8551.469999999999</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,28 +1221,28 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>14434.84</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>14434.84</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2230648.56</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2169249.82</v>
+        <v>49020.81</v>
       </c>
       <c r="M21" t="n">
-        <v>4399898.38</v>
+        <v>49020.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,28 +1264,28 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>13848.72</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>13848.72</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L22" t="n">
-        <v>5233.6</v>
+        <v>26239.01</v>
       </c>
       <c r="M22" t="n">
-        <v>5233.6</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1793.28</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>11306.68</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>13099.96</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>23371.89</v>
+        <v>27395.54</v>
       </c>
       <c r="M23" t="n">
-        <v>23371.89</v>
+        <v>27395.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9773.620000000001</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>9773.620000000001</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,26 +1362,26 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>58727.91</v>
+        <v>109437.94</v>
       </c>
       <c r="M24" t="n">
-        <v>58727.91</v>
+        <v>109437.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8496.639999999999</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8496.639999999999</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7694.63</v>
+        <v>20847.16</v>
       </c>
       <c r="M25" t="n">
-        <v>7694.63</v>
+        <v>20847.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>8394.559999999999</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>8394.559999999999</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,41 +1448,41 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>88137.78999999999</v>
+        <v>20285.63</v>
       </c>
       <c r="M26" t="n">
-        <v>88137.78999999999</v>
+        <v>20285.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5863.45</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1160.7</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7024.15</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>47128.14</v>
+        <v>28340.31</v>
       </c>
       <c r="M27" t="n">
-        <v>47128.14</v>
+        <v>28340.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6512.77</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>6512.77</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>19138.65</v>
+        <v>3381.58</v>
       </c>
       <c r="M28" t="n">
-        <v>19138.65</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>6064.17</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>6064.17</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3588.95</v>
+        <v>19092.22</v>
       </c>
       <c r="M29" t="n">
-        <v>3588.95</v>
+        <v>19092.22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5648</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>5648</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>20733.41</v>
+        <v>8530.73</v>
       </c>
       <c r="M30" t="n">
-        <v>20733.41</v>
+        <v>8530.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ROCIO YANETH OCHOA IBARRA</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>5255.37</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>5255.37</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>20683.11</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>20683.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4468.7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4468.7</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>22506.75</v>
+        <v>12581.61</v>
       </c>
       <c r="M32" t="n">
-        <v>22506.75</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,38 +1737,38 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4276.89</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4276.89</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2211997.08</v>
       </c>
       <c r="L33" t="n">
-        <v>8350.110000000001</v>
+        <v>2150747.29</v>
       </c>
       <c r="M33" t="n">
-        <v>8350.110000000001</v>
+        <v>4362744.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4088.85</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4088.85</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>60354.59</v>
+        <v>1425.78</v>
       </c>
       <c r="M34" t="n">
-        <v>60354.59</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4054.21</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4054.21</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3035.72</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3603.49</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3603.49</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>12612.21</v>
+        <v>24832.77</v>
       </c>
       <c r="M36" t="n">
-        <v>12612.21</v>
+        <v>24832.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3523.31</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3523.31</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>21672.01</v>
+        <v>99727.64</v>
       </c>
       <c r="M37" t="n">
-        <v>21672.01</v>
+        <v>99727.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2968.17</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2968.17</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>24095.39</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2789.54</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2789.54</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>8034.24</v>
+        <v>6049.41</v>
       </c>
       <c r="M39" t="n">
-        <v>8034.24</v>
+        <v>6049.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1694.9</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1694.9</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>5138.05</v>
+        <v>3208.07</v>
       </c>
       <c r="M40" t="n">
-        <v>5138.05</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1599.61</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1599.61</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>62476.76</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>62476.76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L42" t="n">
-        <v>49140.03</v>
+        <v>130020.2</v>
       </c>
       <c r="M42" t="n">
-        <v>49140.03</v>
+        <v>135062.85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1429.25</v>
+        <v>23460.24</v>
       </c>
       <c r="M43" t="n">
-        <v>1429.25</v>
+        <v>23460.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,53 +2222,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3043.1</v>
+        <v>6270.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3043.1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>63441</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3695.34</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3695.34</v>
+        <v>6270.75</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>10 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2019.94</v>
       </c>
       <c r="H9" t="n">
-        <v>5019.7</v>
+        <v>4273.63</v>
       </c>
       <c r="I9" t="n">
-        <v>5019.7</v>
+        <v>6293.57</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,26 +717,26 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>77443.85000000001</v>
+        <v>28233.37</v>
       </c>
       <c r="M9" t="n">
-        <v>77443.85000000001</v>
+        <v>28233.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4699.16</v>
+        <v>5667.45</v>
       </c>
       <c r="I10" t="n">
-        <v>4699.16</v>
+        <v>5667.45</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,26 +760,26 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4193.66</v>
+        <v>112804.12</v>
       </c>
       <c r="M10" t="n">
-        <v>4193.66</v>
+        <v>112804.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,28 +791,28 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3933.48</v>
+        <v>5177.37</v>
       </c>
       <c r="I11" t="n">
-        <v>3933.48</v>
+        <v>5177.37</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3916.42</v>
       </c>
       <c r="L11" t="n">
-        <v>114538.09</v>
+        <v>103682.37</v>
       </c>
       <c r="M11" t="n">
-        <v>114538.09</v>
+        <v>107598.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3468.29</v>
+        <v>5019.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3468.29</v>
+        <v>5019.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>47900.16</v>
+        <v>77443.85000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>47900.16</v>
+        <v>77443.85000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3443.75</v>
+        <v>4699.16</v>
       </c>
       <c r="I13" t="n">
-        <v>3443.75</v>
+        <v>4699.16</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3916.42</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>105415.99</v>
+        <v>4193.66</v>
       </c>
       <c r="M13" t="n">
-        <v>109332.41</v>
+        <v>4193.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3215.73</v>
+        <v>3468.29</v>
       </c>
       <c r="I14" t="n">
-        <v>3215.73</v>
+        <v>3468.29</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>28233.37</v>
+        <v>47900.16</v>
       </c>
       <c r="M14" t="n">
-        <v>28233.37</v>
+        <v>47900.16</v>
       </c>
     </row>
     <row r="15">
@@ -1743,16 +1743,16 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>2211997.08</v>
+        <v>90049.44</v>
       </c>
       <c r="L33" t="n">
-        <v>2150747.29</v>
+        <v>28799.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4362744.37</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="34">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>10 de agosto de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>DESIREE DE LA PE╤A OROZCO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -576,28 +576,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8476.02</v>
+        <v>13525.02</v>
       </c>
       <c r="I6" t="n">
-        <v>8476.02</v>
+        <v>13525.02</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3916.42</v>
       </c>
       <c r="L6" t="n">
-        <v>5756.97</v>
+        <v>98542.37</v>
       </c>
       <c r="M6" t="n">
-        <v>5756.97</v>
+        <v>102458.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8393.23</v>
+        <v>13506.29</v>
       </c>
       <c r="I7" t="n">
-        <v>8393.23</v>
+        <v>13506.29</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>293606.54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>293606.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ANDREA CELESTE IBA╤EZ RINCON</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7537.55</v>
+        <v>8476.02</v>
       </c>
       <c r="I8" t="n">
-        <v>7537.55</v>
+        <v>8476.02</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>72817.25999999999</v>
+        <v>5756.97</v>
       </c>
       <c r="M8" t="n">
-        <v>72817.25999999999</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2019.94</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4273.63</v>
+        <v>8393.23</v>
       </c>
       <c r="I9" t="n">
-        <v>6293.57</v>
+        <v>8393.23</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,26 +717,26 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>28233.37</v>
+        <v>293606.54</v>
       </c>
       <c r="M9" t="n">
-        <v>28233.37</v>
+        <v>293606.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5667.45</v>
+        <v>7537.55</v>
       </c>
       <c r="I10" t="n">
-        <v>5667.45</v>
+        <v>7537.55</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>112804.12</v>
+        <v>72817.25999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>112804.12</v>
+        <v>72817.25999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,50 +779,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>PAULINA LIZBETH SOTO MU╤IZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2019.94</v>
       </c>
       <c r="H11" t="n">
-        <v>5177.37</v>
+        <v>4273.63</v>
       </c>
       <c r="I11" t="n">
-        <v>5177.37</v>
+        <v>6293.57</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3916.42</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>103682.37</v>
+        <v>28233.37</v>
       </c>
       <c r="M11" t="n">
-        <v>107598.79</v>
+        <v>28233.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5019.7</v>
+        <v>5667.45</v>
       </c>
       <c r="I12" t="n">
-        <v>5019.7</v>
+        <v>5667.45</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,26 +846,26 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>77443.85000000001</v>
+        <v>112804.12</v>
       </c>
       <c r="M12" t="n">
-        <v>77443.85000000001</v>
+        <v>112804.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4699.16</v>
+        <v>5025.06</v>
       </c>
       <c r="I13" t="n">
-        <v>4699.16</v>
+        <v>5025.06</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4193.66</v>
+        <v>23315.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4193.66</v>
+        <v>23315.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ORLANDA JIMENA CERVANTES NU╤EZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3468.29</v>
+        <v>5019.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3468.29</v>
+        <v>5019.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>47900.16</v>
+        <v>77443.85000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>47900.16</v>
+        <v>77443.85000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2960.97</v>
+        <v>4699.16</v>
       </c>
       <c r="I15" t="n">
-        <v>2960.97</v>
+        <v>4699.16</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4193.66</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4193.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2439.24</v>
+        <v>3468.29</v>
       </c>
       <c r="I16" t="n">
-        <v>2439.24</v>
+        <v>3468.29</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7690.17</v>
+        <v>42067.73</v>
       </c>
       <c r="M16" t="n">
-        <v>7690.17</v>
+        <v>42067.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>EVELYN CAROLINA VENEGAS I╤IGUEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="I17" t="n">
-        <v>2396.76</v>
+        <v>2960.97</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,41 +1061,41 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H18" t="n">
-        <v>1843.19</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1843.19</v>
+        <v>2396.76</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,26 +1104,26 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1757.71</v>
+        <v>1843.19</v>
       </c>
       <c r="I19" t="n">
-        <v>1757.71</v>
+        <v>1843.19</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9080.91</v>
+        <v>1843.19</v>
       </c>
       <c r="M19" t="n">
-        <v>9080.91</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1627.21</v>
+        <v>1757.71</v>
       </c>
       <c r="I20" t="n">
-        <v>1627.21</v>
+        <v>1757.71</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>15800.91</v>
+        <v>9080.91</v>
       </c>
       <c r="M20" t="n">
-        <v>15800.91</v>
+        <v>9080.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>GABRIELA CASTA╤EDA SALAZAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1659.4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1659.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>49020.81</v>
+        <v>98068.24000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>49020.81</v>
+        <v>98068.24000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,38 +1264,38 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>26239.01</v>
+        <v>15800.91</v>
       </c>
       <c r="M22" t="n">
-        <v>50616.76</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1313,32 +1313,32 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>33305.7</v>
       </c>
       <c r="L23" t="n">
-        <v>27395.54</v>
+        <v>49020.81</v>
       </c>
       <c r="M23" t="n">
-        <v>27395.54</v>
+        <v>82326.50999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1356,22 +1356,22 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>26341.77</v>
       </c>
       <c r="L24" t="n">
-        <v>109437.94</v>
+        <v>26239.01</v>
       </c>
       <c r="M24" t="n">
-        <v>109437.94</v>
+        <v>52580.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1399,32 +1399,32 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="L25" t="n">
-        <v>20847.16</v>
+        <v>45763.67</v>
       </c>
       <c r="M25" t="n">
-        <v>20847.16</v>
+        <v>64131.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>20285.63</v>
+        <v>109437.94</v>
       </c>
       <c r="M26" t="n">
-        <v>20285.63</v>
+        <v>109437.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>28340.31</v>
+        <v>20847.16</v>
       </c>
       <c r="M27" t="n">
-        <v>28340.31</v>
+        <v>20847.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3381.58</v>
+        <v>20285.63</v>
       </c>
       <c r="M28" t="n">
-        <v>3381.58</v>
+        <v>20285.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>19092.22</v>
+        <v>3381.58</v>
       </c>
       <c r="M29" t="n">
-        <v>19092.22</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>HANA SOFIA LOPEZ QUI╤ONEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>8530.73</v>
+        <v>19092.22</v>
       </c>
       <c r="M30" t="n">
-        <v>8530.73</v>
+        <v>19092.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>20683.11</v>
+        <v>8530.73</v>
       </c>
       <c r="M31" t="n">
-        <v>20683.11</v>
+        <v>8530.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>ANA LAURA CONTRERAS I╤IGUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>12581.61</v>
+        <v>20683.11</v>
       </c>
       <c r="M32" t="n">
-        <v>12581.61</v>
+        <v>20683.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1743,22 +1743,22 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>90049.44</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>28799.65</v>
+        <v>12581.61</v>
       </c>
       <c r="M33" t="n">
-        <v>118849.09</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1786,22 +1786,22 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="L34" t="n">
-        <v>1425.78</v>
+        <v>28799.65</v>
       </c>
       <c r="M34" t="n">
-        <v>1425.78</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M35" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>24832.77</v>
+        <v>3035.72</v>
       </c>
       <c r="M36" t="n">
-        <v>24832.77</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>99727.64</v>
+        <v>24832.77</v>
       </c>
       <c r="M37" t="n">
-        <v>99727.64</v>
+        <v>24832.77</v>
       </c>
     </row>
     <row r="38">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>SAMUEL NU╤O RIVERA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>DARINKA URE╤A CASILLAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>11 de agosto de 2026</t>
+          <t>13 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PE╤A OROZCO</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -511,32 +511,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2019.94</v>
       </c>
       <c r="H5" t="n">
-        <v>21079.98</v>
+        <v>35508.38</v>
       </c>
       <c r="I5" t="n">
-        <v>21079.98</v>
+        <v>37528.32</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>49434.03</v>
+        <v>28233.37</v>
       </c>
       <c r="M5" t="n">
-        <v>49434.03</v>
+        <v>28233.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,40 +564,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>33305.7</v>
       </c>
       <c r="H6" t="n">
-        <v>13525.02</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>13525.02</v>
+        <v>33305.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3916.42</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>98542.37</v>
+        <v>49020.81</v>
       </c>
       <c r="M6" t="n">
-        <v>102458.79</v>
+        <v>49020.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,28 +619,28 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>13506.29</v>
+        <v>15302.69</v>
       </c>
       <c r="I7" t="n">
-        <v>13506.29</v>
+        <v>15302.69</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1958.21</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>75224.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>77182.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBA╤EZ RINCON</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8476.02</v>
+        <v>13506.29</v>
       </c>
       <c r="I8" t="n">
-        <v>8476.02</v>
+        <v>13506.29</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5756.97</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5756.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8393.23</v>
+        <v>11483.43</v>
       </c>
       <c r="I9" t="n">
-        <v>8393.23</v>
+        <v>11483.43</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>293606.54</v>
+        <v>106988.14</v>
       </c>
       <c r="M9" t="n">
-        <v>293606.54</v>
+        <v>106988.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7537.55</v>
+        <v>8476.02</v>
       </c>
       <c r="I10" t="n">
-        <v>7537.55</v>
+        <v>8476.02</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>72817.25999999999</v>
+        <v>5756.97</v>
       </c>
       <c r="M10" t="n">
-        <v>72817.25999999999</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,22 +779,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MU╤IZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2019.94</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4273.63</v>
+        <v>8393.23</v>
       </c>
       <c r="I11" t="n">
-        <v>6293.57</v>
+        <v>8393.23</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28233.37</v>
+        <v>291024.67</v>
       </c>
       <c r="M11" t="n">
-        <v>28233.37</v>
+        <v>291024.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,22 +834,22 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5667.45</v>
+        <v>7537.55</v>
       </c>
       <c r="I12" t="n">
-        <v>5667.45</v>
+        <v>7537.55</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>58297.52</v>
       </c>
       <c r="L12" t="n">
-        <v>112804.12</v>
+        <v>72817.25999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>112804.12</v>
+        <v>131114.78</v>
       </c>
     </row>
     <row r="13">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NU╤EZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -984,17 +984,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3468.29</v>
+        <v>3954.41</v>
       </c>
       <c r="I16" t="n">
-        <v>3468.29</v>
+        <v>3954.41</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>42067.73</v>
+        <v>8530.73</v>
       </c>
       <c r="M16" t="n">
-        <v>42067.73</v>
+        <v>8530.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS I╤IGUEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2960.97</v>
+        <v>3468.29</v>
       </c>
       <c r="I17" t="n">
-        <v>2960.97</v>
+        <v>3468.29</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>42067.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>42067.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="I18" t="n">
-        <v>2396.76</v>
+        <v>2960.97</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,41 +1104,41 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H19" t="n">
-        <v>1843.19</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1843.19</v>
+        <v>2396.76</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
       <c r="M19" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,50 +1166,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H20" t="n">
-        <v>1757.71</v>
+        <v>509.43</v>
       </c>
       <c r="I20" t="n">
-        <v>1757.71</v>
+        <v>1964.11</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L20" t="n">
-        <v>9080.91</v>
+        <v>26239.01</v>
       </c>
       <c r="M20" t="n">
-        <v>9080.91</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GABRIELA CASTA╤EDA SALAZAR</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1659.4</v>
+        <v>1843.19</v>
       </c>
       <c r="I21" t="n">
-        <v>1659.4</v>
+        <v>1843.19</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,26 +1233,26 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>98068.24000000001</v>
+        <v>1843.19</v>
       </c>
       <c r="M21" t="n">
-        <v>98068.24000000001</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1627.21</v>
+        <v>1763.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1627.21</v>
+        <v>1763.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>15800.91</v>
+        <v>107674.33</v>
       </c>
       <c r="M22" t="n">
-        <v>15800.91</v>
+        <v>107674.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,28 +1307,28 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1757.71</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1757.71</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>33305.7</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>49020.81</v>
+        <v>9080.91</v>
       </c>
       <c r="M23" t="n">
-        <v>82326.50999999999</v>
+        <v>9080.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,38 +1350,38 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1659.4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1659.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>26341.77</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>26239.01</v>
+        <v>98068.24000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>52580.78</v>
+        <v>98068.24000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>18368.13</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>45763.67</v>
+        <v>15800.91</v>
       </c>
       <c r="M25" t="n">
-        <v>64131.8</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1442,22 +1442,22 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="L26" t="n">
-        <v>109437.94</v>
+        <v>45763.67</v>
       </c>
       <c r="M26" t="n">
-        <v>109437.94</v>
+        <v>64131.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-21079.98</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>21079.98</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1491,26 +1491,26 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>20847.16</v>
+        <v>70514.00999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>20847.16</v>
+        <v>70514.00999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>20285.63</v>
+        <v>20847.16</v>
       </c>
       <c r="M28" t="n">
-        <v>20285.63</v>
+        <v>20847.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3381.58</v>
+        <v>20285.63</v>
       </c>
       <c r="M29" t="n">
-        <v>3381.58</v>
+        <v>20285.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUI╤ONEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>19092.22</v>
+        <v>3381.58</v>
       </c>
       <c r="M30" t="n">
-        <v>19092.22</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8530.73</v>
+        <v>19092.22</v>
       </c>
       <c r="M31" t="n">
-        <v>8530.73</v>
+        <v>19092.22</v>
       </c>
     </row>
     <row r="32">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS I╤IGUEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAMUEL NU╤O RIVERA</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA URE╤A CASILLAS</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>13 de agosto de 2026</t>
+          <t>14 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -597,7 +597,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,38 +619,38 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="I7" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1958.21</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>75224.37</v>
+        <v>65931.12</v>
       </c>
       <c r="M7" t="n">
-        <v>77182.58</v>
+        <v>65931.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>13506.29</v>
+        <v>15495.26</v>
       </c>
       <c r="I8" t="n">
-        <v>13506.29</v>
+        <v>15495.26</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>102976.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>102976.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11483.43</v>
+        <v>15302.69</v>
       </c>
       <c r="I9" t="n">
-        <v>11483.43</v>
+        <v>15302.69</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>106988.14</v>
+        <v>53684.04</v>
       </c>
       <c r="M9" t="n">
-        <v>106988.14</v>
+        <v>53684.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8476.02</v>
+        <v>13506.29</v>
       </c>
       <c r="I10" t="n">
-        <v>8476.02</v>
+        <v>13506.29</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5756.97</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5756.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8393.23</v>
+        <v>8476.02</v>
       </c>
       <c r="I11" t="n">
-        <v>8393.23</v>
+        <v>8476.02</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>291024.67</v>
+        <v>5756.97</v>
       </c>
       <c r="M11" t="n">
-        <v>291024.67</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,38 +834,38 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7537.55</v>
+        <v>8393.23</v>
       </c>
       <c r="I12" t="n">
-        <v>7537.55</v>
+        <v>8393.23</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>58297.52</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>72817.25999999999</v>
+        <v>291024.67</v>
       </c>
       <c r="M12" t="n">
-        <v>131114.78</v>
+        <v>291024.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,38 +877,38 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5025.06</v>
+        <v>7537.55</v>
       </c>
       <c r="I13" t="n">
-        <v>5025.06</v>
+        <v>7537.55</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>58297.52</v>
       </c>
       <c r="L13" t="n">
-        <v>23315.2</v>
+        <v>72817.25999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>23315.2</v>
+        <v>131114.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5019.7</v>
+        <v>5025.06</v>
       </c>
       <c r="I14" t="n">
-        <v>5019.7</v>
+        <v>5025.06</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>77443.85000000001</v>
+        <v>23315.2</v>
       </c>
       <c r="M14" t="n">
-        <v>77443.85000000001</v>
+        <v>23315.2</v>
       </c>
     </row>
     <row r="15">
@@ -1485,16 +1485,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>16392.68</v>
       </c>
       <c r="L27" t="n">
         <v>70514.00999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>70514.00999999999</v>
+        <v>86906.69</v>
       </c>
     </row>
     <row r="28">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>14 de agosto de 2026</t>
+          <t>18 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>162964</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8374.200000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>162964</v>
+        <v>171338.2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>84466.67</v>
+        <v>80161.03</v>
       </c>
       <c r="M4" t="n">
-        <v>84466.67</v>
+        <v>80161.03</v>
       </c>
     </row>
     <row r="5">
@@ -597,32 +597,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="H7" t="n">
-        <v>16532.42</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>16532.42</v>
+        <v>18368.13</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>65931.12</v>
+        <v>45763.67</v>
       </c>
       <c r="M7" t="n">
-        <v>65931.12</v>
+        <v>45763.67</v>
       </c>
     </row>
     <row r="8">
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>15495.26</v>
+        <v>17290.35</v>
       </c>
       <c r="I8" t="n">
-        <v>15495.26</v>
+        <v>17290.35</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>102976.31</v>
+        <v>101181.23</v>
       </c>
       <c r="M8" t="n">
-        <v>102976.31</v>
+        <v>101181.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="I9" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,41 +717,41 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>53684.04</v>
+        <v>65931.12</v>
       </c>
       <c r="M9" t="n">
-        <v>53684.04</v>
+        <v>65931.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-19514.59</v>
       </c>
       <c r="H10" t="n">
-        <v>13506.29</v>
+        <v>35907.27</v>
       </c>
       <c r="I10" t="n">
-        <v>13506.29</v>
+        <v>16392.68</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>70514.00999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>70514.00999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8476.02</v>
+        <v>15302.69</v>
       </c>
       <c r="I11" t="n">
-        <v>8476.02</v>
+        <v>15302.69</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5756.97</v>
+        <v>53684.04</v>
       </c>
       <c r="M11" t="n">
-        <v>5756.97</v>
+        <v>53684.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8393.23</v>
+        <v>13506.29</v>
       </c>
       <c r="I12" t="n">
-        <v>8393.23</v>
+        <v>13506.29</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>291024.67</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>291024.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,38 +877,38 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7537.55</v>
+        <v>12093.46</v>
       </c>
       <c r="I13" t="n">
-        <v>7537.55</v>
+        <v>12093.46</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>58297.52</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>72817.25999999999</v>
+        <v>33442.54</v>
       </c>
       <c r="M13" t="n">
-        <v>131114.78</v>
+        <v>33442.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,28 +920,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5025.06</v>
+        <v>10530.97</v>
       </c>
       <c r="I14" t="n">
-        <v>5025.06</v>
+        <v>10530.97</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>58297.52</v>
       </c>
       <c r="L14" t="n">
-        <v>23315.2</v>
+        <v>69823.8</v>
       </c>
       <c r="M14" t="n">
-        <v>23315.2</v>
+        <v>128121.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4699.16</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>4699.16</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,26 +975,26 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4193.66</v>
+        <v>18063.4</v>
       </c>
       <c r="M15" t="n">
-        <v>4193.66</v>
+        <v>18063.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3954.41</v>
+        <v>8476.02</v>
       </c>
       <c r="I16" t="n">
-        <v>3954.41</v>
+        <v>8476.02</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8530.73</v>
+        <v>5756.97</v>
       </c>
       <c r="M16" t="n">
-        <v>8530.73</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3468.29</v>
+        <v>8393.23</v>
       </c>
       <c r="I17" t="n">
-        <v>3468.29</v>
+        <v>8393.23</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42067.73</v>
+        <v>291024.67</v>
       </c>
       <c r="M17" t="n">
-        <v>42067.73</v>
+        <v>291024.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2960.97</v>
+        <v>7590.14</v>
       </c>
       <c r="I18" t="n">
-        <v>2960.97</v>
+        <v>7590.14</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,41 +1104,41 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>92596.31</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>92596.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>6087.09</v>
       </c>
       <c r="I19" t="n">
-        <v>2396.76</v>
+        <v>6087.09</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>26364.37</v>
+        <v>6398.05</v>
       </c>
       <c r="M19" t="n">
-        <v>26364.37</v>
+        <v>6398.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,50 +1166,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1454.68</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>509.43</v>
+        <v>6049.46</v>
       </c>
       <c r="I20" t="n">
-        <v>1964.11</v>
+        <v>6049.46</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>26239.01</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>50616.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1843.19</v>
+        <v>5808.77</v>
       </c>
       <c r="I21" t="n">
-        <v>1843.19</v>
+        <v>5808.77</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,26 +1233,26 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1843.19</v>
+        <v>103783.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1843.19</v>
+        <v>103783.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1763.6</v>
+        <v>5465.98</v>
       </c>
       <c r="I22" t="n">
-        <v>1763.6</v>
+        <v>5465.98</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>107674.33</v>
+        <v>57010.81</v>
       </c>
       <c r="M22" t="n">
-        <v>107674.33</v>
+        <v>57010.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1757.71</v>
+        <v>5443.04</v>
       </c>
       <c r="I23" t="n">
-        <v>1757.71</v>
+        <v>5443.04</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>9080.91</v>
+        <v>17698.48</v>
       </c>
       <c r="M23" t="n">
-        <v>9080.91</v>
+        <v>17698.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1659.4</v>
+        <v>5025.06</v>
       </c>
       <c r="I24" t="n">
-        <v>1659.4</v>
+        <v>5025.06</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>98068.24000000001</v>
+        <v>23315.2</v>
       </c>
       <c r="M24" t="n">
-        <v>98068.24000000001</v>
+        <v>23315.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1627.21</v>
+        <v>4699.16</v>
       </c>
       <c r="I25" t="n">
-        <v>1627.21</v>
+        <v>4699.16</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,26 +1405,26 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>15800.91</v>
+        <v>4193.66</v>
       </c>
       <c r="M25" t="n">
-        <v>15800.91</v>
+        <v>4193.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,81 +1436,81 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>18368.13</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>45763.67</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>64131.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>-21079.98</v>
+        <v>2396.76</v>
       </c>
       <c r="H27" t="n">
-        <v>21079.98</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>16392.68</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>70514.00999999999</v>
+        <v>26364.37</v>
       </c>
       <c r="M27" t="n">
-        <v>86906.69</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2068.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2068.31</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>20847.16</v>
+        <v>18614.8</v>
       </c>
       <c r="M28" t="n">
-        <v>20847.16</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,50 +1553,50 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>509.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1964.11</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L29" t="n">
-        <v>20285.63</v>
+        <v>26239.01</v>
       </c>
       <c r="M29" t="n">
-        <v>20285.63</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1843.19</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1843.19</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3381.58</v>
+        <v>1843.19</v>
       </c>
       <c r="M30" t="n">
-        <v>3381.58</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1777.67</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1777.67</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>19092.22</v>
+        <v>19069.49</v>
       </c>
       <c r="M31" t="n">
-        <v>19092.22</v>
+        <v>19069.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1757.71</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1757.71</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>20683.11</v>
+        <v>9080.91</v>
       </c>
       <c r="M32" t="n">
-        <v>20683.11</v>
+        <v>9080.91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>12581.61</v>
+        <v>15800.91</v>
       </c>
       <c r="M33" t="n">
-        <v>12581.61</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1786,22 +1786,22 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>90049.44</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>28799.65</v>
+        <v>20285.63</v>
       </c>
       <c r="M34" t="n">
-        <v>118849.09</v>
+        <v>20285.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1425.78</v>
+        <v>3381.58</v>
       </c>
       <c r="M35" t="n">
-        <v>1425.78</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>3035.72</v>
+        <v>19092.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3035.72</v>
+        <v>19092.22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>24832.77</v>
+        <v>12581.61</v>
       </c>
       <c r="M37" t="n">
-        <v>24832.77</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1958,22 +1958,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="L38" t="n">
-        <v>24095.39</v>
+        <v>28799.65</v>
       </c>
       <c r="M38" t="n">
-        <v>24095.39</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>6049.41</v>
+        <v>1425.78</v>
       </c>
       <c r="M39" t="n">
-        <v>6049.41</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3208.07</v>
+        <v>3035.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3208.07</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>62476.76</v>
+        <v>24095.39</v>
       </c>
       <c r="M41" t="n">
-        <v>62476.76</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>130020.2</v>
+        <v>3208.07</v>
       </c>
       <c r="M42" t="n">
-        <v>135062.85</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L43" t="n">
-        <v>23460.24</v>
+        <v>130020.2</v>
       </c>
       <c r="M43" t="n">
-        <v>23460.24</v>
+        <v>135062.85</v>
       </c>
     </row>
     <row r="44">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>18 de agosto de 2026</t>
+          <t>19 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -527,16 +527,16 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2019.94</v>
+        <v>31798.96</v>
       </c>
       <c r="H5" t="n">
-        <v>35508.38</v>
+        <v>37240.77</v>
       </c>
       <c r="I5" t="n">
-        <v>37528.32</v>
+        <v>69039.73</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>18368.13</v>
+        <v>-19514.59</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>37963.62</v>
       </c>
       <c r="I7" t="n">
-        <v>18368.13</v>
+        <v>18449.03</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>45763.67</v>
+        <v>68457.66</v>
       </c>
       <c r="M7" t="n">
-        <v>45763.67</v>
+        <v>68457.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="H8" t="n">
-        <v>17290.35</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>17290.35</v>
+        <v>18368.13</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>101181.23</v>
+        <v>45763.67</v>
       </c>
       <c r="M8" t="n">
-        <v>101181.23</v>
+        <v>45763.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>16532.42</v>
+        <v>17290.35</v>
       </c>
       <c r="I9" t="n">
-        <v>16532.42</v>
+        <v>17290.35</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,41 +717,41 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>65931.12</v>
+        <v>101181.23</v>
       </c>
       <c r="M9" t="n">
-        <v>65931.12</v>
+        <v>101181.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-19514.59</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>35907.27</v>
+        <v>16532.42</v>
       </c>
       <c r="I10" t="n">
-        <v>16392.68</v>
+        <v>16532.42</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,10 +760,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>70514.00999999999</v>
+        <v>65931.12</v>
       </c>
       <c r="M10" t="n">
-        <v>70514.00999999999</v>
+        <v>65931.12</v>
       </c>
     </row>
     <row r="11">
@@ -812,7 +812,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13506.29</v>
+        <v>15064.73</v>
       </c>
       <c r="I12" t="n">
-        <v>13506.29</v>
+        <v>15064.73</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5220.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5220.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>12093.46</v>
+        <v>13506.29</v>
       </c>
       <c r="I13" t="n">
-        <v>12093.46</v>
+        <v>13506.29</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>33442.54</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>33442.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,28 +920,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10530.97</v>
+        <v>12093.46</v>
       </c>
       <c r="I14" t="n">
-        <v>10530.97</v>
+        <v>12093.46</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>58297.52</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>69823.8</v>
+        <v>33442.54</v>
       </c>
       <c r="M14" t="n">
-        <v>128121.32</v>
+        <v>33442.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>9886.120000000001</v>
+        <v>10530.97</v>
       </c>
       <c r="I15" t="n">
-        <v>9886.120000000001</v>
+        <v>10530.97</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>58297.52</v>
       </c>
       <c r="L15" t="n">
-        <v>18063.4</v>
+        <v>69823.8</v>
       </c>
       <c r="M15" t="n">
-        <v>18063.4</v>
+        <v>128121.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8476.02</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>8476.02</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5756.97</v>
+        <v>18063.4</v>
       </c>
       <c r="M16" t="n">
-        <v>5756.97</v>
+        <v>18063.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>8393.23</v>
+        <v>9749.9</v>
       </c>
       <c r="I17" t="n">
-        <v>8393.23</v>
+        <v>9749.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>291024.67</v>
+        <v>52726.89</v>
       </c>
       <c r="M17" t="n">
-        <v>291024.67</v>
+        <v>52726.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7590.14</v>
+        <v>8476.02</v>
       </c>
       <c r="I18" t="n">
-        <v>7590.14</v>
+        <v>8476.02</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,26 +1104,26 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>92596.31</v>
+        <v>5756.97</v>
       </c>
       <c r="M18" t="n">
-        <v>92596.31</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>6087.09</v>
+        <v>8393.23</v>
       </c>
       <c r="I19" t="n">
-        <v>6087.09</v>
+        <v>8393.23</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6398.05</v>
+        <v>291024.67</v>
       </c>
       <c r="M19" t="n">
-        <v>6398.05</v>
+        <v>291024.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6049.46</v>
+        <v>7940.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6049.46</v>
+        <v>7940.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,26 +1190,26 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>17698.48</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>17698.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5808.77</v>
+        <v>7590.14</v>
       </c>
       <c r="I21" t="n">
-        <v>5808.77</v>
+        <v>7590.14</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,26 +1233,26 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>103783.01</v>
+        <v>92596.31</v>
       </c>
       <c r="M21" t="n">
-        <v>103783.01</v>
+        <v>92596.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5465.98</v>
+        <v>6087.09</v>
       </c>
       <c r="I22" t="n">
-        <v>5465.98</v>
+        <v>6087.09</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>57010.81</v>
+        <v>6398.05</v>
       </c>
       <c r="M22" t="n">
-        <v>57010.81</v>
+        <v>6398.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5443.04</v>
+        <v>6049.46</v>
       </c>
       <c r="I23" t="n">
-        <v>5443.04</v>
+        <v>6049.46</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>17698.48</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>17698.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5025.06</v>
+        <v>5808.77</v>
       </c>
       <c r="I24" t="n">
-        <v>5025.06</v>
+        <v>5808.77</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,26 +1362,26 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>23315.2</v>
+        <v>103783.01</v>
       </c>
       <c r="M24" t="n">
-        <v>23315.2</v>
+        <v>103783.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4699.16</v>
+        <v>5025.06</v>
       </c>
       <c r="I25" t="n">
-        <v>4699.16</v>
+        <v>5025.06</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>4193.66</v>
+        <v>23315.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4193.66</v>
+        <v>23315.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2960.97</v>
+        <v>4699.16</v>
       </c>
       <c r="I26" t="n">
-        <v>2960.97</v>
+        <v>4699.16</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4193.66</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4193.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,22 +1467,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>4266.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2396.76</v>
+        <v>4266.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>26364.37</v>
+        <v>6572.15</v>
       </c>
       <c r="M27" t="n">
-        <v>26364.37</v>
+        <v>6572.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2068.31</v>
+        <v>2960.97</v>
       </c>
       <c r="I28" t="n">
-        <v>2068.31</v>
+        <v>2960.97</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>18614.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>18614.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1562,41 +1562,41 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1454.68</v>
+        <v>2396.76</v>
       </c>
       <c r="H29" t="n">
-        <v>509.43</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1964.11</v>
+        <v>2396.76</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>26239.01</v>
+        <v>26364.37</v>
       </c>
       <c r="M29" t="n">
-        <v>50616.76</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1843.19</v>
+        <v>2068.31</v>
       </c>
       <c r="I30" t="n">
-        <v>1843.19</v>
+        <v>2068.31</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,69 +1620,69 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1843.19</v>
+        <v>18614.8</v>
       </c>
       <c r="M30" t="n">
-        <v>1843.19</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H31" t="n">
-        <v>1777.67</v>
+        <v>509.43</v>
       </c>
       <c r="I31" t="n">
-        <v>1777.67</v>
+        <v>1964.11</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L31" t="n">
-        <v>19069.49</v>
+        <v>26239.01</v>
       </c>
       <c r="M31" t="n">
-        <v>19069.49</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1757.71</v>
+        <v>1843.19</v>
       </c>
       <c r="I32" t="n">
-        <v>1757.71</v>
+        <v>1843.19</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9080.91</v>
+        <v>1843.19</v>
       </c>
       <c r="M32" t="n">
-        <v>9080.91</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1627.21</v>
+        <v>1777.67</v>
       </c>
       <c r="I33" t="n">
-        <v>1627.21</v>
+        <v>1777.67</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>15800.91</v>
+        <v>19069.49</v>
       </c>
       <c r="M33" t="n">
-        <v>15800.91</v>
+        <v>19069.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>20285.63</v>
+        <v>15800.91</v>
       </c>
       <c r="M34" t="n">
-        <v>20285.63</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="35">
@@ -1930,7 +1930,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1961,19 +1961,19 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>90049.44</v>
+        <v>6086.13</v>
       </c>
       <c r="L38" t="n">
-        <v>28799.65</v>
+        <v>66947.41</v>
       </c>
       <c r="M38" t="n">
-        <v>118849.09</v>
+        <v>73033.53999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="L39" t="n">
-        <v>1425.78</v>
+        <v>28799.65</v>
       </c>
       <c r="M39" t="n">
-        <v>1425.78</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M40" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
       <c r="M41" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2173,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>130020.2</v>
+        <v>3208.07</v>
       </c>
       <c r="M43" t="n">
-        <v>135062.85</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,15 +2216,58 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L44" t="n">
+        <v>130020.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>135062.85</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>65046</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>6270.75</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>6270.75</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>19 de agosto de 2026</t>
+          <t>20 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -496,16 +496,16 @@
         <v>171338.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>93618.86</v>
       </c>
       <c r="L4" t="n">
         <v>80161.03</v>
       </c>
       <c r="M4" t="n">
-        <v>80161.03</v>
+        <v>173779.89</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>33305.7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>52177.88</v>
       </c>
       <c r="I6" t="n">
-        <v>33305.7</v>
+        <v>52177.88</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,26 +588,26 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>49020.81</v>
+        <v>247240.02</v>
       </c>
       <c r="M6" t="n">
-        <v>49020.81</v>
+        <v>247240.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-19514.59</v>
+        <v>33305.7</v>
       </c>
       <c r="H7" t="n">
-        <v>37963.62</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>18449.03</v>
+        <v>33305.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>68457.66</v>
+        <v>49020.81</v>
       </c>
       <c r="M7" t="n">
-        <v>68457.66</v>
+        <v>49020.81</v>
       </c>
     </row>
     <row r="8">
@@ -662,10 +662,10 @@
         <v>18368.13</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1659.4</v>
       </c>
       <c r="I8" t="n">
-        <v>18368.13</v>
+        <v>20027.53</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>45763.67</v>
+        <v>44104.27</v>
       </c>
       <c r="M8" t="n">
-        <v>45763.67</v>
+        <v>44104.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-19514.59</v>
       </c>
       <c r="H9" t="n">
-        <v>17290.35</v>
+        <v>37963.62</v>
       </c>
       <c r="I9" t="n">
-        <v>17290.35</v>
+        <v>18449.03</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,26 +717,26 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>101181.23</v>
+        <v>68457.66</v>
       </c>
       <c r="M9" t="n">
-        <v>101181.23</v>
+        <v>68457.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>16532.42</v>
+        <v>17290.35</v>
       </c>
       <c r="I10" t="n">
-        <v>16532.42</v>
+        <v>17290.35</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>65931.12</v>
+        <v>101181.23</v>
       </c>
       <c r="M10" t="n">
-        <v>65931.12</v>
+        <v>101181.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="I11" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>53684.04</v>
+        <v>65931.12</v>
       </c>
       <c r="M11" t="n">
-        <v>53684.04</v>
+        <v>65931.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>15064.73</v>
+        <v>15302.69</v>
       </c>
       <c r="I12" t="n">
-        <v>15064.73</v>
+        <v>15302.69</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5220.9</v>
+        <v>53684.04</v>
       </c>
       <c r="M12" t="n">
-        <v>5220.9</v>
+        <v>53684.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>13506.29</v>
+        <v>15064.73</v>
       </c>
       <c r="I13" t="n">
-        <v>13506.29</v>
+        <v>15064.73</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5220.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5220.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>12093.46</v>
+        <v>13506.29</v>
       </c>
       <c r="I14" t="n">
-        <v>12093.46</v>
+        <v>13506.29</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>33442.54</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>33442.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>10530.97</v>
+        <v>12093.46</v>
       </c>
       <c r="I15" t="n">
-        <v>10530.97</v>
+        <v>12093.46</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>58297.52</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>69823.8</v>
+        <v>33442.54</v>
       </c>
       <c r="M15" t="n">
-        <v>128121.32</v>
+        <v>33442.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9886.120000000001</v>
+        <v>10530.97</v>
       </c>
       <c r="I16" t="n">
-        <v>9886.120000000001</v>
+        <v>10530.97</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>58297.52</v>
       </c>
       <c r="L16" t="n">
-        <v>18063.4</v>
+        <v>69823.8</v>
       </c>
       <c r="M16" t="n">
-        <v>18063.4</v>
+        <v>128121.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9749.9</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>9749.9</v>
+        <v>9886.120000000001</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>52726.89</v>
+        <v>18063.4</v>
       </c>
       <c r="M17" t="n">
-        <v>52726.89</v>
+        <v>18063.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8476.02</v>
+        <v>9749.9</v>
       </c>
       <c r="I18" t="n">
-        <v>8476.02</v>
+        <v>9749.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5756.97</v>
+        <v>52726.89</v>
       </c>
       <c r="M18" t="n">
-        <v>5756.97</v>
+        <v>52726.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8393.23</v>
+        <v>8476.02</v>
       </c>
       <c r="I19" t="n">
-        <v>8393.23</v>
+        <v>8476.02</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>291024.67</v>
+        <v>5756.97</v>
       </c>
       <c r="M19" t="n">
-        <v>291024.67</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="20">
@@ -1242,17 +1242,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6087.09</v>
+        <v>7004.2</v>
       </c>
       <c r="I22" t="n">
-        <v>6087.09</v>
+        <v>7004.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6398.05</v>
+        <v>1888.66</v>
       </c>
       <c r="M22" t="n">
-        <v>6398.05</v>
+        <v>1888.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6049.46</v>
+        <v>6087.09</v>
       </c>
       <c r="I23" t="n">
-        <v>6049.46</v>
+        <v>6087.09</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,69 +1319,69 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6398.05</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>6398.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>6086.13</v>
       </c>
       <c r="H24" t="n">
-        <v>5808.77</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5808.77</v>
+        <v>6086.13</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>114882.54</v>
       </c>
       <c r="L24" t="n">
-        <v>103783.01</v>
+        <v>66947.41</v>
       </c>
       <c r="M24" t="n">
-        <v>103783.01</v>
+        <v>181829.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>5025.06</v>
+        <v>6049.46</v>
       </c>
       <c r="I25" t="n">
-        <v>5025.06</v>
+        <v>6049.46</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,26 +1405,26 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>23315.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>23315.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4699.16</v>
+        <v>5808.77</v>
       </c>
       <c r="I26" t="n">
-        <v>4699.16</v>
+        <v>5808.77</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,26 +1448,26 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>4193.66</v>
+        <v>103783.01</v>
       </c>
       <c r="M26" t="n">
-        <v>4193.66</v>
+        <v>103783.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4266.5</v>
+        <v>5025.06</v>
       </c>
       <c r="I27" t="n">
-        <v>4266.5</v>
+        <v>5025.06</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>6572.15</v>
+        <v>23315.2</v>
       </c>
       <c r="M27" t="n">
-        <v>6572.15</v>
+        <v>23315.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2960.97</v>
+        <v>4266.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2960.97</v>
+        <v>4266.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>6572.15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6572.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,22 +1553,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="I29" t="n">
-        <v>2396.76</v>
+        <v>2960.97</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H30" t="n">
-        <v>2068.31</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2068.31</v>
+        <v>2396.76</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
       <c r="M30" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,93 +1639,93 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1454.68</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>509.43</v>
+        <v>2068.31</v>
       </c>
       <c r="I31" t="n">
-        <v>1964.11</v>
+        <v>2068.31</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>26239.01</v>
+        <v>18614.8</v>
       </c>
       <c r="M31" t="n">
-        <v>50616.76</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H32" t="n">
-        <v>1843.19</v>
+        <v>509.43</v>
       </c>
       <c r="I32" t="n">
-        <v>1843.19</v>
+        <v>1964.11</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1843.19</v>
+        <v>26239.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1843.19</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1777.67</v>
+        <v>1843.19</v>
       </c>
       <c r="I33" t="n">
-        <v>1777.67</v>
+        <v>1843.19</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,26 +1749,26 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>19069.49</v>
+        <v>1843.19</v>
       </c>
       <c r="M33" t="n">
-        <v>19069.49</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1627.21</v>
+        <v>1777.67</v>
       </c>
       <c r="I34" t="n">
-        <v>1627.21</v>
+        <v>1777.67</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>15800.91</v>
+        <v>19069.49</v>
       </c>
       <c r="M34" t="n">
-        <v>15800.91</v>
+        <v>19069.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1699.41</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1699.41</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3381.58</v>
+        <v>17392.81</v>
       </c>
       <c r="M35" t="n">
-        <v>3381.58</v>
+        <v>17392.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>19092.22</v>
+        <v>15800.91</v>
       </c>
       <c r="M36" t="n">
-        <v>19092.22</v>
+        <v>15800.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>12581.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>12581.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1958,22 +1958,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6086.13</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>66947.41</v>
+        <v>3381.58</v>
       </c>
       <c r="M38" t="n">
-        <v>73033.53999999999</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>90049.44</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>28799.65</v>
+        <v>12581.61</v>
       </c>
       <c r="M39" t="n">
-        <v>118849.09</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="L40" t="n">
-        <v>1425.78</v>
+        <v>28799.65</v>
       </c>
       <c r="M40" t="n">
-        <v>1425.78</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M41" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
       <c r="M42" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>130020.2</v>
+        <v>3208.07</v>
       </c>
       <c r="M44" t="n">
-        <v>135062.85</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2259,15 +2259,58 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L45" t="n">
+        <v>130020.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>135062.85</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>65046</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>6270.75</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M46" t="n">
         <v>6270.75</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>21 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -576,22 +576,22 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>52177.88</v>
+        <v>56135.2</v>
       </c>
       <c r="I6" t="n">
-        <v>52177.88</v>
+        <v>56135.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>84784.83</v>
       </c>
       <c r="L6" t="n">
-        <v>247240.02</v>
+        <v>243282.71</v>
       </c>
       <c r="M6" t="n">
-        <v>247240.02</v>
+        <v>328067.54</v>
       </c>
     </row>
     <row r="7">
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>65931.12</v>
+        <v>62070.69</v>
       </c>
       <c r="M11" t="n">
-        <v>65931.12</v>
+        <v>62070.69</v>
       </c>
     </row>
     <row r="12">
@@ -1543,17 +1543,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2960.97</v>
+        <v>3610.04</v>
       </c>
       <c r="I29" t="n">
-        <v>2960.97</v>
+        <v>3610.04</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>17237.12</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>17237.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1605,13 +1605,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2396.76</v>
+        <v>3052.25</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2396.76</v>
+        <v>3052.25</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>26364.37</v>
+        <v>33574.79</v>
       </c>
       <c r="M30" t="n">
-        <v>26364.37</v>
+        <v>33574.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2068.31</v>
+        <v>2960.97</v>
       </c>
       <c r="I31" t="n">
-        <v>2068.31</v>
+        <v>2960.97</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>18614.8</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>18614.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1691,41 +1691,41 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1454.68</v>
+        <v>2396.76</v>
       </c>
       <c r="H32" t="n">
-        <v>509.43</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1964.11</v>
+        <v>2396.76</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>26239.01</v>
+        <v>26364.37</v>
       </c>
       <c r="M32" t="n">
-        <v>50616.76</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1843.19</v>
+        <v>2068.31</v>
       </c>
       <c r="I33" t="n">
-        <v>1843.19</v>
+        <v>2068.31</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,69 +1749,69 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1843.19</v>
+        <v>18614.8</v>
       </c>
       <c r="M33" t="n">
-        <v>1843.19</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H34" t="n">
-        <v>1777.67</v>
+        <v>509.43</v>
       </c>
       <c r="I34" t="n">
-        <v>1777.67</v>
+        <v>1964.11</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>24377.75</v>
       </c>
       <c r="L34" t="n">
-        <v>19069.49</v>
+        <v>26239.01</v>
       </c>
       <c r="M34" t="n">
-        <v>19069.49</v>
+        <v>50616.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1699.41</v>
+        <v>1843.19</v>
       </c>
       <c r="I35" t="n">
-        <v>1699.41</v>
+        <v>1843.19</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>17392.81</v>
+        <v>1843.19</v>
       </c>
       <c r="M35" t="n">
-        <v>17392.81</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1627.21</v>
+        <v>1699.41</v>
       </c>
       <c r="I36" t="n">
-        <v>1627.21</v>
+        <v>1699.41</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>15800.91</v>
+        <v>17392.81</v>
       </c>
       <c r="M36" t="n">
-        <v>15800.91</v>
+        <v>17392.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1909,28 +1909,28 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1595.73</v>
+        <v>1627.21</v>
       </c>
       <c r="I37" t="n">
-        <v>1595.73</v>
+        <v>1627.21</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1958.21</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>37341.24</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>39299.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>12581.61</v>
+        <v>3381.58</v>
       </c>
       <c r="M39" t="n">
-        <v>12581.61</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>90049.44</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>28799.65</v>
+        <v>12581.61</v>
       </c>
       <c r="M40" t="n">
-        <v>118849.09</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2087,22 +2087,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="L41" t="n">
-        <v>1425.78</v>
+        <v>28799.65</v>
       </c>
       <c r="M41" t="n">
-        <v>1425.78</v>
+        <v>118849.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M42" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
       <c r="M43" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,16 +2222,16 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2259,22 +2259,22 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>130020.2</v>
+        <v>3208.07</v>
       </c>
       <c r="M45" t="n">
-        <v>135062.85</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2302,15 +2302,58 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L46" t="n">
+        <v>130020.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>135062.85</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>65046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>6270.75</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>6270.75</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>21 de agosto de 2026</t>
+          <t>25 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -499,19 +499,19 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>93618.86</v>
+        <v>72756.09</v>
       </c>
       <c r="L4" t="n">
         <v>80161.03</v>
       </c>
       <c r="M4" t="n">
-        <v>173779.89</v>
+        <v>152917.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,13 +530,13 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>31798.96</v>
+        <v>85004.67999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>37240.77</v>
+        <v>63882.48</v>
       </c>
       <c r="I5" t="n">
-        <v>69039.73</v>
+        <v>148887.16</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>28233.37</v>
+        <v>235535.47</v>
       </c>
       <c r="M5" t="n">
-        <v>28233.37</v>
+        <v>235535.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,40 +564,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>90049.44</v>
       </c>
       <c r="H6" t="n">
-        <v>56135.2</v>
+        <v>14399.82</v>
       </c>
       <c r="I6" t="n">
-        <v>56135.2</v>
+        <v>104449.26</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>84784.83</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>243282.71</v>
+        <v>14399.82</v>
       </c>
       <c r="M6" t="n">
-        <v>328067.54</v>
+        <v>14399.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>33305.7</v>
+        <v>31798.96</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>37240.77</v>
       </c>
       <c r="I7" t="n">
-        <v>33305.7</v>
+        <v>69039.73</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,26 +631,26 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>49020.81</v>
+        <v>28233.37</v>
       </c>
       <c r="M7" t="n">
-        <v>49020.81</v>
+        <v>28233.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -659,13 +659,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>18368.13</v>
+        <v>2211.03</v>
       </c>
       <c r="H8" t="n">
-        <v>1659.4</v>
+        <v>66617.46000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>20027.53</v>
+        <v>68828.49000000001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,26 +674,26 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>44104.27</v>
+        <v>69823.8</v>
       </c>
       <c r="M8" t="n">
-        <v>44104.27</v>
+        <v>69823.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -702,13 +702,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-19514.59</v>
+        <v>33305.7</v>
       </c>
       <c r="H9" t="n">
-        <v>37963.62</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>18449.03</v>
+        <v>33305.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>68457.66</v>
+        <v>49020.81</v>
       </c>
       <c r="M9" t="n">
-        <v>68457.66</v>
+        <v>49020.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,22 +736,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="H10" t="n">
-        <v>17290.35</v>
+        <v>1659.4</v>
       </c>
       <c r="I10" t="n">
-        <v>17290.35</v>
+        <v>20027.53</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -760,41 +760,41 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>101181.23</v>
+        <v>44104.27</v>
       </c>
       <c r="M10" t="n">
-        <v>101181.23</v>
+        <v>44104.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-19514.59</v>
       </c>
       <c r="H11" t="n">
-        <v>16532.42</v>
+        <v>37963.62</v>
       </c>
       <c r="I11" t="n">
-        <v>16532.42</v>
+        <v>18449.03</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,26 +803,26 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>62070.69</v>
+        <v>68457.66</v>
       </c>
       <c r="M11" t="n">
-        <v>62070.69</v>
+        <v>68457.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>15302.69</v>
+        <v>17363.6</v>
       </c>
       <c r="I12" t="n">
-        <v>15302.69</v>
+        <v>17363.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>53684.04</v>
+        <v>98929.74000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>53684.04</v>
+        <v>98929.74000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>15064.73</v>
+        <v>16956.37</v>
       </c>
       <c r="I13" t="n">
-        <v>15064.73</v>
+        <v>16956.37</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5220.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5220.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>13506.29</v>
+        <v>16532.42</v>
       </c>
       <c r="I14" t="n">
-        <v>13506.29</v>
+        <v>16532.42</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>38466.09</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>38466.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>12093.46</v>
+        <v>15302.69</v>
       </c>
       <c r="I15" t="n">
-        <v>12093.46</v>
+        <v>15302.69</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>33442.54</v>
+        <v>51962.79</v>
       </c>
       <c r="M15" t="n">
-        <v>33442.54</v>
+        <v>51962.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,22 +1006,22 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>10530.97</v>
+        <v>15064.73</v>
       </c>
       <c r="I16" t="n">
-        <v>10530.97</v>
+        <v>15064.73</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>58297.52</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>69823.8</v>
+        <v>5220.9</v>
       </c>
       <c r="M16" t="n">
-        <v>128121.32</v>
+        <v>5220.9</v>
       </c>
     </row>
     <row r="17">
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9886.120000000001</v>
+        <v>15040.89</v>
       </c>
       <c r="I17" t="n">
-        <v>9886.120000000001</v>
+        <v>15040.89</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>18063.4</v>
+        <v>13568.13</v>
       </c>
       <c r="M17" t="n">
-        <v>18063.4</v>
+        <v>13568.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9749.9</v>
+        <v>14560.31</v>
       </c>
       <c r="I18" t="n">
-        <v>9749.9</v>
+        <v>14560.31</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>52726.89</v>
+        <v>30975.68</v>
       </c>
       <c r="M18" t="n">
-        <v>52726.89</v>
+        <v>30975.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,40 +1123,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>12340.66</v>
       </c>
       <c r="H19" t="n">
-        <v>8476.02</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>8476.02</v>
+        <v>12340.66</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>5042.65</v>
       </c>
       <c r="L19" t="n">
-        <v>5756.97</v>
+        <v>142360.86</v>
       </c>
       <c r="M19" t="n">
-        <v>5756.97</v>
+        <v>147403.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7940.4</v>
+        <v>10596.4</v>
       </c>
       <c r="I20" t="n">
-        <v>7940.4</v>
+        <v>10596.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17698.48</v>
+        <v>89590.05</v>
       </c>
       <c r="M20" t="n">
-        <v>17698.48</v>
+        <v>89590.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>7590.14</v>
+        <v>9749.9</v>
       </c>
       <c r="I21" t="n">
-        <v>7590.14</v>
+        <v>9749.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>92596.31</v>
+        <v>52726.89</v>
       </c>
       <c r="M21" t="n">
-        <v>92596.31</v>
+        <v>52726.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7004.2</v>
+        <v>8476.02</v>
       </c>
       <c r="I22" t="n">
-        <v>7004.2</v>
+        <v>8476.02</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1888.66</v>
+        <v>5756.97</v>
       </c>
       <c r="M22" t="n">
-        <v>1888.66</v>
+        <v>5756.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6087.09</v>
+        <v>7940.4</v>
       </c>
       <c r="I23" t="n">
-        <v>6087.09</v>
+        <v>7940.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>6398.05</v>
+        <v>17698.48</v>
       </c>
       <c r="M23" t="n">
-        <v>6398.05</v>
+        <v>17698.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1338,50 +1338,50 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>6086.13</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>7004.2</v>
       </c>
       <c r="I24" t="n">
-        <v>6086.13</v>
+        <v>7004.2</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>114882.54</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>66947.41</v>
+        <v>1888.66</v>
       </c>
       <c r="M24" t="n">
-        <v>181829.95</v>
+        <v>1888.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6049.46</v>
+        <v>6813.99</v>
       </c>
       <c r="I25" t="n">
-        <v>6049.46</v>
+        <v>6813.99</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>21526.27</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>21526.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5808.77</v>
+        <v>6087.09</v>
       </c>
       <c r="I26" t="n">
-        <v>5808.77</v>
+        <v>6087.09</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,59 +1448,59 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>103783.01</v>
+        <v>6398.05</v>
       </c>
       <c r="M26" t="n">
-        <v>103783.01</v>
+        <v>6398.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6086.13</v>
       </c>
       <c r="H27" t="n">
-        <v>5025.06</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5025.06</v>
+        <v>6086.13</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>114882.54</v>
       </c>
       <c r="L27" t="n">
-        <v>23315.2</v>
+        <v>66947.41</v>
       </c>
       <c r="M27" t="n">
-        <v>23315.2</v>
+        <v>181829.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4266.5</v>
+        <v>6049.46</v>
       </c>
       <c r="I28" t="n">
-        <v>4266.5</v>
+        <v>6049.46</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6572.15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6572.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3610.04</v>
+        <v>5808.77</v>
       </c>
       <c r="I29" t="n">
-        <v>3610.04</v>
+        <v>5808.77</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,41 +1577,41 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>17237.12</v>
+        <v>103783.01</v>
       </c>
       <c r="M29" t="n">
-        <v>17237.12</v>
+        <v>103783.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3052.25</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4266.5</v>
       </c>
       <c r="I30" t="n">
-        <v>3052.25</v>
+        <v>4266.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>33574.79</v>
+        <v>6572.15</v>
       </c>
       <c r="M30" t="n">
-        <v>33574.79</v>
+        <v>6572.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2960.97</v>
+        <v>3610.04</v>
       </c>
       <c r="I31" t="n">
-        <v>2960.97</v>
+        <v>3610.04</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>17237.12</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>17237.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1691,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2396.76</v>
+        <v>1958.21</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I32" t="n">
-        <v>2396.76</v>
+        <v>3585.42</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,41 +1706,41 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>26364.37</v>
+        <v>37341.24</v>
       </c>
       <c r="M32" t="n">
-        <v>26364.37</v>
+        <v>37341.24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3052.25</v>
       </c>
       <c r="H33" t="n">
-        <v>2068.31</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2068.31</v>
+        <v>3052.25</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>18614.8</v>
+        <v>33574.79</v>
       </c>
       <c r="M33" t="n">
-        <v>18614.8</v>
+        <v>33574.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1768,65 +1768,65 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1454.68</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>509.43</v>
+        <v>2960.97</v>
       </c>
       <c r="I34" t="n">
-        <v>1964.11</v>
+        <v>2960.97</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>24377.75</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>26239.01</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>50616.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H35" t="n">
-        <v>1843.19</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1843.19</v>
+        <v>2396.76</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
       <c r="M35" t="n">
-        <v>1843.19</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1699.41</v>
+        <v>2068.31</v>
       </c>
       <c r="I36" t="n">
-        <v>1699.41</v>
+        <v>2068.31</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>17392.81</v>
+        <v>18614.8</v>
       </c>
       <c r="M36" t="n">
-        <v>17392.81</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,50 +1897,50 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H37" t="n">
-        <v>1627.21</v>
+        <v>509.43</v>
       </c>
       <c r="I37" t="n">
-        <v>1627.21</v>
+        <v>1964.11</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1958.21</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>37341.24</v>
+        <v>26239.01</v>
       </c>
       <c r="M37" t="n">
-        <v>39299.45</v>
+        <v>26239.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1595.73</v>
+        <v>1843.19</v>
       </c>
       <c r="I38" t="n">
-        <v>1595.73</v>
+        <v>1843.19</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1843.19</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1843.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1699.41</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1699.41</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3381.58</v>
+        <v>17392.81</v>
       </c>
       <c r="M39" t="n">
-        <v>3381.58</v>
+        <v>17392.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>12581.61</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>12581.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2087,22 +2087,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>90049.44</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>28799.65</v>
+        <v>3381.58</v>
       </c>
       <c r="M41" t="n">
-        <v>118849.09</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1425.78</v>
+        <v>12581.61</v>
       </c>
       <c r="M42" t="n">
-        <v>1425.78</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M43" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,16 +2222,16 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
       <c r="M44" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2265,16 +2265,16 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
       <c r="M45" t="n">
-        <v>3208.07</v>
+        <v>24095.39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>130020.2</v>
+        <v>3208.07</v>
       </c>
       <c r="M46" t="n">
-        <v>135062.85</v>
+        <v>3208.07</v>
       </c>
     </row>
     <row r="47">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>25 de agosto de 2026</t>
+          <t>27 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>162964</v>
       </c>
       <c r="H4" t="n">
-        <v>8374.200000000001</v>
+        <v>9770.84</v>
       </c>
       <c r="I4" t="n">
-        <v>171338.2</v>
+        <v>172734.84</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -533,10 +533,10 @@
         <v>85004.67999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>63882.48</v>
+        <v>77510.67</v>
       </c>
       <c r="I5" t="n">
-        <v>148887.16</v>
+        <v>162515.35</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>235535.47</v>
+        <v>228558.77</v>
       </c>
       <c r="M5" t="n">
-        <v>235535.47</v>
+        <v>228558.77</v>
       </c>
     </row>
     <row r="6">
@@ -726,17 +726,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -745,31 +745,31 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>18368.13</v>
+        <v>12340.66</v>
       </c>
       <c r="H10" t="n">
-        <v>1659.4</v>
+        <v>10127.69</v>
       </c>
       <c r="I10" t="n">
-        <v>20027.53</v>
+        <v>22468.35</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7957.05</v>
       </c>
       <c r="L10" t="n">
-        <v>44104.27</v>
+        <v>135596.86</v>
       </c>
       <c r="M10" t="n">
-        <v>44104.27</v>
+        <v>143553.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,22 +779,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-19514.59</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>37963.62</v>
+        <v>21851.98</v>
       </c>
       <c r="I11" t="n">
-        <v>18449.03</v>
+        <v>21851.98</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>68457.66</v>
+        <v>96692.85000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>68457.66</v>
+        <v>96692.85000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,22 +822,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>18368.13</v>
       </c>
       <c r="H12" t="n">
-        <v>17363.6</v>
+        <v>1659.4</v>
       </c>
       <c r="I12" t="n">
-        <v>17363.6</v>
+        <v>20027.53</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,59 +846,59 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>98929.74000000001</v>
+        <v>44104.27</v>
       </c>
       <c r="M12" t="n">
-        <v>98929.74000000001</v>
+        <v>44104.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-19514.59</v>
       </c>
       <c r="H13" t="n">
-        <v>16956.37</v>
+        <v>37963.62</v>
       </c>
       <c r="I13" t="n">
-        <v>16956.37</v>
+        <v>18449.03</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2308.82</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>93854.71000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>96163.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>16532.42</v>
+        <v>16956.37</v>
       </c>
       <c r="I14" t="n">
-        <v>16532.42</v>
+        <v>16956.37</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>38466.09</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>38466.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="I15" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>51962.79</v>
+        <v>38466.09</v>
       </c>
       <c r="M15" t="n">
-        <v>51962.79</v>
+        <v>38466.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>15064.73</v>
+        <v>15302.69</v>
       </c>
       <c r="I16" t="n">
-        <v>15064.73</v>
+        <v>15302.69</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5220.9</v>
+        <v>51962.79</v>
       </c>
       <c r="M16" t="n">
-        <v>5220.9</v>
+        <v>51962.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>15040.89</v>
+        <v>15064.73</v>
       </c>
       <c r="I17" t="n">
-        <v>15040.89</v>
+        <v>15064.73</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>13568.13</v>
+        <v>5220.9</v>
       </c>
       <c r="M17" t="n">
-        <v>13568.13</v>
+        <v>5220.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>14560.31</v>
+        <v>15040.89</v>
       </c>
       <c r="I18" t="n">
-        <v>14560.31</v>
+        <v>15040.89</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>30975.68</v>
+        <v>13568.13</v>
       </c>
       <c r="M18" t="n">
-        <v>30975.68</v>
+        <v>13568.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,34 +1123,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>12340.66</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14560.31</v>
       </c>
       <c r="I19" t="n">
-        <v>12340.66</v>
+        <v>14560.31</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5042.65</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>142360.86</v>
+        <v>30975.68</v>
       </c>
       <c r="M19" t="n">
-        <v>147403.51</v>
+        <v>30975.68</v>
       </c>
     </row>
     <row r="20">
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>10596.4</v>
+        <v>12649.59</v>
       </c>
       <c r="I20" t="n">
-        <v>10596.4</v>
+        <v>12649.59</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>89590.05</v>
+        <v>87536.87</v>
       </c>
       <c r="M20" t="n">
-        <v>89590.05</v>
+        <v>87536.87</v>
       </c>
     </row>
     <row r="21">
@@ -1399,16 +1399,16 @@
         <v>6813.99</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>38963.3</v>
       </c>
       <c r="L25" t="n">
         <v>21526.27</v>
       </c>
       <c r="M25" t="n">
-        <v>21526.27</v>
+        <v>60489.57</v>
       </c>
     </row>
     <row r="26">
@@ -1629,17 +1629,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3610.04</v>
+        <v>3686.38</v>
       </c>
       <c r="I31" t="n">
-        <v>3610.04</v>
+        <v>3686.38</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,41 +1663,41 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>17237.12</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>17237.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1958.21</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1627.21</v>
+        <v>3610.04</v>
       </c>
       <c r="I32" t="n">
-        <v>3585.42</v>
+        <v>3610.04</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>37341.24</v>
+        <v>17237.12</v>
       </c>
       <c r="M32" t="n">
-        <v>37341.24</v>
+        <v>17237.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1734,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3052.25</v>
+        <v>1958.21</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1627.21</v>
       </c>
       <c r="I33" t="n">
-        <v>3052.25</v>
+        <v>3585.42</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,41 +1749,41 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>33574.79</v>
+        <v>37341.24</v>
       </c>
       <c r="M33" t="n">
-        <v>33574.79</v>
+        <v>37341.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3052.25</v>
       </c>
       <c r="H34" t="n">
-        <v>2960.97</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2960.97</v>
+        <v>3052.25</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>33574.79</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>33574.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2960.97</v>
       </c>
       <c r="I35" t="n">
-        <v>2396.76</v>
+        <v>2960.97</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>26364.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H36" t="n">
-        <v>2068.31</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2068.31</v>
+        <v>2396.76</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
       <c r="M36" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1454.68</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>509.43</v>
+        <v>2068.31</v>
       </c>
       <c r="I37" t="n">
-        <v>1964.11</v>
+        <v>2068.31</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,41 +1921,41 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>26239.01</v>
+        <v>18614.8</v>
       </c>
       <c r="M37" t="n">
-        <v>26239.01</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H38" t="n">
-        <v>1843.19</v>
+        <v>509.43</v>
       </c>
       <c r="I38" t="n">
-        <v>1843.19</v>
+        <v>1964.11</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1843.19</v>
+        <v>26239.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1843.19</v>
+        <v>26239.01</v>
       </c>
     </row>
     <row r="39">

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>28 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -619,10 +619,10 @@
         <v>31798.96</v>
       </c>
       <c r="H7" t="n">
-        <v>37240.77</v>
+        <v>49011.06</v>
       </c>
       <c r="I7" t="n">
-        <v>69039.73</v>
+        <v>80810.02</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>28233.37</v>
+        <v>16463.08</v>
       </c>
       <c r="M7" t="n">
-        <v>28233.37</v>
+        <v>16463.08</v>
       </c>
     </row>
     <row r="8">
@@ -662,10 +662,10 @@
         <v>2211.03</v>
       </c>
       <c r="H8" t="n">
-        <v>66617.46000000001</v>
+        <v>72024.35000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>68828.49000000001</v>
+        <v>74235.38</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>69823.8</v>
+        <v>64416.9</v>
       </c>
       <c r="M8" t="n">
-        <v>69823.8</v>
+        <v>64416.9</v>
       </c>
     </row>
     <row r="9">
@@ -941,7 +941,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>16532.42</v>
+        <v>16805.03</v>
       </c>
       <c r="I15" t="n">
-        <v>16532.42</v>
+        <v>16805.03</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>38466.09</v>
+        <v>3480.6</v>
       </c>
       <c r="M15" t="n">
-        <v>38466.09</v>
+        <v>3480.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="I16" t="n">
-        <v>15302.69</v>
+        <v>16532.42</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>51962.79</v>
+        <v>38466.09</v>
       </c>
       <c r="M16" t="n">
-        <v>51962.79</v>
+        <v>38466.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>15064.73</v>
+        <v>16294.28</v>
       </c>
       <c r="I17" t="n">
-        <v>15064.73</v>
+        <v>16294.28</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5220.9</v>
+        <v>29241.71</v>
       </c>
       <c r="M17" t="n">
-        <v>5220.9</v>
+        <v>29241.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>15040.89</v>
+        <v>15302.69</v>
       </c>
       <c r="I18" t="n">
-        <v>15040.89</v>
+        <v>15302.69</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>13568.13</v>
+        <v>51962.79</v>
       </c>
       <c r="M18" t="n">
-        <v>13568.13</v>
+        <v>51962.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>14560.31</v>
+        <v>15040.89</v>
       </c>
       <c r="I19" t="n">
-        <v>14560.31</v>
+        <v>15040.89</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>30975.68</v>
+        <v>13568.13</v>
       </c>
       <c r="M19" t="n">
-        <v>30975.68</v>
+        <v>13568.13</v>
       </c>
     </row>
     <row r="20">
@@ -1586,7 +1586,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1958.21</v>
       </c>
       <c r="H30" t="n">
-        <v>4266.5</v>
+        <v>3564.58</v>
       </c>
       <c r="I30" t="n">
-        <v>4266.5</v>
+        <v>5522.79</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>6572.15</v>
+        <v>35403.87</v>
       </c>
       <c r="M30" t="n">
-        <v>6572.15</v>
+        <v>35403.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3686.38</v>
+        <v>4266.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3686.38</v>
+        <v>4266.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,26 +1663,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>6572.15</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>6572.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3610.04</v>
+        <v>3686.38</v>
       </c>
       <c r="I32" t="n">
-        <v>3610.04</v>
+        <v>3686.38</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,41 +1706,41 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>17237.12</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>17237.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1958.21</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1627.21</v>
+        <v>3610.04</v>
       </c>
       <c r="I33" t="n">
-        <v>3585.42</v>
+        <v>3610.04</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>37341.24</v>
+        <v>17237.12</v>
       </c>
       <c r="M33" t="n">
-        <v>37341.24</v>
+        <v>17237.12</v>
       </c>
     </row>
     <row r="34">
@@ -1786,16 +1786,16 @@
         <v>3052.25</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1739.6</v>
       </c>
       <c r="L34" t="n">
-        <v>33574.79</v>
+        <v>52710.36</v>
       </c>
       <c r="M34" t="n">
-        <v>33574.79</v>
+        <v>54449.96</v>
       </c>
     </row>
     <row r="35">
@@ -1844,7 +1844,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2396.76</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2475.99</v>
       </c>
       <c r="I36" t="n">
-        <v>2396.76</v>
+        <v>2475.99</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>26364.37</v>
+        <v>21619.43</v>
       </c>
       <c r="M36" t="n">
-        <v>26364.37</v>
+        <v>21619.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2396.76</v>
       </c>
       <c r="H37" t="n">
-        <v>2068.31</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2068.31</v>
+        <v>2396.76</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
       <c r="M37" t="n">
-        <v>18614.8</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,22 +1940,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1454.68</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>509.43</v>
+        <v>2068.31</v>
       </c>
       <c r="I38" t="n">
-        <v>1964.11</v>
+        <v>2068.31</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>26239.01</v>
+        <v>18614.8</v>
       </c>
       <c r="M38" t="n">
-        <v>26239.01</v>
+        <v>18614.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,22 +1983,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1454.68</v>
       </c>
       <c r="H39" t="n">
-        <v>1699.41</v>
+        <v>509.43</v>
       </c>
       <c r="I39" t="n">
-        <v>1699.41</v>
+        <v>1964.11</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17392.81</v>
+        <v>26239.01</v>
       </c>
       <c r="M39" t="n">
-        <v>17392.81</v>
+        <v>26239.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1595.73</v>
+        <v>1699.41</v>
       </c>
       <c r="I40" t="n">
-        <v>1595.73</v>
+        <v>1699.41</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>17392.81</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>17392.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1595.73</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>12581.61</v>
+        <v>3381.58</v>
       </c>
       <c r="M42" t="n">
-        <v>12581.61</v>
+        <v>3381.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2179,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1425.78</v>
+        <v>12581.61</v>
       </c>
       <c r="M43" t="n">
-        <v>1425.78</v>
+        <v>12581.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2222,16 +2222,16 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
       <c r="M44" t="n">
-        <v>3035.72</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2265,16 +2265,16 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
       <c r="M45" t="n">
-        <v>24095.39</v>
+        <v>3035.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SAMUEL NUÐO RIVERA</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2308,52 +2308,9 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3208.07</v>
+        <v>6270.75</v>
       </c>
       <c r="M46" t="n">
-        <v>3208.07</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>65046</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>6270.75</v>
-      </c>
-      <c r="M47" t="n">
         <v>6270.75</v>
       </c>
     </row>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>28 de agosto de 2026</t>
+          <t>31 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -487,25 +487,25 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>162964</v>
+        <v>163272.44</v>
       </c>
       <c r="H4" t="n">
-        <v>9770.84</v>
+        <v>9789.33</v>
       </c>
       <c r="I4" t="n">
-        <v>172734.84</v>
+        <v>173061.77</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>72756.09</v>
+        <v>72893.8</v>
       </c>
       <c r="L4" t="n">
-        <v>80161.03</v>
+        <v>80312.75</v>
       </c>
       <c r="M4" t="n">
-        <v>152917.12</v>
+        <v>153206.55</v>
       </c>
     </row>
     <row r="5">
@@ -530,13 +530,13 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>85004.67999999999</v>
+        <v>83421.06</v>
       </c>
       <c r="H5" t="n">
-        <v>77510.67</v>
+        <v>76661.97</v>
       </c>
       <c r="I5" t="n">
-        <v>162515.35</v>
+        <v>160083.03</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>228558.77</v>
+        <v>228605.9</v>
       </c>
       <c r="M5" t="n">
-        <v>228558.77</v>
+        <v>228605.9</v>
       </c>
     </row>
     <row r="6">
@@ -573,13 +573,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>90049.44</v>
+        <v>90219.87</v>
       </c>
       <c r="H6" t="n">
-        <v>14399.82</v>
+        <v>14427.08</v>
       </c>
       <c r="I6" t="n">
-        <v>104449.26</v>
+        <v>104646.95</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14399.82</v>
+        <v>14427.08</v>
       </c>
       <c r="M6" t="n">
-        <v>14399.82</v>
+        <v>14427.08</v>
       </c>
     </row>
     <row r="7">
@@ -616,13 +616,13 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>31798.96</v>
+        <v>31859.15</v>
       </c>
       <c r="H7" t="n">
-        <v>49011.06</v>
+        <v>49103.83</v>
       </c>
       <c r="I7" t="n">
-        <v>80810.02</v>
+        <v>80962.98</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16463.08</v>
+        <v>16494.24</v>
       </c>
       <c r="M7" t="n">
-        <v>16463.08</v>
+        <v>16494.24</v>
       </c>
     </row>
     <row r="8">
@@ -659,13 +659,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2211.03</v>
+        <v>2215.22</v>
       </c>
       <c r="H8" t="n">
-        <v>72024.35000000001</v>
+        <v>72160.67</v>
       </c>
       <c r="I8" t="n">
-        <v>74235.38</v>
+        <v>74375.89</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>64416.9</v>
+        <v>64538.83</v>
       </c>
       <c r="M8" t="n">
-        <v>64416.9</v>
+        <v>64538.83</v>
       </c>
     </row>
     <row r="9">
@@ -702,13 +702,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>33305.7</v>
+        <v>33368.74</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33305.7</v>
+        <v>33368.74</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49020.81</v>
+        <v>49113.6</v>
       </c>
       <c r="M9" t="n">
-        <v>49020.81</v>
+        <v>49113.6</v>
       </c>
     </row>
     <row r="10">
@@ -742,34 +742,34 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14025.77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14138.01</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28163.78</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>12340.66</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10127.69</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22468.35</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
       <c r="K10" t="n">
-        <v>7957.05</v>
+        <v>5052.2</v>
       </c>
       <c r="L10" t="n">
-        <v>135596.86</v>
+        <v>132563.5</v>
       </c>
       <c r="M10" t="n">
-        <v>143553.91</v>
+        <v>137615.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,22 +779,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-17238.33</v>
       </c>
       <c r="H11" t="n">
-        <v>21851.98</v>
+        <v>42122.13</v>
       </c>
       <c r="I11" t="n">
-        <v>21851.98</v>
+        <v>24883.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,41 +803,41 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>96692.85000000001</v>
+        <v>89945.69</v>
       </c>
       <c r="M11" t="n">
-        <v>96692.85000000001</v>
+        <v>89945.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>18368.13</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1659.4</v>
+        <v>22403.65</v>
       </c>
       <c r="I12" t="n">
-        <v>20027.53</v>
+        <v>22403.65</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>44104.27</v>
+        <v>10604.95</v>
       </c>
       <c r="M12" t="n">
-        <v>44104.27</v>
+        <v>10604.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,65 +865,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-19514.59</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>37963.62</v>
+        <v>21893.33</v>
       </c>
       <c r="I13" t="n">
-        <v>18449.03</v>
+        <v>21893.33</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2308.82</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>93854.71000000001</v>
+        <v>97042.89</v>
       </c>
       <c r="M13" t="n">
-        <v>96163.53</v>
+        <v>97042.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>18402.9</v>
       </c>
       <c r="H14" t="n">
-        <v>16956.37</v>
+        <v>3446.05</v>
       </c>
       <c r="I14" t="n">
-        <v>16956.37</v>
+        <v>21848.95</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>42404.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>42404.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>16805.03</v>
+        <v>16988.45</v>
       </c>
       <c r="I15" t="n">
-        <v>16805.03</v>
+        <v>16988.45</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3480.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3480.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>16532.42</v>
+        <v>16904.67</v>
       </c>
       <c r="I16" t="n">
-        <v>16532.42</v>
+        <v>16904.67</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>38466.09</v>
+        <v>50488.12</v>
       </c>
       <c r="M16" t="n">
-        <v>38466.09</v>
+        <v>50488.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>16294.28</v>
+        <v>16836.83</v>
       </c>
       <c r="I17" t="n">
-        <v>16294.28</v>
+        <v>16836.83</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>29241.71</v>
+        <v>3487.19</v>
       </c>
       <c r="M17" t="n">
-        <v>29241.71</v>
+        <v>3487.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>15302.69</v>
+        <v>16326.83</v>
       </c>
       <c r="I18" t="n">
-        <v>15302.69</v>
+        <v>16326.83</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>51962.79</v>
+        <v>38302.03</v>
       </c>
       <c r="M18" t="n">
-        <v>51962.79</v>
+        <v>38302.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>15040.89</v>
+        <v>16325.12</v>
       </c>
       <c r="I19" t="n">
-        <v>15040.89</v>
+        <v>16325.12</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>13568.13</v>
+        <v>29297.06</v>
       </c>
       <c r="M19" t="n">
-        <v>13568.13</v>
+        <v>29297.06</v>
       </c>
     </row>
     <row r="20">
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12649.59</v>
+        <v>12673.52</v>
       </c>
       <c r="I20" t="n">
-        <v>12649.59</v>
+        <v>12673.52</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>87536.87</v>
+        <v>87702.55</v>
       </c>
       <c r="M20" t="n">
-        <v>87536.87</v>
+        <v>87702.55</v>
       </c>
     </row>
     <row r="21">
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9749.9</v>
+        <v>9768.370000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>9749.9</v>
+        <v>9768.370000000001</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>52726.89</v>
+        <v>52826.69</v>
       </c>
       <c r="M21" t="n">
-        <v>52726.89</v>
+        <v>52826.69</v>
       </c>
     </row>
     <row r="22">
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8476.02</v>
+        <v>8492.07</v>
       </c>
       <c r="I22" t="n">
-        <v>8476.02</v>
+        <v>8492.07</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5756.97</v>
+        <v>5767.87</v>
       </c>
       <c r="M22" t="n">
-        <v>5756.97</v>
+        <v>5767.87</v>
       </c>
     </row>
     <row r="23">
@@ -1307,10 +1307,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>7940.4</v>
+        <v>7955.43</v>
       </c>
       <c r="I23" t="n">
-        <v>7940.4</v>
+        <v>7955.43</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>17698.48</v>
+        <v>17731.98</v>
       </c>
       <c r="M23" t="n">
-        <v>17698.48</v>
+        <v>17731.98</v>
       </c>
     </row>
     <row r="24">
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>7004.2</v>
+        <v>7017.46</v>
       </c>
       <c r="I24" t="n">
-        <v>7004.2</v>
+        <v>7017.46</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1888.66</v>
+        <v>1892.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1888.66</v>
+        <v>1892.23</v>
       </c>
     </row>
     <row r="25">
@@ -1393,22 +1393,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6813.99</v>
+        <v>6826.89</v>
       </c>
       <c r="I25" t="n">
-        <v>6813.99</v>
+        <v>6826.89</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>38963.3</v>
+        <v>39037.05</v>
       </c>
       <c r="L25" t="n">
-        <v>21526.27</v>
+        <v>21567.01</v>
       </c>
       <c r="M25" t="n">
-        <v>60489.57</v>
+        <v>60604.06</v>
       </c>
     </row>
     <row r="26">
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6087.09</v>
+        <v>6098.62</v>
       </c>
       <c r="I26" t="n">
-        <v>6087.09</v>
+        <v>6098.62</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6398.05</v>
+        <v>6410.16</v>
       </c>
       <c r="M26" t="n">
-        <v>6398.05</v>
+        <v>6410.16</v>
       </c>
     </row>
     <row r="27">
@@ -1476,25 +1476,25 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>6086.13</v>
+        <v>6097.65</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>6086.13</v>
+        <v>6097.65</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>114882.54</v>
+        <v>115099.97</v>
       </c>
       <c r="L27" t="n">
-        <v>66947.41</v>
+        <v>67074.12</v>
       </c>
       <c r="M27" t="n">
-        <v>181829.95</v>
+        <v>182174.09</v>
       </c>
     </row>
     <row r="28">
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6049.46</v>
+        <v>6060.91</v>
       </c>
       <c r="I28" t="n">
-        <v>6049.46</v>
+        <v>6060.91</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5808.77</v>
+        <v>5819.76</v>
       </c>
       <c r="I29" t="n">
-        <v>5808.77</v>
+        <v>5819.76</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>103783.01</v>
+        <v>103979.43</v>
       </c>
       <c r="M29" t="n">
-        <v>103783.01</v>
+        <v>103979.43</v>
       </c>
     </row>
     <row r="30">
@@ -1605,13 +1605,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1958.21</v>
+        <v>1961.92</v>
       </c>
       <c r="H30" t="n">
-        <v>3564.58</v>
+        <v>3571.33</v>
       </c>
       <c r="I30" t="n">
-        <v>5522.79</v>
+        <v>5533.25</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,26 +1620,26 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>35403.87</v>
+        <v>35470.88</v>
       </c>
       <c r="M30" t="n">
-        <v>35403.87</v>
+        <v>35470.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>116060</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4266.5</v>
+        <v>5319.15</v>
       </c>
       <c r="I31" t="n">
-        <v>4266.5</v>
+        <v>5319.15</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,41 +1663,41 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6572.15</v>
+        <v>15937.48</v>
       </c>
       <c r="M31" t="n">
-        <v>6572.15</v>
+        <v>15937.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4800.92</v>
       </c>
       <c r="H32" t="n">
-        <v>3686.38</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3686.38</v>
+        <v>4800.92</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,26 +1706,26 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>52810.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>52810.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3610.04</v>
+        <v>4274.58</v>
       </c>
       <c r="I33" t="n">
-        <v>3610.04</v>
+        <v>4274.58</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,59 +1749,59 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>17237.12</v>
+        <v>6584.58</v>
       </c>
       <c r="M33" t="n">
-        <v>17237.12</v>
+        <v>6584.58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3052.25</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3693.35</v>
       </c>
       <c r="I34" t="n">
-        <v>3052.25</v>
+        <v>3693.35</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1739.6</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>52710.36</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>54449.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2960.97</v>
+        <v>3521.42</v>
       </c>
       <c r="I35" t="n">
-        <v>2960.97</v>
+        <v>3521.42</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>20619.61</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>20619.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2475.99</v>
+        <v>2966.58</v>
       </c>
       <c r="I36" t="n">
-        <v>2475.99</v>
+        <v>2966.58</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>21619.43</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>21619.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1906,13 +1906,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>2396.76</v>
+        <v>2401.3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2396.76</v>
+        <v>2401.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>26364.37</v>
+        <v>26414.27</v>
       </c>
       <c r="M37" t="n">
-        <v>26364.37</v>
+        <v>26414.27</v>
       </c>
     </row>
     <row r="38">
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2068.31</v>
+        <v>2072.23</v>
       </c>
       <c r="I38" t="n">
-        <v>2068.31</v>
+        <v>2072.23</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>18614.8</v>
+        <v>18650.03</v>
       </c>
       <c r="M38" t="n">
-        <v>18614.8</v>
+        <v>18650.03</v>
       </c>
     </row>
     <row r="39">
@@ -1992,13 +1992,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1454.68</v>
+        <v>1457.43</v>
       </c>
       <c r="H39" t="n">
-        <v>509.43</v>
+        <v>510.39</v>
       </c>
       <c r="I39" t="n">
-        <v>1964.11</v>
+        <v>1967.82</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>26239.01</v>
+        <v>26288.67</v>
       </c>
       <c r="M39" t="n">
-        <v>26239.01</v>
+        <v>26288.67</v>
       </c>
     </row>
     <row r="40">
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1699.41</v>
+        <v>1702.63</v>
       </c>
       <c r="I40" t="n">
-        <v>1699.41</v>
+        <v>1702.63</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17392.81</v>
+        <v>17425.73</v>
       </c>
       <c r="M40" t="n">
-        <v>17392.81</v>
+        <v>17425.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1595.73</v>
+        <v>1693.99</v>
       </c>
       <c r="I41" t="n">
-        <v>1595.73</v>
+        <v>1693.99</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1693.99</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1693.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1598.75</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1598.75</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3381.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1040.74</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1040.74</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>12581.61</v>
+        <v>5241.88</v>
       </c>
       <c r="M43" t="n">
-        <v>12581.61</v>
+        <v>5241.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2488.17</v>
       </c>
       <c r="L44" t="n">
-        <v>1425.78</v>
+        <v>27369.85</v>
       </c>
       <c r="M44" t="n">
-        <v>1425.78</v>
+        <v>29858.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2265,16 +2265,16 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>3035.72</v>
+        <v>12605.42</v>
       </c>
       <c r="M45" t="n">
-        <v>3035.72</v>
+        <v>12605.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2308,10 +2308,53 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>6270.75</v>
+        <v>1428.48</v>
       </c>
       <c r="M46" t="n">
-        <v>6270.75</v>
+        <v>1428.48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>108405</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3041.47</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3041.47</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>31 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,75 +468,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>115047</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DESIREE DE LA PEÐA OROZCO</t>
+          <t>VELIA PATRICIA BERNAL RAMOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>163272.44</v>
+        <v>39037.05</v>
       </c>
       <c r="H4" t="n">
-        <v>9789.33</v>
+        <v>1821.92</v>
       </c>
       <c r="I4" t="n">
-        <v>173061.77</v>
+        <v>40858.97</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>72893.8</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>80312.75</v>
+        <v>24779.71</v>
       </c>
       <c r="M4" t="n">
-        <v>153206.55</v>
+        <v>24779.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>83421.06</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>76661.97</v>
+        <v>13505.41</v>
       </c>
       <c r="I5" t="n">
-        <v>160083.03</v>
+        <v>13505.41</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>228605.9</v>
+        <v>94372.73</v>
       </c>
       <c r="M5" t="n">
-        <v>228605.9</v>
+        <v>94372.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JOSE RENE DE ALBA MORALES</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>90219.87</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>14427.08</v>
+        <v>10023.33</v>
       </c>
       <c r="I6" t="n">
-        <v>104646.95</v>
+        <v>10023.33</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,41 +588,41 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14427.08</v>
+        <v>65066.43</v>
       </c>
       <c r="M6" t="n">
-        <v>14427.08</v>
+        <v>65066.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>31859.15</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>49103.83</v>
+        <v>9440.07</v>
       </c>
       <c r="I7" t="n">
-        <v>80962.98</v>
+        <v>9440.07</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16494.24</v>
+        <v>89858.53999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>16494.24</v>
+        <v>89858.53999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2215.22</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>72160.67</v>
+        <v>8492.07</v>
       </c>
       <c r="I8" t="n">
-        <v>74375.89</v>
+        <v>8492.07</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>64538.83</v>
+        <v>3845.25</v>
       </c>
       <c r="M8" t="n">
-        <v>64538.83</v>
+        <v>3845.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>33368.74</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7409.62</v>
       </c>
       <c r="I9" t="n">
-        <v>33368.74</v>
+        <v>7409.62</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49113.6</v>
+        <v>235826.63</v>
       </c>
       <c r="M9" t="n">
-        <v>49113.6</v>
+        <v>235826.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,65 +736,65 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DARINKA UREÐA CASILLAS</t>
+          <t>MARICELA ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>14025.77</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>14138.01</v>
+        <v>5431.4</v>
       </c>
       <c r="I10" t="n">
-        <v>28163.78</v>
+        <v>5431.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5052.2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>132563.5</v>
+        <v>12899.71</v>
       </c>
       <c r="M10" t="n">
-        <v>137615.7</v>
+        <v>12899.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>ROGELIO TORRES ORTIZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-17238.33</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>42122.13</v>
+        <v>5152.9</v>
       </c>
       <c r="I11" t="n">
-        <v>24883.8</v>
+        <v>5152.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>89945.69</v>
+        <v>29490.48</v>
       </c>
       <c r="M11" t="n">
-        <v>89945.69</v>
+        <v>29490.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARICELA ARREOLA LOPEZ</t>
+          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>22403.65</v>
+        <v>5090.96</v>
       </c>
       <c r="I12" t="n">
-        <v>22403.65</v>
+        <v>5090.96</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -846,26 +846,26 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10604.95</v>
+        <v>48657.15</v>
       </c>
       <c r="M12" t="n">
-        <v>10604.95</v>
+        <v>48657.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MARIA TERESA ASENCIO LOZANO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>21893.33</v>
+        <v>4709.73</v>
       </c>
       <c r="I13" t="n">
-        <v>21893.33</v>
+        <v>4709.73</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -889,41 +889,41 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>97042.89</v>
+        <v>2309.36</v>
       </c>
       <c r="M13" t="n">
-        <v>97042.89</v>
+        <v>2309.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>18402.9</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3446.05</v>
+        <v>4021.19</v>
       </c>
       <c r="I14" t="n">
-        <v>21848.95</v>
+        <v>4021.19</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>42404.25</v>
+        <v>31449.72</v>
       </c>
       <c r="M14" t="n">
-        <v>42404.25</v>
+        <v>31449.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>16988.45</v>
+        <v>2966.58</v>
       </c>
       <c r="I15" t="n">
-        <v>16988.45</v>
+        <v>2966.58</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>16904.67</v>
+        <v>2426.76</v>
       </c>
       <c r="I16" t="n">
-        <v>16904.67</v>
+        <v>2426.76</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>50488.12</v>
+        <v>38711.19</v>
       </c>
       <c r="M16" t="n">
-        <v>50488.12</v>
+        <v>38711.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANA VERONICA GONZALEZ GAYTAN</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>16836.83</v>
+        <v>2408.61</v>
       </c>
       <c r="I17" t="n">
-        <v>16836.83</v>
+        <v>2408.61</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3487.19</v>
+        <v>5453.73</v>
       </c>
       <c r="M17" t="n">
-        <v>3487.19</v>
+        <v>5453.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>16326.83</v>
+        <v>1800.77</v>
       </c>
       <c r="I18" t="n">
-        <v>16326.83</v>
+        <v>1800.77</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>38302.03</v>
+        <v>10804.65</v>
       </c>
       <c r="M18" t="n">
-        <v>38302.03</v>
+        <v>10804.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROGELIO TORRES ORTIZ</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>16325.12</v>
+        <v>1761.04</v>
       </c>
       <c r="I19" t="n">
-        <v>16325.12</v>
+        <v>1761.04</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>29297.06</v>
+        <v>7337.05</v>
       </c>
       <c r="M19" t="n">
-        <v>29297.06</v>
+        <v>7337.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12673.52</v>
+        <v>1747.29</v>
       </c>
       <c r="I20" t="n">
-        <v>12673.52</v>
+        <v>1747.29</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>87702.55</v>
+        <v>3494.59</v>
       </c>
       <c r="M20" t="n">
-        <v>87702.55</v>
+        <v>3494.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9768.370000000001</v>
+        <v>1737.43</v>
       </c>
       <c r="I21" t="n">
-        <v>9768.370000000001</v>
+        <v>1737.43</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>52826.69</v>
+        <v>91447.39999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>52826.69</v>
+        <v>91447.39999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8492.07</v>
+        <v>1516.55</v>
       </c>
       <c r="I22" t="n">
-        <v>8492.07</v>
+        <v>1516.55</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5767.87</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5767.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIREYA LIZETTE TORRES GARCIA</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,38 +1307,38 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>7955.43</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>7955.43</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2488.17</v>
       </c>
       <c r="L23" t="n">
-        <v>17731.98</v>
+        <v>27369.85</v>
       </c>
       <c r="M23" t="n">
-        <v>17731.98</v>
+        <v>29858.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARIA TERESA ASENCIO LOZANO</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>7017.46</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7017.46</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,26 +1362,26 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1892.23</v>
+        <v>52810.13</v>
       </c>
       <c r="M24" t="n">
-        <v>1892.23</v>
+        <v>52810.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VELIA PATRICIA BERNAL RAMOS</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1393,38 +1393,38 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6826.89</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>6826.89</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>39037.05</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>21567.01</v>
+        <v>26414.27</v>
       </c>
       <c r="M25" t="n">
-        <v>60604.06</v>
+        <v>26414.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6098.62</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>6098.62</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6410.16</v>
+        <v>49113.6</v>
       </c>
       <c r="M26" t="n">
-        <v>6410.16</v>
+        <v>49113.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,50 +1467,50 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO LUNA LARA</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>6097.65</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>6097.65</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>115099.97</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>67074.12</v>
+        <v>28256.41</v>
       </c>
       <c r="M27" t="n">
-        <v>182174.09</v>
+        <v>28256.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA RIOS BERNAL</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6060.91</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>6060.91</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>42404.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>42404.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5819.76</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5819.76</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1577,16 +1577,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>103979.43</v>
+        <v>68825.82000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>103979.43</v>
+        <v>68825.82000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>108404</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+          <t>GERARDO DANIEL BARAJAS TORRES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1961.92</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3571.33</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>5533.25</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>35470.88</v>
+        <v>4796.14</v>
       </c>
       <c r="M30" t="n">
-        <v>35470.88</v>
+        <v>4796.14</v>
       </c>
     </row>
     <row r="31">
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>5319.15</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>5319.15</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1663,41 +1663,41 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>15937.48</v>
+        <v>17269.74</v>
       </c>
       <c r="M31" t="n">
-        <v>15937.48</v>
+        <v>17269.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>ANA VERONICA GONZALEZ GAYTAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4800.92</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4800.92</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>52810.13</v>
+        <v>3487.19</v>
       </c>
       <c r="M32" t="n">
-        <v>52810.13</v>
+        <v>3487.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>MARIA JOSE GUZMAN ZAMORA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4274.58</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4274.58</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1749,26 +1749,26 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>6584.58</v>
+        <v>1693.99</v>
       </c>
       <c r="M33" t="n">
-        <v>6584.58</v>
+        <v>1693.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA CARLOS VAZQUEZ</t>
+          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3693.35</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3693.35</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1792,26 +1792,26 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>17425.73</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>17425.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
+          <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3521.42</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3521.42</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>20619.61</v>
+        <v>6410.16</v>
       </c>
       <c r="M35" t="n">
-        <v>20619.61</v>
+        <v>6410.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2966.58</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2966.58</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>18650.03</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>18650.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>JORGE ANTONIO LUNA LARA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2401.3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2401.3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>26414.27</v>
+        <v>67074.12</v>
       </c>
       <c r="M37" t="n">
-        <v>26414.27</v>
+        <v>67074.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+          <t>JOSE RENE DE ALBA MORALES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2072.23</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2072.23</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>18650.03</v>
+        <v>14427.08</v>
       </c>
       <c r="M38" t="n">
-        <v>18650.03</v>
+        <v>14427.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>108405</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1983,22 +1983,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1457.43</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>510.39</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1967.82</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>26288.67</v>
+        <v>3041.47</v>
       </c>
       <c r="M39" t="n">
-        <v>26288.67</v>
+        <v>3041.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+          <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1702.63</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1702.63</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17425.73</v>
+        <v>39833.53</v>
       </c>
       <c r="M40" t="n">
-        <v>17425.73</v>
+        <v>39833.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARIA JOSE GUZMAN ZAMORA</t>
+          <t>MIREYA LIZETTE TORRES GARCIA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1693.99</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1693.99</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1693.99</v>
+        <v>23106.58</v>
       </c>
       <c r="M41" t="n">
-        <v>1693.99</v>
+        <v>23106.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1598.75</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1598.75</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>12811.03</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>12811.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>103982</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>MARIA FERNANDA RIOS BERNAL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1040.74</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1040.74</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2179,26 +2179,26 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>5241.88</v>
+        <v>6060.86</v>
       </c>
       <c r="M43" t="n">
-        <v>5241.88</v>
+        <v>6060.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>SAMUEL NUÐO RIVERA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2488.17</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>27369.85</v>
+        <v>3214.14</v>
       </c>
       <c r="M44" t="n">
-        <v>29858.02</v>
+        <v>3214.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2265,16 +2265,16 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>12605.42</v>
+        <v>56725.37</v>
       </c>
       <c r="M45" t="n">
-        <v>12605.42</v>
+        <v>56725.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>DARINKA UREÐA CASILLAS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.48</v>
+        <v>86129.07000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>1428.48</v>
+        <v>86129.07000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>108405</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+          <t>DESIREE DE LA PEÐA OROZCO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2345,16 +2345,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>72893.8</v>
       </c>
       <c r="L47" t="n">
-        <v>3041.47</v>
+        <v>80312.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3041.47</v>
+        <v>153206.55</v>
       </c>
     </row>
   </sheetData>

--- a/administrador/pagado_emitido/pagado_emitido.xlsx
+++ b/administrador/pagado_emitido/pagado_emitido.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>8 de septiembre de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -490,10 +490,10 @@
         <v>39037.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1821.92</v>
+        <v>6821.96</v>
       </c>
       <c r="I4" t="n">
-        <v>40858.97</v>
+        <v>45859.01</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,16 +502,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>24779.71</v>
+        <v>19745.09</v>
       </c>
       <c r="M4" t="n">
-        <v>24779.71</v>
+        <v>19745.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,22 +521,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SOFIA CAMPILLO VASCONCELOS</t>
+          <t>ANAIS LUA MORENO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>29655.2</v>
       </c>
       <c r="H5" t="n">
-        <v>13505.41</v>
+        <v>11503.4</v>
       </c>
       <c r="I5" t="n">
-        <v>13505.41</v>
+        <v>41158.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,26 +545,26 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>94372.73</v>
+        <v>89858.53999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>94372.73</v>
+        <v>89858.53999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MONSERRAT VELASCO SANTOS</t>
+          <t>SOFIA CAMPILLO VASCONCELOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>10023.33</v>
+        <v>14976.76</v>
       </c>
       <c r="I6" t="n">
-        <v>10023.33</v>
+        <v>14976.76</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -588,26 +588,26 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>65066.43</v>
+        <v>94372.73</v>
       </c>
       <c r="M6" t="n">
-        <v>65066.43</v>
+        <v>94372.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ANAIS LUA MORENO</t>
+          <t>MONSERRAT VELASCO SANTOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -619,10 +619,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9440.07</v>
+        <v>10023.33</v>
       </c>
       <c r="I7" t="n">
-        <v>9440.07</v>
+        <v>10023.33</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>89858.53999999999</v>
+        <v>65066.43</v>
       </c>
       <c r="M7" t="n">
-        <v>89858.53999999999</v>
+        <v>65066.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>87538</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
+          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -662,28 +662,28 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8492.07</v>
+        <v>9142.639999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8492.07</v>
+        <v>9142.639999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9832.18</v>
       </c>
       <c r="L8" t="n">
-        <v>3845.25</v>
+        <v>234093.61</v>
       </c>
       <c r="M8" t="n">
-        <v>3845.25</v>
+        <v>243925.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>87538</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MONICA ANDREA AMBRIZ GOMEZ</t>
+          <t>ANDREA CELESTE IBAÐEZ RINCON</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7409.62</v>
+        <v>8492.07</v>
       </c>
       <c r="I9" t="n">
-        <v>7409.62</v>
+        <v>8492.07</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>235826.63</v>
+        <v>3845.25</v>
       </c>
       <c r="M9" t="n">
-        <v>235826.63</v>
+        <v>3845.25</v>
       </c>
     </row>
     <row r="10">
@@ -941,17 +941,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+          <t>PAULA ANGELICA LOMELI CAZARES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2966.58</v>
+        <v>3524.19</v>
       </c>
       <c r="I15" t="n">
-        <v>2966.58</v>
+        <v>3524.19</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>68825.82000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>68825.82000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
+          <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2426.76</v>
+        <v>2966.58</v>
       </c>
       <c r="I16" t="n">
-        <v>2426.76</v>
+        <v>2966.58</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>38711.19</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>38711.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JULIANA RIASCOS VALENCIA</t>
+          <t>PAULINA LIZBETH SOTO MUÐIZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2408.61</v>
+        <v>2426.76</v>
       </c>
       <c r="I17" t="n">
-        <v>2408.61</v>
+        <v>2426.76</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5453.73</v>
+        <v>38711.19</v>
       </c>
       <c r="M17" t="n">
-        <v>5453.73</v>
+        <v>38711.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+          <t>JULIANA RIASCOS VALENCIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1800.77</v>
+        <v>2408.61</v>
       </c>
       <c r="I18" t="n">
-        <v>1800.77</v>
+        <v>2408.61</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>10804.65</v>
+        <v>5453.73</v>
       </c>
       <c r="M18" t="n">
-        <v>10804.65</v>
+        <v>5453.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
+          <t>JOSE ANTEMIO OLIVA SANTOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1761.04</v>
+        <v>1967.73</v>
       </c>
       <c r="I19" t="n">
-        <v>1761.04</v>
+        <v>1967.73</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1147,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7337.05</v>
+        <v>26288.67</v>
       </c>
       <c r="M19" t="n">
-        <v>7337.05</v>
+        <v>26288.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PAULINA RODRIGUEZ DE LA MORA</t>
+          <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1747.29</v>
+        <v>1800.77</v>
       </c>
       <c r="I20" t="n">
-        <v>1747.29</v>
+        <v>1800.77</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>3494.59</v>
+        <v>10804.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3494.59</v>
+        <v>10804.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GABRIELA CASTAÐEDA SALAZAR</t>
+          <t>JOSE EDUARDO EZQUERRO BARQUERA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1737.43</v>
+        <v>1761.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1737.43</v>
+        <v>1761.04</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>91447.39999999999</v>
+        <v>7337.05</v>
       </c>
       <c r="M21" t="n">
-        <v>91447.39999999999</v>
+        <v>7337.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+          <t>PAULINA RODRIGUEZ DE LA MORA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1516.55</v>
+        <v>1747.29</v>
       </c>
       <c r="I22" t="n">
-        <v>1516.55</v>
+        <v>1747.29</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1276,26 +1276,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3494.59</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3494.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
+          <t>GABRIELA CASTAÐEDA SALAZAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1307,38 +1307,38 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1737.43</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1737.43</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>2488.17</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>27369.85</v>
+        <v>91447.39999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>29858.02</v>
+        <v>91447.39999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
+          <t>ISAI ANTONIO ROJAS MARTINEZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1516.55</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1516.55</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1362,26 +1362,26 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>52810.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>52810.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OSCAR RAMIREZ RUIZ</t>
+          <t>GUILLERMO JOSE RAMIREZ RAMIREZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1399,32 +1399,32 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2488.17</v>
       </c>
       <c r="L25" t="n">
-        <v>26414.27</v>
+        <v>27369.85</v>
       </c>
       <c r="M25" t="n">
-        <v>26414.27</v>
+        <v>29858.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>119447</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
+          <t>LUIS ANTONIO SALAZAR ESPINOSA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>49113.6</v>
+        <v>52810.13</v>
       </c>
       <c r="M26" t="n">
-        <v>49113.6</v>
+        <v>52810.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1491,26 +1491,26 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>28256.41</v>
+        <v>26414.27</v>
       </c>
       <c r="M27" t="n">
-        <v>28256.41</v>
+        <v>26414.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARIO IVAN ROMERO GONZALEZ</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>42404.25</v>
+        <v>49113.6</v>
       </c>
       <c r="M28" t="n">
-        <v>42404.25</v>
+        <v>49113.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAULA ANGELICA LOMELI CAZARES</t>
+          <t>MARIO IVAN ROMERO GONZALEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>68825.82000000001</v>
+        <v>42404.25</v>
       </c>
       <c r="M29" t="n">
-        <v>68825.82000000001</v>
+        <v>42404.25</v>
       </c>
     </row>
     <row r="30">
